--- a/data/historico/semana_318.xlsx
+++ b/data/historico/semana_318.xlsx
@@ -31,7 +31,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$F$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$E$39</definedName>
   </definedNames>
@@ -4898,19 +4898,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (3 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
+          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (4 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4942,71 +4942,93 @@
     <row r="3">
       <c r="A3" s="31" t="inlineStr">
         <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="31" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="C3" s="31" t="inlineStr">
+        <is>
+          <t>Férias/Atestado (automático)</t>
+        </is>
+      </c>
+      <c r="D3" s="31" t="inlineStr">
+        <is>
+          <t>Rafael Ramos Recalde</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="31" t="inlineStr">
+        <is>
           <t>23/07/2026</t>
         </is>
       </c>
-      <c r="B3" s="31" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>07/08/2026</t>
         </is>
       </c>
-      <c r="C3" s="31" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
         <is>
           <t>Férias/Atestado (automático)</t>
         </is>
       </c>
-      <c r="D3" s="31" t="inlineStr">
+      <c r="D4" s="31" t="inlineStr">
         <is>
           <t>Agente_3035</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="32" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="32" t="inlineStr">
-        <is>
-          <t>06/08/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="32" t="inlineStr">
-        <is>
-          <t>Levantamento de Índice</t>
-        </is>
-      </c>
-      <c r="D4" s="32" t="inlineStr">
-        <is>
-          <t>Todos os agentes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="32" t="inlineStr">
         <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="32" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="32" t="inlineStr">
+        <is>
+          <t>Levantamento de Índice</t>
+        </is>
+      </c>
+      <c r="D5" s="32" t="inlineStr">
+        <is>
+          <t>Todos os agentes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="32" t="inlineStr">
+        <is>
           <t>07/08/2026</t>
         </is>
       </c>
-      <c r="B5" s="32" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>07/08/2026</t>
         </is>
       </c>
-      <c r="C5" s="32" t="inlineStr">
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>Instalação de Ovitrampa</t>
         </is>
       </c>
-      <c r="D5" s="32" t="inlineStr">
+      <c r="D6" s="32" t="inlineStr">
         <is>
           <t>Todos os agentes</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D5"/>
+  <autoFilter ref="A2:D6"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -16408,47 +16430,47 @@
     <row r="9">
       <c r="A9" s="23" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Gisele Olimpia Torres</t>
         </is>
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
         <is>
-          <t>16758244</t>
+          <t>16759717</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
         <is>
-          <t>408 - PARQUE DE EXPOSIÇÕES</t>
+          <t>421 - JARDIM IPANEMA</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q035</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t>Avenida PROCURADOR DR. WILSON DIAS DE PINHO</t>
+          <t>Rua BALTAZAR SALDANHA</t>
         </is>
       </c>
       <c r="G9" s="23" t="inlineStr">
         <is>
-          <t>175 - 1 - C</t>
+          <t>779 - OU</t>
         </is>
       </c>
       <c r="H9" s="23" t="inlineStr">
         <is>
-          <t>05/08/2026 07:41</t>
+          <t>05/08/2026 09:03</t>
         </is>
       </c>
       <c r="I9" s="23" t="inlineStr">
         <is>
-          <t>05/08/2026 08:00</t>
+          <t>05/08/2026 09:22</t>
         </is>
       </c>
       <c r="J9" s="23" t="n">
@@ -16458,47 +16480,47 @@
     <row r="10">
       <c r="A10" s="23" t="inlineStr">
         <is>
-          <t>Gisele Olimpia Torres</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>16759717</t>
+          <t>16758244</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
         <is>
-          <t>421 - JARDIM IPANEMA</t>
+          <t>408 - PARQUE DE EXPOSIÇÕES</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
         <is>
-          <t>Q035</t>
+          <t>Q027</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
         <is>
-          <t>Rua BALTAZAR SALDANHA</t>
+          <t>Avenida PROCURADOR DR. WILSON DIAS DE PINHO</t>
         </is>
       </c>
       <c r="G10" s="23" t="inlineStr">
         <is>
-          <t>779 - OU</t>
+          <t>175 - 1 - C</t>
         </is>
       </c>
       <c r="H10" s="23" t="inlineStr">
         <is>
-          <t>05/08/2026 09:03</t>
+          <t>05/08/2026 07:41</t>
         </is>
       </c>
       <c r="I10" s="23" t="inlineStr">
         <is>
-          <t>05/08/2026 09:22</t>
+          <t>05/08/2026 08:00</t>
         </is>
       </c>
       <c r="J10" s="23" t="n">
@@ -16558,47 +16580,47 @@
     <row r="12">
       <c r="A12" s="23" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>16760781</t>
+          <t>16739131</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>405 - ALTOS DA GLÓRIA</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q034</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
         <is>
-          <t>Rua JOAQUIM PEREIRA TEIXEIRA</t>
+          <t>Rua BARRA BONITA</t>
         </is>
       </c>
       <c r="G12" s="23" t="inlineStr">
         <is>
-          <t>355 - 1 - R</t>
+          <t>50 - R</t>
         </is>
       </c>
       <c r="H12" s="23" t="inlineStr">
         <is>
-          <t>05/08/2026 13:52</t>
+          <t>04/08/2026 15:37</t>
         </is>
       </c>
       <c r="I12" s="23" t="inlineStr">
         <is>
-          <t>05/08/2026 14:09</t>
+          <t>04/08/2026 15:54</t>
         </is>
       </c>
       <c r="J12" s="23" t="n">
@@ -16608,47 +16630,47 @@
     <row r="13">
       <c r="A13" s="23" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
-          <t>16739131</t>
+          <t>16760781</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
         <is>
-          <t>405 - ALTOS DA GLÓRIA</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
         <is>
-          <t>Q034</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t>Rua BARRA BONITA</t>
+          <t>Rua JOAQUIM PEREIRA TEIXEIRA</t>
         </is>
       </c>
       <c r="G13" s="23" t="inlineStr">
         <is>
-          <t>50 - R</t>
+          <t>355 - 1 - R</t>
         </is>
       </c>
       <c r="H13" s="23" t="inlineStr">
         <is>
-          <t>04/08/2026 15:37</t>
+          <t>05/08/2026 13:52</t>
         </is>
       </c>
       <c r="I13" s="23" t="inlineStr">
         <is>
-          <t>04/08/2026 15:54</t>
+          <t>05/08/2026 14:09</t>
         </is>
       </c>
       <c r="J13" s="23" t="n">
@@ -16708,47 +16730,47 @@
     <row r="15">
       <c r="A15" s="23" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Gisele Olimpia Torres</t>
         </is>
       </c>
       <c r="B15" s="23" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
         <is>
-          <t>16762597</t>
+          <t>16733193</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>421 - JARDIM IPANEMA</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q029</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
-          <t>Rua FRANCISCO FAUSTO MACENAS</t>
+          <t>Rua BALTAZAR SALDANHA</t>
         </is>
       </c>
       <c r="G15" s="23" t="inlineStr">
         <is>
-          <t>651 - R</t>
+          <t>1501 - OU</t>
         </is>
       </c>
       <c r="H15" s="23" t="inlineStr">
         <is>
-          <t>05/08/2026 09:49</t>
+          <t>04/08/2026 14:46</t>
         </is>
       </c>
       <c r="I15" s="23" t="inlineStr">
         <is>
-          <t>05/08/2026 10:05</t>
+          <t>04/08/2026 15:02</t>
         </is>
       </c>
       <c r="J15" s="23" t="n">
@@ -16768,7 +16790,7 @@
       </c>
       <c r="C16" s="24" t="inlineStr">
         <is>
-          <t>16733193</t>
+          <t>16759754</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -16778,27 +16800,27 @@
       </c>
       <c r="E16" s="23" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="F16" s="23" t="inlineStr">
         <is>
-          <t>Rua BALTAZAR SALDANHA</t>
+          <t>Rua TUIUTI</t>
         </is>
       </c>
       <c r="G16" s="23" t="inlineStr">
         <is>
-          <t>1501 - OU</t>
+          <t>360 - R</t>
         </is>
       </c>
       <c r="H16" s="23" t="inlineStr">
         <is>
-          <t>04/08/2026 14:46</t>
+          <t>05/08/2026 15:15</t>
         </is>
       </c>
       <c r="I16" s="23" t="inlineStr">
         <is>
-          <t>04/08/2026 15:02</t>
+          <t>05/08/2026 15:31</t>
         </is>
       </c>
       <c r="J16" s="23" t="n">
@@ -16808,47 +16830,47 @@
     <row r="17">
       <c r="A17" s="23" t="inlineStr">
         <is>
-          <t>Gisele Olimpia Torres</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
         <is>
-          <t>16759754</t>
+          <t>16762597</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
         <is>
-          <t>421 - JARDIM IPANEMA</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q028</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t>Rua TUIUTI</t>
+          <t>Rua FRANCISCO FAUSTO MACENAS</t>
         </is>
       </c>
       <c r="G17" s="23" t="inlineStr">
         <is>
-          <t>360 - R</t>
+          <t>651 - R</t>
         </is>
       </c>
       <c r="H17" s="23" t="inlineStr">
         <is>
-          <t>05/08/2026 15:15</t>
+          <t>05/08/2026 09:49</t>
         </is>
       </c>
       <c r="I17" s="23" t="inlineStr">
         <is>
-          <t>05/08/2026 15:31</t>
+          <t>05/08/2026 10:05</t>
         </is>
       </c>
       <c r="J17" s="23" t="n">

--- a/data/historico/semana_318.xlsx
+++ b/data/historico/semana_318.xlsx
@@ -22,8 +22,8 @@
     <sheet name="Ranking" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumo Geral'!$A$2:$AC$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Por Área'!$A$2:$N$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumo Geral'!$A$2:$AC$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Por Área'!$A$2:$N$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Visitas Duplicadas'!$A$2:$J$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Visitas Suspeitas'!$A$2:$K$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Visitas Negativas'!$A$2:$K$2</definedName>
@@ -33,7 +33,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$F$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$E$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$E$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -732,7 +732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC57"/>
+  <dimension ref="A1:AC58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -4659,7 +4659,7 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -4673,16 +4673,16 @@
         </is>
       </c>
       <c r="D39" s="4" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>15.33</v>
+        <v>9</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>6.39</v>
+        <v>6.78</v>
       </c>
       <c r="H39" s="4" t="n">
         <v>6</v>
@@ -4700,7 +4700,7 @@
         <v>0</v>
       </c>
       <c r="M39" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N39" s="4" t="n">
         <v>0</v>
@@ -4715,170 +4715,267 @@
         <v>0</v>
       </c>
       <c r="R39" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="S39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="U39" s="4" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="V39" s="4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W39" s="4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X39" s="4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y39" s="4" t="inlineStr">
+        <is>
+          <t>R$ 217,42</t>
+        </is>
+      </c>
+      <c r="Z39" s="4" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AA39" s="4" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AB39" s="4" t="n"/>
+      <c r="AC39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Silvina Regina de Souza Valiente</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>🟢 NORMAL</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="S39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" s="4" t="n">
+      <c r="S40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="4" t="n">
         <v>62</v>
       </c>
-      <c r="U39" s="4" t="n">
+      <c r="U40" s="4" t="n">
         <v>25.81</v>
       </c>
-      <c r="V39" s="4" t="n">
+      <c r="V40" s="4" t="n">
         <v>2.69</v>
       </c>
-      <c r="W39" s="4" t="n">
+      <c r="W40" s="4" t="n">
         <v>8.08</v>
       </c>
-      <c r="X39" s="4" t="n">
+      <c r="X40" s="4" t="n">
         <v>1.63</v>
       </c>
-      <c r="Y39" s="4" t="inlineStr">
+      <c r="Y40" s="4" t="inlineStr">
         <is>
           <t>R$ 135,33</t>
         </is>
       </c>
-      <c r="Z39" s="4" t="inlineStr">
+      <c r="Z40" s="4" t="inlineStr">
         <is>
           <t>09:43</t>
         </is>
       </c>
-      <c r="AA39" s="4" t="inlineStr">
+      <c r="AA40" s="4" t="inlineStr">
         <is>
           <t>10:39</t>
         </is>
       </c>
-      <c r="AB39" s="4" t="inlineStr">
+      <c r="AB40" s="4" t="inlineStr">
         <is>
           <t>14:25</t>
         </is>
       </c>
-      <c r="AC39" s="4" t="inlineStr">
+      <c r="AC40" s="4" t="inlineStr">
         <is>
           <t>16:42</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>LEGENDA — CLASSIFICAÇÃO (baseada em % de Visitas Rápidas)</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>🟢 NORMAL</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>% Rápidas até 10%</t>
         </is>
       </c>
-      <c r="C43" s="10" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="11" t="inlineStr">
+      <c r="C44" s="10" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>🟡 ATENÇÃO</t>
         </is>
       </c>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>% Rápidas entre 11% e 20%</t>
         </is>
       </c>
-      <c r="C44" s="10" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="12" t="inlineStr">
+      <c r="C45" s="10" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
       </c>
-      <c r="B45" s="9" t="inlineStr">
+      <c r="B46" s="9" t="inlineStr">
         <is>
           <t>% Rápidas acima de 20%</t>
         </is>
       </c>
-      <c r="C45" s="10" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="13" t="inlineStr">
+      <c r="C46" s="10" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="inlineStr">
         <is>
           <t>⚠️ SEQUÊNCIA SUSPEITA</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="45" customHeight="1">
-      <c r="A48" s="14" t="inlineStr">
+    <row r="49" ht="45" customHeight="1">
+      <c r="A49" s="14" t="inlineStr">
         <is>
           <t>Duas ou mais visitas consecutivas do mesmo agente registradas no MESMO MINUTO de chegada são marcadas como suspeitas (o e-Visita não registra segundos, então o critério de negócio de 50s de diferença equivale, na prática, a 'mesmo minuto') — sugere lançamento em lote no sistema, não visita real de campo. Colunas: 'Visitas em Sequência Suspeita' (total de visitas envolvidas) e 'Maior Sequência Suspeita' (maior número de visitas seguidas nessa condição). Na aba 'Visitas Suspeitas', a coluna 'Diferença p/ Anterior (s)*' fica em branco quando o alerta da linha veio do par com a visita SEGUINTE (não da anterior).</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="15" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="15" t="inlineStr">
         <is>
           <t>🍽️ VISITAS NO HORÁRIO DE ALMOÇO</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="70" customHeight="1">
-      <c r="A51" s="14" t="inlineStr">
+    <row r="52" ht="70" customHeight="1">
+      <c r="A52" s="14" t="inlineStr">
         <is>
           <t>Coluna 'Visitas no Almoço (11h15-12h45)' conta as visitas com chegada registrada nesse intervalo — o horário oficial de almoço é 11h15 às 12h45, JÁ COM 15 MINUTOS DE TOLERÂNCIA em cada borda (visitas entre 11h-11h15 ou 12h45-13h não são tratadas como violação, só como 'fora do expediente' genérico) — use para checar se o agente está trabalhando no horário de almoço ou se há erro de lançamento. Essas visitas ficam de fora do cálculo de 'Início/Fim Manhã' e 'Início/Fim Tarde', que usam a primeira chegada e a última saída de cada dia (não a média de todos os horários), para refletir melhor o início e o fim reais do expediente.</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="16" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="16" t="inlineStr">
         <is>
           <t>💰 HORAS TRABALHADAS, HORAS ÚTEIS E CUSTO DA HORA ÚTIL</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" s="14" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" s="14" t="inlineStr">
         <is>
           <t>'Horas Trabalhadas' = jornada total do dia (primeira chegada até a última saída), descontando a sobreposição com o horário de almoço — depois tira-se a média entre os dias/semanas trabalhados, 'Horas Úteis' = soma das durações de visita no dia (tempo realmente dentro de imóveis), sem contar deslocamento entre visitas, 'Custo Hora Útil' = salário mensal do agente (R$ 4863,00, equivalente a 3 salários mínimos federais) dividido pelas horas úteis mensais estimadas (Média Horas Úteis/Dia × 22 dias úteis/mês). Quanto menos tempo o agente passa efetivamente em visita por dia, mais caro fica o custo por hora útil.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="17" t="inlineStr">
-        <is>
-          <t>ℹ️ A lista detalhada de visitas duplicadas (com endereço) está na aba 'Visitas Duplicadas' — use-a para localizar e excluir os registros repetidos.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="17" t="inlineStr">
         <is>
+          <t>ℹ️ A lista detalhada de visitas duplicadas (com endereço) está na aba 'Visitas Duplicadas' — use-a para localizar e excluir os registros repetidos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="17" t="inlineStr">
+        <is>
           <t>ℹ️ Visitas com duração NEGATIVA (saída antes da chegada — provável bug do sistema) foram excluídas do cálculo de Média/Mediana e estão detalhadas na aba 'Visitas Negativas', para investigação junto ao suporte do e-Visita.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AC39"/>
+  <autoFilter ref="A2:AC40"/>
   <mergeCells count="13">
-    <mergeCell ref="A42:C42"/>
     <mergeCell ref="B44:C44"/>
     <mergeCell ref="A1:AC1"/>
-    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A49:C49"/>
     <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A58:C58"/>
     <mergeCell ref="B45:C45"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="A55:C55"/>
     <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A43:C43"/>
     <mergeCell ref="A54:C54"/>
     <mergeCell ref="A51:C51"/>
-    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="A52:C52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5034,7 +5131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -6149,7 +6246,7 @@
     <row r="39">
       <c r="A39" s="23" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="B39" s="23" t="inlineStr">
@@ -6158,60 +6255,78 @@
         </is>
       </c>
       <c r="C39" s="23" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="D39" s="23" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E39" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F39" s="23" t="n">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="G39" s="23" t="n">
-        <v>25.81</v>
+        <v>57.14</v>
       </c>
       <c r="H39" s="2" t="n"/>
       <c r="I39" s="2" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="33" t="inlineStr">
-        <is>
-          <t>TOTAL GERAL</t>
-        </is>
-      </c>
-      <c r="B40" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C40" s="33" t="n">
-        <v>1394</v>
-      </c>
-      <c r="D40" s="33" t="n">
-        <v>716</v>
-      </c>
-      <c r="E40" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="F40" s="33" t="n">
-        <v>2112</v>
-      </c>
-      <c r="G40" s="33" t="n">
-        <v>34</v>
+      <c r="A40" s="23" t="inlineStr">
+        <is>
+          <t>Silvina Regina de Souza Valiente</t>
+        </is>
+      </c>
+      <c r="B40" s="23" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C40" s="23" t="n">
+        <v>46</v>
+      </c>
+      <c r="D40" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="E40" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="23" t="n">
+        <v>62</v>
+      </c>
+      <c r="G40" s="23" t="n">
+        <v>25.81</v>
       </c>
       <c r="H40" s="2" t="n"/>
       <c r="I40" s="2" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="2" t="n"/>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n"/>
-      <c r="E41" s="2" t="n"/>
-      <c r="F41" s="2" t="n"/>
-      <c r="G41" s="2" t="n"/>
+      <c r="A41" s="33" t="inlineStr">
+        <is>
+          <t>TOTAL GERAL</t>
+        </is>
+      </c>
+      <c r="B41" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C41" s="33" t="n">
+        <v>1403</v>
+      </c>
+      <c r="D41" s="33" t="n">
+        <v>728</v>
+      </c>
+      <c r="E41" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" s="33" t="n">
+        <v>2133</v>
+      </c>
+      <c r="G41" s="33" t="n">
+        <v>34.22</v>
+      </c>
       <c r="H41" s="2" t="n"/>
       <c r="I41" s="2" t="n"/>
     </row>
@@ -6227,11 +6342,7 @@
       <c r="I42" s="2" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="34" t="inlineStr">
-        <is>
-          <t>DETALHE — IMÓVEIS COM VISITA RECUSADA PELO MORADOR</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="n"/>
       <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n"/>
@@ -6242,141 +6353,156 @@
       <c r="I43" s="2" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="35" t="inlineStr">
+      <c r="A44" s="34" t="inlineStr">
+        <is>
+          <t>DETALHE — IMÓVEIS COM VISITA RECUSADA PELO MORADOR</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="n"/>
+      <c r="F44" s="2" t="n"/>
+      <c r="G44" s="2" t="n"/>
+      <c r="H44" s="2" t="n"/>
+      <c r="I44" s="2" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="35" t="inlineStr">
         <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="B44" s="35" t="inlineStr">
+      <c r="B45" s="35" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="C44" s="35" t="inlineStr">
+      <c r="C45" s="35" t="inlineStr">
         <is>
           <t>ID Visita</t>
         </is>
       </c>
-      <c r="D44" s="35" t="inlineStr">
+      <c r="D45" s="35" t="inlineStr">
         <is>
           <t>Área</t>
         </is>
       </c>
-      <c r="E44" s="35" t="inlineStr">
+      <c r="E45" s="35" t="inlineStr">
         <is>
           <t>Quarteirão</t>
         </is>
       </c>
-      <c r="F44" s="35" t="inlineStr">
+      <c r="F45" s="35" t="inlineStr">
         <is>
           <t>Logradouro</t>
         </is>
       </c>
-      <c r="G44" s="35" t="inlineStr">
+      <c r="G45" s="35" t="inlineStr">
         <is>
           <t>Imóvel</t>
         </is>
       </c>
-      <c r="H44" s="35" t="inlineStr">
+      <c r="H45" s="35" t="inlineStr">
         <is>
           <t>Data Chegada</t>
         </is>
       </c>
-      <c r="I44" s="35" t="inlineStr">
+      <c r="I45" s="35" t="inlineStr">
         <is>
           <t>Data Saída</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="36" t="inlineStr">
-        <is>
-          <t>Adriana de Jesus Saraiva</t>
-        </is>
-      </c>
-      <c r="B45" s="36" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C45" s="37" t="inlineStr">
-        <is>
-          <t>16731309</t>
-        </is>
-      </c>
-      <c r="D45" s="36" t="inlineStr">
-        <is>
-          <t>404 - JARDIM DOS ESTADOS</t>
-        </is>
-      </c>
-      <c r="E45" s="36" t="inlineStr">
-        <is>
-          <t>Q011</t>
-        </is>
-      </c>
-      <c r="F45" s="36" t="inlineStr">
-        <is>
-          <t>Rua JOÃO BREMBATI CALVOSO</t>
-        </is>
-      </c>
-      <c r="G45" s="36" t="inlineStr">
-        <is>
-          <t>838 - R</t>
-        </is>
-      </c>
-      <c r="H45" s="36" t="inlineStr">
-        <is>
-          <t>04/08/2026 14:43</t>
-        </is>
-      </c>
-      <c r="I45" s="36" t="inlineStr">
-        <is>
-          <t>04/08/2026 14:43</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="36" t="inlineStr">
         <is>
+          <t>Adriana de Jesus Saraiva</t>
+        </is>
+      </c>
+      <c r="B46" s="36" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C46" s="37" t="inlineStr">
+        <is>
+          <t>16731309</t>
+        </is>
+      </c>
+      <c r="D46" s="36" t="inlineStr">
+        <is>
+          <t>404 - JARDIM DOS ESTADOS</t>
+        </is>
+      </c>
+      <c r="E46" s="36" t="inlineStr">
+        <is>
+          <t>Q011</t>
+        </is>
+      </c>
+      <c r="F46" s="36" t="inlineStr">
+        <is>
+          <t>Rua JOÃO BREMBATI CALVOSO</t>
+        </is>
+      </c>
+      <c r="G46" s="36" t="inlineStr">
+        <is>
+          <t>838 - R</t>
+        </is>
+      </c>
+      <c r="H46" s="36" t="inlineStr">
+        <is>
+          <t>04/08/2026 14:43</t>
+        </is>
+      </c>
+      <c r="I46" s="36" t="inlineStr">
+        <is>
+          <t>04/08/2026 14:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="36" t="inlineStr">
+        <is>
           <t>Gisele Olimpia Torres</t>
         </is>
       </c>
-      <c r="B46" s="36" t="inlineStr">
+      <c r="B47" s="36" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C46" s="37" t="inlineStr">
+      <c r="C47" s="37" t="inlineStr">
         <is>
           <t>16759761</t>
         </is>
       </c>
-      <c r="D46" s="36" t="inlineStr">
+      <c r="D47" s="36" t="inlineStr">
         <is>
           <t>421 - JARDIM IPANEMA</t>
         </is>
       </c>
-      <c r="E46" s="36" t="inlineStr">
+      <c r="E47" s="36" t="inlineStr">
         <is>
           <t>Q020</t>
         </is>
       </c>
-      <c r="F46" s="36" t="inlineStr">
+      <c r="F47" s="36" t="inlineStr">
         <is>
           <t>Rua HUMAITA</t>
         </is>
       </c>
-      <c r="G46" s="36" t="inlineStr">
+      <c r="G47" s="36" t="inlineStr">
         <is>
           <t>359 - R</t>
         </is>
       </c>
-      <c r="H46" s="36" t="inlineStr">
+      <c r="H47" s="36" t="inlineStr">
         <is>
           <t>05/08/2026 15:52</t>
         </is>
       </c>
-      <c r="I46" s="36" t="inlineStr">
+      <c r="I47" s="36" t="inlineStr">
         <is>
           <t>05/08/2026 15:52</t>
         </is>
@@ -6384,12 +6510,12 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A43:I43"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A44:I44"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6865,7 +6991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F250"/>
+  <dimension ref="A1:F255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -7258,16 +7384,16 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>107.4</v>
+        <v>108.4</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
@@ -7282,16 +7408,16 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>107.2</v>
+        <v>107.4</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
@@ -7306,16 +7432,16 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Carlos Alberto Albiero</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>106.8</v>
+        <v>107.2</v>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
@@ -7330,16 +7456,16 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Geancarlos Ferreira Barrios</t>
+          <t>Carlos Alberto Albiero</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>106.6</v>
+        <v>106.8</v>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
@@ -7354,16 +7480,16 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Cicero Isrrael Sanabria</t>
+          <t>Geancarlos Ferreira Barrios</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>106.2</v>
+        <v>106.6</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -7378,16 +7504,16 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Cicero Isrrael Sanabria</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>106</v>
+        <v>106.2</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -7402,16 +7528,16 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>105.6</v>
+        <v>106</v>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
@@ -7426,16 +7552,16 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>102</v>
+        <v>105.6</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
@@ -7450,16 +7576,16 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>101.2</v>
+        <v>102</v>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
@@ -7474,7 +7600,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Adriano Ricardo Thiel</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -7483,7 +7609,7 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>100.4</v>
+        <v>101.2</v>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
@@ -7498,16 +7624,16 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Adriano Ricardo Thiel</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D27" s="4" t="n">
-        <v>100.2</v>
+        <v>100.4</v>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
@@ -7522,16 +7648,16 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>100</v>
+        <v>100.2</v>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
@@ -7546,16 +7672,16 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
@@ -7570,7 +7696,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -7579,7 +7705,7 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>99.40000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
@@ -7594,16 +7720,16 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>99</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
@@ -7618,7 +7744,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -7627,7 +7753,7 @@
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>98.59999999999999</v>
+        <v>99</v>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
@@ -7642,16 +7768,16 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D33" s="4" t="n">
-        <v>96.8</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
@@ -7666,16 +7792,16 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Gisele Olimpia Torres</t>
+          <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>95.40000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
@@ -7690,16 +7816,16 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Tânia Raquel Ortiz dos Santos</t>
+          <t>Gisele Olimpia Torres</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D35" s="4" t="n">
-        <v>92</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -7714,16 +7840,16 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Tânia Raquel Ortiz dos Santos</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>90.8</v>
+        <v>92</v>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
@@ -7738,44 +7864,44 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
+          <t>Juliana Patricia Goncalves</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>🟢 EXCELENTE</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
           <t>Ramona dos Santos Oliveira</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D38" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>Mateus Falcao de Souza</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>🟡 BOM</t>
         </is>
       </c>
       <c r="F38" s="2" t="n"/>
@@ -7786,30 +7912,46 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
+          <t>Mateus Falcao de Souza</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>🟡 BOM</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
           <t>Anderson Jose de Santana</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D40" s="6" t="n">
         <v>83.8</v>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
       </c>
-      <c r="F39" s="2" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n"/>
-      <c r="B40" s="2" t="n"/>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n"/>
-      <c r="E40" s="2" t="n"/>
       <c r="F40" s="2" t="n"/>
     </row>
     <row r="41">
@@ -7821,11 +7963,7 @@
       <c r="F41" s="2" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="39" t="inlineStr">
-        <is>
-          <t>DETALHAMENTO — TODOS OS CRITÉRIOS APLICADOS POR AGENTE</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="n"/>
       <c r="B42" s="2" t="n"/>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n"/>
@@ -7833,61 +7971,47 @@
       <c r="F42" s="2" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="39" t="inlineStr">
+        <is>
+          <t>DETALHAMENTO — TODOS OS CRITÉRIOS APLICADOS POR AGENTE</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" s="2" t="n"/>
+      <c r="F43" s="2" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>Critério</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>Quantidade</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>Peso (pontos/ocorrência)</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="F44" s="3" t="inlineStr">
         <is>
           <t>Pontos Aplicados</t>
         </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="40" t="inlineStr">
-        <is>
-          <t>Adriana de Jesus Saraiva</t>
-        </is>
-      </c>
-      <c r="B44" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C44" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D44" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F44" s="40" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -7903,7 +8027,7 @@
       </c>
       <c r="C45" s="40" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D45" s="40" t="n">
@@ -7929,43 +8053,43 @@
       </c>
       <c r="C46" s="40" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D46" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F46" s="40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="40" t="inlineStr">
+        <is>
+          <t>Adriana de Jesus Saraiva</t>
+        </is>
+      </c>
+      <c r="B47" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C47" s="40" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D46" s="40" t="n">
+      <c r="D47" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="E46" s="40" t="n">
+      <c r="E47" s="40" t="n">
         <v>0.5</v>
       </c>
-      <c r="F46" s="40" t="n">
+      <c r="F47" s="40" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="41" t="inlineStr">
-        <is>
-          <t>Adriana de Jesus Saraiva</t>
-        </is>
-      </c>
-      <c r="B47" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C47" s="41" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D47" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F47" s="41" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="48">
@@ -7981,17 +8105,17 @@
       </c>
       <c r="C48" s="41" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D48" s="41" t="n">
         <v>1</v>
       </c>
       <c r="E48" s="41" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F48" s="41" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="49">
@@ -8007,7 +8131,7 @@
       </c>
       <c r="C49" s="41" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D49" s="41" t="n">
@@ -8021,29 +8145,29 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="40" t="inlineStr">
-        <is>
-          <t>Adriano Ricardo Thiel</t>
-        </is>
-      </c>
-      <c r="B50" s="40" t="inlineStr">
+      <c r="A50" s="41" t="inlineStr">
+        <is>
+          <t>Adriana de Jesus Saraiva</t>
+        </is>
+      </c>
+      <c r="B50" s="41" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C50" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D50" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F50" s="40" t="n">
-        <v>5</v>
+      <c r="C50" s="41" t="inlineStr">
+        <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D50" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F50" s="41" t="n">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="51">
@@ -8059,43 +8183,43 @@
       </c>
       <c r="C51" s="40" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D51" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F51" s="40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="40" t="inlineStr">
+        <is>
+          <t>Adriano Ricardo Thiel</t>
+        </is>
+      </c>
+      <c r="B52" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C52" s="40" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D51" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" s="40" t="n">
+      <c r="D52" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="40" t="n">
         <v>0.5</v>
       </c>
-      <c r="F51" s="40" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="41" t="inlineStr">
-        <is>
-          <t>Adriano Ricardo Thiel</t>
-        </is>
-      </c>
-      <c r="B52" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C52" s="41" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D52" s="41" t="n">
-        <v>2</v>
-      </c>
-      <c r="E52" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F52" s="41" t="n">
-        <v>-2</v>
+      <c r="F52" s="40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -8111,17 +8235,17 @@
       </c>
       <c r="C53" s="41" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D53" s="41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53" s="41" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F53" s="41" t="n">
-        <v>-0.6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="54">
@@ -8137,7 +8261,7 @@
       </c>
       <c r="C54" s="41" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D54" s="41" t="n">
@@ -8163,7 +8287,7 @@
       </c>
       <c r="C55" s="41" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D55" s="41" t="n">
@@ -8189,43 +8313,43 @@
       </c>
       <c r="C56" s="41" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D56" s="41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E56" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F56" s="41" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="41" t="inlineStr">
+        <is>
+          <t>Adriano Ricardo Thiel</t>
+        </is>
+      </c>
+      <c r="B57" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C57" s="41" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D57" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="E57" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F57" s="41" t="n">
         <v>-1.8</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="40" t="inlineStr">
-        <is>
-          <t>Ana Gabriela Silva Garcete</t>
-        </is>
-      </c>
-      <c r="B57" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C57" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D57" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F57" s="40" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="58">
@@ -8241,7 +8365,7 @@
       </c>
       <c r="C58" s="40" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D58" s="40" t="n">
@@ -8267,43 +8391,43 @@
       </c>
       <c r="C59" s="40" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D59" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F59" s="40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="40" t="inlineStr">
+        <is>
+          <t>Ana Gabriela Silva Garcete</t>
+        </is>
+      </c>
+      <c r="B60" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C60" s="40" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D59" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E59" s="40" t="n">
+      <c r="D60" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="40" t="n">
         <v>0.5</v>
       </c>
-      <c r="F59" s="40" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="41" t="inlineStr">
-        <is>
-          <t>Ana Gabriela Silva Garcete</t>
-        </is>
-      </c>
-      <c r="B60" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C60" s="41" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D60" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F60" s="41" t="n">
-        <v>-1</v>
+      <c r="F60" s="40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -8319,17 +8443,17 @@
       </c>
       <c r="C61" s="41" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D61" s="41" t="n">
         <v>1</v>
       </c>
       <c r="E61" s="41" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F61" s="41" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="62">
@@ -8345,7 +8469,7 @@
       </c>
       <c r="C62" s="41" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D62" s="41" t="n">
@@ -8359,29 +8483,29 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="40" t="inlineStr">
-        <is>
-          <t>Anderson Jose de Santana</t>
-        </is>
-      </c>
-      <c r="B63" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C63" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D63" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E63" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F63" s="40" t="n">
-        <v>5</v>
+      <c r="A63" s="41" t="inlineStr">
+        <is>
+          <t>Ana Gabriela Silva Garcete</t>
+        </is>
+      </c>
+      <c r="B63" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C63" s="41" t="inlineStr">
+        <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D63" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F63" s="41" t="n">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="64">
@@ -8397,43 +8521,43 @@
       </c>
       <c r="C64" s="40" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D64" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F64" s="40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="40" t="inlineStr">
+        <is>
+          <t>Anderson Jose de Santana</t>
+        </is>
+      </c>
+      <c r="B65" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C65" s="40" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D64" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" s="40" t="n">
+      <c r="D65" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="40" t="n">
         <v>0.5</v>
       </c>
-      <c r="F64" s="40" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="41" t="inlineStr">
-        <is>
-          <t>Anderson Jose de Santana</t>
-        </is>
-      </c>
-      <c r="B65" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C65" s="41" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D65" s="41" t="n">
-        <v>3</v>
-      </c>
-      <c r="E65" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F65" s="41" t="n">
-        <v>-3</v>
+      <c r="F65" s="40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -8449,17 +8573,17 @@
       </c>
       <c r="C66" s="41" t="inlineStr">
         <is>
-          <t>Fim manhã antes de 10h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D66" s="41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E66" s="41" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F66" s="41" t="n">
-        <v>-0.6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="67">
@@ -8475,17 +8599,17 @@
       </c>
       <c r="C67" s="41" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D67" s="41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E67" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F67" s="41" t="n">
-        <v>-1.8</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="68">
@@ -8501,17 +8625,17 @@
       </c>
       <c r="C68" s="41" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D68" s="41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E68" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F68" s="41" t="n">
-        <v>-0.6</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="69">
@@ -8527,43 +8651,43 @@
       </c>
       <c r="C69" s="41" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D69" s="41" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="E69" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F69" s="41" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="41" t="inlineStr">
+        <is>
+          <t>Anderson Jose de Santana</t>
+        </is>
+      </c>
+      <c r="B70" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C70" s="41" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D70" s="41" t="n">
+        <v>27</v>
+      </c>
+      <c r="E70" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F70" s="41" t="n">
         <v>-16.2</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="40" t="inlineStr">
-        <is>
-          <t>Bianca Afonso Narbaez</t>
-        </is>
-      </c>
-      <c r="B70" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C70" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D70" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E70" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F70" s="40" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="71">
@@ -8579,7 +8703,7 @@
       </c>
       <c r="C71" s="40" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D71" s="40" t="n">
@@ -8605,69 +8729,69 @@
       </c>
       <c r="C72" s="40" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D72" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F72" s="40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="40" t="inlineStr">
+        <is>
+          <t>Bianca Afonso Narbaez</t>
+        </is>
+      </c>
+      <c r="B73" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C73" s="40" t="inlineStr">
+        <is>
           <t>Bônus: pontualidade perfeita no período</t>
         </is>
       </c>
-      <c r="D72" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E72" s="40" t="n">
+      <c r="D73" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="F72" s="40" t="n">
+      <c r="F73" s="40" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="41" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="41" t="inlineStr">
         <is>
           <t>Bianca Afonso Narbaez</t>
         </is>
       </c>
-      <c r="B73" s="41" t="inlineStr">
+      <c r="B74" s="41" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C73" s="41" t="inlineStr">
+      <c r="C74" s="41" t="inlineStr">
         <is>
           <t>Dia sem bater a meta diária</t>
         </is>
       </c>
-      <c r="D73" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" s="41" t="n">
+      <c r="D74" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" s="41" t="n">
         <v>0.5</v>
       </c>
-      <c r="F73" s="41" t="n">
+      <c r="F74" s="41" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="40" t="inlineStr">
-        <is>
-          <t>Carlos Alberto Albiero</t>
-        </is>
-      </c>
-      <c r="B74" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C74" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D74" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E74" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F74" s="40" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="75">
@@ -8683,7 +8807,7 @@
       </c>
       <c r="C75" s="40" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D75" s="40" t="n">
@@ -8697,29 +8821,29 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="41" t="inlineStr">
+      <c r="A76" s="40" t="inlineStr">
         <is>
           <t>Carlos Alberto Albiero</t>
         </is>
       </c>
-      <c r="B76" s="41" t="inlineStr">
+      <c r="B76" s="40" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C76" s="41" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D76" s="41" t="n">
-        <v>2</v>
-      </c>
-      <c r="E76" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F76" s="41" t="n">
-        <v>-2</v>
+      <c r="C76" s="40" t="inlineStr">
+        <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D76" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F76" s="40" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="77">
@@ -8735,17 +8859,17 @@
       </c>
       <c r="C77" s="41" t="inlineStr">
         <is>
-          <t>Fim manhã antes de 10h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D77" s="41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E77" s="41" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F77" s="41" t="n">
-        <v>-0.6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="78">
@@ -8761,7 +8885,7 @@
       </c>
       <c r="C78" s="41" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D78" s="41" t="n">
@@ -8775,29 +8899,29 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="40" t="inlineStr">
-        <is>
-          <t>Cicero Isrrael Sanabria</t>
-        </is>
-      </c>
-      <c r="B79" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C79" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D79" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E79" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F79" s="40" t="n">
-        <v>5</v>
+      <c r="A79" s="41" t="inlineStr">
+        <is>
+          <t>Carlos Alberto Albiero</t>
+        </is>
+      </c>
+      <c r="B79" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C79" s="41" t="inlineStr">
+        <is>
+          <t>Início manhã após 08h30</t>
+        </is>
+      </c>
+      <c r="D79" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F79" s="41" t="n">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="80">
@@ -8813,7 +8937,7 @@
       </c>
       <c r="C80" s="40" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D80" s="40" t="n">
@@ -8827,29 +8951,29 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="41" t="inlineStr">
+      <c r="A81" s="40" t="inlineStr">
         <is>
           <t>Cicero Isrrael Sanabria</t>
         </is>
       </c>
-      <c r="B81" s="41" t="inlineStr">
+      <c r="B81" s="40" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C81" s="41" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D81" s="41" t="n">
-        <v>2</v>
-      </c>
-      <c r="E81" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F81" s="41" t="n">
-        <v>-2</v>
+      <c r="C81" s="40" t="inlineStr">
+        <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D81" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F81" s="40" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="82">
@@ -8865,17 +8989,17 @@
       </c>
       <c r="C82" s="41" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D82" s="41" t="n">
         <v>2</v>
       </c>
       <c r="E82" s="41" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F82" s="41" t="n">
-        <v>-1.2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="83">
@@ -8891,43 +9015,43 @@
       </c>
       <c r="C83" s="41" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D83" s="41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E83" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F83" s="41" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="41" t="inlineStr">
+        <is>
+          <t>Cicero Isrrael Sanabria</t>
+        </is>
+      </c>
+      <c r="B84" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C84" s="41" t="inlineStr">
+        <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D84" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F84" s="41" t="n">
         <v>-0.6</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="40" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B84" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C84" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D84" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E84" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F84" s="40" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="85">
@@ -8943,7 +9067,7 @@
       </c>
       <c r="C85" s="40" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D85" s="40" t="n">
@@ -8957,29 +9081,29 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="41" t="inlineStr">
+      <c r="A86" s="40" t="inlineStr">
         <is>
           <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
-      <c r="B86" s="41" t="inlineStr">
+      <c r="B86" s="40" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C86" s="41" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D86" s="41" t="n">
-        <v>2</v>
-      </c>
-      <c r="E86" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F86" s="41" t="n">
-        <v>-2</v>
+      <c r="C86" s="40" t="inlineStr">
+        <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D86" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F86" s="40" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="87">
@@ -8995,43 +9119,43 @@
       </c>
       <c r="C87" s="41" t="inlineStr">
         <is>
+          <t>Dia sem bater a meta diária</t>
+        </is>
+      </c>
+      <c r="D87" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E87" s="41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F87" s="41" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="41" t="inlineStr">
+        <is>
+          <t>Claine Luisa Figueiredo Torraca</t>
+        </is>
+      </c>
+      <c r="B88" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C88" s="41" t="inlineStr">
+        <is>
           <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
-      <c r="D87" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E87" s="41" t="n">
+      <c r="D88" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" s="41" t="n">
         <v>0.3</v>
       </c>
-      <c r="F87" s="41" t="n">
+      <c r="F88" s="41" t="n">
         <v>-0.6</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="40" t="inlineStr">
-        <is>
-          <t>Cris Milene Cardenas da Silva</t>
-        </is>
-      </c>
-      <c r="B88" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C88" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D88" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E88" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F88" s="40" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="89">
@@ -9047,7 +9171,7 @@
       </c>
       <c r="C89" s="40" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D89" s="40" t="n">
@@ -9073,43 +9197,43 @@
       </c>
       <c r="C90" s="40" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D90" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F90" s="40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="40" t="inlineStr">
+        <is>
+          <t>Cris Milene Cardenas da Silva</t>
+        </is>
+      </c>
+      <c r="B91" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C91" s="40" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D90" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E90" s="40" t="n">
+      <c r="D91" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" s="40" t="n">
         <v>0.5</v>
       </c>
-      <c r="F90" s="40" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="41" t="inlineStr">
-        <is>
-          <t>Cris Milene Cardenas da Silva</t>
-        </is>
-      </c>
-      <c r="B91" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C91" s="41" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D91" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E91" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F91" s="41" t="n">
-        <v>-1</v>
+      <c r="F91" s="40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -9125,43 +9249,43 @@
       </c>
       <c r="C92" s="41" t="inlineStr">
         <is>
+          <t>Dia sem bater a meta diária</t>
+        </is>
+      </c>
+      <c r="D92" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" s="41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F92" s="41" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="41" t="inlineStr">
+        <is>
+          <t>Cris Milene Cardenas da Silva</t>
+        </is>
+      </c>
+      <c r="B93" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C93" s="41" t="inlineStr">
+        <is>
           <t>Início manhã após 08h30</t>
         </is>
       </c>
-      <c r="D92" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E92" s="41" t="n">
+      <c r="D93" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" s="41" t="n">
         <v>0.3</v>
       </c>
-      <c r="F92" s="41" t="n">
+      <c r="F93" s="41" t="n">
         <v>-0.6</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="40" t="inlineStr">
-        <is>
-          <t>Emidio Rainer Vilhalba</t>
-        </is>
-      </c>
-      <c r="B93" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C93" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D93" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E93" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F93" s="40" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="94">
@@ -9177,7 +9301,7 @@
       </c>
       <c r="C94" s="40" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D94" s="40" t="n">
@@ -9191,29 +9315,29 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="41" t="inlineStr">
+      <c r="A95" s="40" t="inlineStr">
         <is>
           <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
-      <c r="B95" s="41" t="inlineStr">
+      <c r="B95" s="40" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C95" s="41" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D95" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E95" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F95" s="41" t="n">
-        <v>-1</v>
+      <c r="C95" s="40" t="inlineStr">
+        <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D95" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F95" s="40" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="96">
@@ -9229,43 +9353,43 @@
       </c>
       <c r="C96" s="41" t="inlineStr">
         <is>
+          <t>Dia sem bater a meta diária</t>
+        </is>
+      </c>
+      <c r="D96" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" s="41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F96" s="41" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="41" t="inlineStr">
+        <is>
+          <t>Emidio Rainer Vilhalba</t>
+        </is>
+      </c>
+      <c r="B97" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C97" s="41" t="inlineStr">
+        <is>
           <t>Início tarde após 14h30</t>
         </is>
       </c>
-      <c r="D96" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E96" s="41" t="n">
+      <c r="D97" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" s="41" t="n">
         <v>0.3</v>
       </c>
-      <c r="F96" s="41" t="n">
+      <c r="F97" s="41" t="n">
         <v>-0.6</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="40" t="inlineStr">
-        <is>
-          <t>Evelyn Santana Santos Oliveira</t>
-        </is>
-      </c>
-      <c r="B97" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C97" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D97" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E97" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F97" s="40" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="98">
@@ -9281,7 +9405,7 @@
       </c>
       <c r="C98" s="40" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D98" s="40" t="n">
@@ -9295,29 +9419,29 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="41" t="inlineStr">
+      <c r="A99" s="40" t="inlineStr">
         <is>
           <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
-      <c r="B99" s="41" t="inlineStr">
+      <c r="B99" s="40" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C99" s="41" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D99" s="41" t="n">
-        <v>4</v>
-      </c>
-      <c r="E99" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F99" s="41" t="n">
-        <v>-4</v>
+      <c r="C99" s="40" t="inlineStr">
+        <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D99" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F99" s="40" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="100">
@@ -9333,17 +9457,17 @@
       </c>
       <c r="C100" s="41" t="inlineStr">
         <is>
-          <t>Fim manhã antes de 10h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D100" s="41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E100" s="41" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F100" s="41" t="n">
-        <v>-0.6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="101">
@@ -9359,17 +9483,17 @@
       </c>
       <c r="C101" s="41" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D101" s="41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E101" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F101" s="41" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="102">
@@ -9385,7 +9509,7 @@
       </c>
       <c r="C102" s="41" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D102" s="41" t="n">
@@ -9411,43 +9535,43 @@
       </c>
       <c r="C103" s="41" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D103" s="41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E103" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F103" s="41" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="41" t="inlineStr">
+        <is>
+          <t>Evelyn Santana Santos Oliveira</t>
+        </is>
+      </c>
+      <c r="B104" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C104" s="41" t="inlineStr">
+        <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D104" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="E104" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F104" s="41" t="n">
         <v>-1.8</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="40" t="inlineStr">
-        <is>
-          <t>Fabiana de Figueredo Vieira</t>
-        </is>
-      </c>
-      <c r="B104" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C104" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D104" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E104" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F104" s="40" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="105">
@@ -9463,7 +9587,7 @@
       </c>
       <c r="C105" s="40" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D105" s="40" t="n">
@@ -9489,17 +9613,17 @@
       </c>
       <c r="C106" s="40" t="inlineStr">
         <is>
-          <t>Bônus: pontualidade perfeita no período</t>
+          <t>Bônus: nenhuma visita rápida no período</t>
         </is>
       </c>
       <c r="D106" s="40" t="n">
         <v>1</v>
       </c>
       <c r="E106" s="40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F106" s="40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107">
@@ -9515,69 +9639,69 @@
       </c>
       <c r="C107" s="40" t="inlineStr">
         <is>
-          <t>Dia com meta diária batida</t>
+          <t>Bônus: pontualidade perfeita no período</t>
         </is>
       </c>
       <c r="D107" s="40" t="n">
         <v>1</v>
       </c>
       <c r="E107" s="40" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="F107" s="40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="40" t="inlineStr">
         <is>
+          <t>Fabiana de Figueredo Vieira</t>
+        </is>
+      </c>
+      <c r="B108" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C108" s="40" t="inlineStr">
+        <is>
+          <t>Dia com meta diária batida</t>
+        </is>
+      </c>
+      <c r="D108" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F108" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="40" t="inlineStr">
+        <is>
           <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
-      <c r="B108" s="40" t="inlineStr">
+      <c r="B109" s="40" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C108" s="40" t="inlineStr">
+      <c r="C109" s="40" t="inlineStr">
         <is>
           <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
-      <c r="D108" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E108" s="40" t="n">
+      <c r="D109" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" s="40" t="n">
         <v>5</v>
       </c>
-      <c r="F108" s="40" t="n">
+      <c r="F109" s="40" t="n">
         <v>5</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="41" t="inlineStr">
-        <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
-        </is>
-      </c>
-      <c r="B109" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C109" s="41" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D109" s="41" t="n">
-        <v>4</v>
-      </c>
-      <c r="E109" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F109" s="41" t="n">
-        <v>-4</v>
       </c>
     </row>
     <row r="110">
@@ -9593,17 +9717,17 @@
       </c>
       <c r="C110" s="41" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D110" s="41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E110" s="41" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F110" s="41" t="n">
-        <v>-0.6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="111">
@@ -9619,17 +9743,17 @@
       </c>
       <c r="C111" s="41" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D111" s="41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E111" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F111" s="41" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="112">
@@ -9645,17 +9769,17 @@
       </c>
       <c r="C112" s="41" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D112" s="41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E112" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F112" s="41" t="n">
-        <v>-1.8</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="113">
@@ -9671,43 +9795,43 @@
       </c>
       <c r="C113" s="41" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D113" s="41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E113" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F113" s="41" t="n">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="41" t="inlineStr">
+        <is>
+          <t>Gabriel Alan de Oliveira Martins</t>
+        </is>
+      </c>
+      <c r="B114" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C114" s="41" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D114" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F114" s="41" t="n">
         <v>-0.6</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="40" t="inlineStr">
-        <is>
-          <t>Geancarlos Ferreira Barrios</t>
-        </is>
-      </c>
-      <c r="B114" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C114" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D114" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E114" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F114" s="40" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="115">
@@ -9723,7 +9847,7 @@
       </c>
       <c r="C115" s="40" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D115" s="40" t="n">
@@ -9749,43 +9873,43 @@
       </c>
       <c r="C116" s="40" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D116" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F116" s="40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="40" t="inlineStr">
+        <is>
+          <t>Geancarlos Ferreira Barrios</t>
+        </is>
+      </c>
+      <c r="B117" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C117" s="40" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D116" s="40" t="n">
+      <c r="D117" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="E116" s="40" t="n">
+      <c r="E117" s="40" t="n">
         <v>0.5</v>
       </c>
-      <c r="F116" s="40" t="n">
+      <c r="F117" s="40" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="41" t="inlineStr">
-        <is>
-          <t>Geancarlos Ferreira Barrios</t>
-        </is>
-      </c>
-      <c r="B117" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C117" s="41" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D117" s="41" t="n">
-        <v>2</v>
-      </c>
-      <c r="E117" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F117" s="41" t="n">
-        <v>-2</v>
       </c>
     </row>
     <row r="118">
@@ -9801,17 +9925,17 @@
       </c>
       <c r="C118" s="41" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D118" s="41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E118" s="41" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F118" s="41" t="n">
-        <v>-0.6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="119">
@@ -9827,7 +9951,7 @@
       </c>
       <c r="C119" s="41" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D119" s="41" t="n">
@@ -9853,17 +9977,17 @@
       </c>
       <c r="C120" s="41" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D120" s="41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E120" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F120" s="41" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="121">
@@ -9879,43 +10003,43 @@
       </c>
       <c r="C121" s="41" t="inlineStr">
         <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D121" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E121" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F121" s="41" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="41" t="inlineStr">
+        <is>
+          <t>Geancarlos Ferreira Barrios</t>
+        </is>
+      </c>
+      <c r="B122" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C122" s="41" t="inlineStr">
+        <is>
           <t>Visita fora do expediente/fim de semana</t>
         </is>
       </c>
-      <c r="D121" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E121" s="41" t="n">
+      <c r="D122" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" s="41" t="n">
         <v>0.5</v>
       </c>
-      <c r="F121" s="41" t="n">
+      <c r="F122" s="41" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="40" t="inlineStr">
-        <is>
-          <t>Gilmar Bitencourt Luiz</t>
-        </is>
-      </c>
-      <c r="B122" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C122" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D122" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E122" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F122" s="40" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="123">
@@ -9931,7 +10055,7 @@
       </c>
       <c r="C123" s="40" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D123" s="40" t="n">
@@ -9957,69 +10081,69 @@
       </c>
       <c r="C124" s="40" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D124" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F124" s="40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="40" t="inlineStr">
+        <is>
+          <t>Gilmar Bitencourt Luiz</t>
+        </is>
+      </c>
+      <c r="B125" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C125" s="40" t="inlineStr">
+        <is>
           <t>Bônus: pontualidade perfeita no período</t>
         </is>
       </c>
-      <c r="D124" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E124" s="40" t="n">
+      <c r="D125" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="F124" s="40" t="n">
+      <c r="F125" s="40" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="41" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="41" t="inlineStr">
         <is>
           <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
-      <c r="B125" s="41" t="inlineStr">
+      <c r="B126" s="41" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C125" s="41" t="inlineStr">
+      <c r="C126" s="41" t="inlineStr">
         <is>
           <t>Dia sem bater a meta diária</t>
         </is>
       </c>
-      <c r="D125" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E125" s="41" t="n">
+      <c r="D126" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" s="41" t="n">
         <v>0.5</v>
       </c>
-      <c r="F125" s="41" t="n">
+      <c r="F126" s="41" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="40" t="inlineStr">
-        <is>
-          <t>Gisele Lopes Justiniano</t>
-        </is>
-      </c>
-      <c r="B126" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C126" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D126" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E126" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F126" s="40" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="127">
@@ -10035,7 +10159,7 @@
       </c>
       <c r="C127" s="40" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D127" s="40" t="n">
@@ -10061,43 +10185,43 @@
       </c>
       <c r="C128" s="40" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D128" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F128" s="40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="40" t="inlineStr">
+        <is>
+          <t>Gisele Lopes Justiniano</t>
+        </is>
+      </c>
+      <c r="B129" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C129" s="40" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D128" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E128" s="40" t="n">
+      <c r="D129" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" s="40" t="n">
         <v>0.5</v>
       </c>
-      <c r="F128" s="40" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="41" t="inlineStr">
-        <is>
-          <t>Gisele Lopes Justiniano</t>
-        </is>
-      </c>
-      <c r="B129" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C129" s="41" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D129" s="41" t="n">
-        <v>2</v>
-      </c>
-      <c r="E129" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F129" s="41" t="n">
-        <v>-2</v>
+      <c r="F129" s="40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -10113,17 +10237,17 @@
       </c>
       <c r="C130" s="41" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D130" s="41" t="n">
         <v>2</v>
       </c>
       <c r="E130" s="41" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F130" s="41" t="n">
-        <v>-1.2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="131">
@@ -10139,17 +10263,17 @@
       </c>
       <c r="C131" s="41" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D131" s="41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E131" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F131" s="41" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="132">
@@ -10165,69 +10289,69 @@
       </c>
       <c r="C132" s="41" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D132" s="41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E132" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F132" s="41" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="41" t="inlineStr">
+        <is>
+          <t>Gisele Lopes Justiniano</t>
+        </is>
+      </c>
+      <c r="B133" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C133" s="41" t="inlineStr">
+        <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D133" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E133" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F133" s="41" t="n">
         <v>-1.2</v>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="40" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="40" t="inlineStr">
         <is>
           <t>Gisele Olimpia Torres</t>
         </is>
       </c>
-      <c r="B133" s="40" t="inlineStr">
+      <c r="B134" s="40" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C133" s="40" t="inlineStr">
+      <c r="C134" s="40" t="inlineStr">
         <is>
           <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
-      <c r="D133" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E133" s="40" t="n">
+      <c r="D134" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" s="40" t="n">
         <v>5</v>
       </c>
-      <c r="F133" s="40" t="n">
+      <c r="F134" s="40" t="n">
         <v>5</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="41" t="inlineStr">
-        <is>
-          <t>Gisele Olimpia Torres</t>
-        </is>
-      </c>
-      <c r="B134" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C134" s="41" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D134" s="41" t="n">
-        <v>3</v>
-      </c>
-      <c r="E134" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F134" s="41" t="n">
-        <v>-3</v>
       </c>
     </row>
     <row r="135">
@@ -10243,17 +10367,17 @@
       </c>
       <c r="C135" s="41" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D135" s="41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E135" s="41" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F135" s="41" t="n">
-        <v>-0.6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="136">
@@ -10269,7 +10393,7 @@
       </c>
       <c r="C136" s="41" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D136" s="41" t="n">
@@ -10295,7 +10419,7 @@
       </c>
       <c r="C137" s="41" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D137" s="41" t="n">
@@ -10321,69 +10445,69 @@
       </c>
       <c r="C138" s="41" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D138" s="41" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E138" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F138" s="41" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="41" t="inlineStr">
+        <is>
+          <t>Gisele Olimpia Torres</t>
+        </is>
+      </c>
+      <c r="B139" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C139" s="41" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D139" s="41" t="n">
+        <v>8</v>
+      </c>
+      <c r="E139" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F139" s="41" t="n">
         <v>-4.8</v>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="40" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="40" t="inlineStr">
         <is>
           <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
-      <c r="B139" s="40" t="inlineStr">
+      <c r="B140" s="40" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C139" s="40" t="inlineStr">
+      <c r="C140" s="40" t="inlineStr">
         <is>
           <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
-      <c r="D139" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E139" s="40" t="n">
+      <c r="D140" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" s="40" t="n">
         <v>5</v>
       </c>
-      <c r="F139" s="40" t="n">
+      <c r="F140" s="40" t="n">
         <v>5</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="41" t="inlineStr">
-        <is>
-          <t>Juliana Patricia Goncalves</t>
-        </is>
-      </c>
-      <c r="B140" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C140" s="41" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D140" s="41" t="n">
-        <v>4</v>
-      </c>
-      <c r="E140" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F140" s="41" t="n">
-        <v>-4</v>
       </c>
     </row>
     <row r="141">
@@ -10399,17 +10523,17 @@
       </c>
       <c r="C141" s="41" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D141" s="41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E141" s="41" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F141" s="41" t="n">
-        <v>-1.8</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="142">
@@ -10425,17 +10549,17 @@
       </c>
       <c r="C142" s="41" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D142" s="41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E142" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F142" s="41" t="n">
-        <v>-0.6</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="143">
@@ -10451,17 +10575,17 @@
       </c>
       <c r="C143" s="41" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D143" s="41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E143" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F143" s="41" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="144">
@@ -10477,43 +10601,43 @@
       </c>
       <c r="C144" s="41" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D144" s="41" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E144" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F144" s="41" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="41" t="inlineStr">
+        <is>
+          <t>Juliana Patricia Goncalves</t>
+        </is>
+      </c>
+      <c r="B145" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C145" s="41" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D145" s="41" t="n">
+        <v>11</v>
+      </c>
+      <c r="E145" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F145" s="41" t="n">
         <v>-6.6</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="40" t="inlineStr">
-        <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
-        </is>
-      </c>
-      <c r="B145" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C145" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D145" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E145" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F145" s="40" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="146">
@@ -10529,43 +10653,43 @@
       </c>
       <c r="C146" s="40" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D146" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F146" s="40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="40" t="inlineStr">
+        <is>
+          <t>Kariele Jackeline Rodrigues Silva</t>
+        </is>
+      </c>
+      <c r="B147" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C147" s="40" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D146" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E146" s="40" t="n">
+      <c r="D147" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" s="40" t="n">
         <v>0.5</v>
       </c>
-      <c r="F146" s="40" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="41" t="inlineStr">
-        <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
-        </is>
-      </c>
-      <c r="B147" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C147" s="41" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D147" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E147" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F147" s="41" t="n">
-        <v>-1</v>
+      <c r="F147" s="40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -10581,17 +10705,17 @@
       </c>
       <c r="C148" s="41" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D148" s="41" t="n">
         <v>1</v>
       </c>
       <c r="E148" s="41" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F148" s="41" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="149">
@@ -10607,43 +10731,43 @@
       </c>
       <c r="C149" s="41" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D149" s="41" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E149" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F149" s="41" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="41" t="inlineStr">
+        <is>
+          <t>Kariele Jackeline Rodrigues Silva</t>
+        </is>
+      </c>
+      <c r="B150" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C150" s="41" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D150" s="41" t="n">
+        <v>9</v>
+      </c>
+      <c r="E150" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F150" s="41" t="n">
         <v>-5.4</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="40" t="inlineStr">
-        <is>
-          <t>Kátia Cilene Silveira Machado</t>
-        </is>
-      </c>
-      <c r="B150" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C150" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D150" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E150" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F150" s="40" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="151">
@@ -10659,43 +10783,43 @@
       </c>
       <c r="C151" s="40" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D151" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E151" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F151" s="40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="40" t="inlineStr">
+        <is>
+          <t>Kátia Cilene Silveira Machado</t>
+        </is>
+      </c>
+      <c r="B152" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C152" s="40" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D151" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E151" s="40" t="n">
+      <c r="D152" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E152" s="40" t="n">
         <v>0.5</v>
       </c>
-      <c r="F151" s="40" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="41" t="inlineStr">
-        <is>
-          <t>Kátia Cilene Silveira Machado</t>
-        </is>
-      </c>
-      <c r="B152" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C152" s="41" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D152" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E152" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F152" s="41" t="n">
-        <v>-1</v>
+      <c r="F152" s="40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -10711,17 +10835,17 @@
       </c>
       <c r="C153" s="41" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D153" s="41" t="n">
         <v>1</v>
       </c>
       <c r="E153" s="41" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F153" s="41" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="154">
@@ -10737,17 +10861,17 @@
       </c>
       <c r="C154" s="41" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D154" s="41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E154" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F154" s="41" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="155">
@@ -10763,43 +10887,43 @@
       </c>
       <c r="C155" s="41" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D155" s="41" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E155" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F155" s="41" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="41" t="inlineStr">
+        <is>
+          <t>Kátia Cilene Silveira Machado</t>
+        </is>
+      </c>
+      <c r="B156" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C156" s="41" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D156" s="41" t="n">
+        <v>5</v>
+      </c>
+      <c r="E156" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F156" s="41" t="n">
         <v>-3</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="40" t="inlineStr">
-        <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
-        </is>
-      </c>
-      <c r="B156" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C156" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D156" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E156" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F156" s="40" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="157">
@@ -10815,43 +10939,43 @@
       </c>
       <c r="C157" s="40" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D157" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E157" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F157" s="40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="40" t="inlineStr">
+        <is>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
+        </is>
+      </c>
+      <c r="B158" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C158" s="40" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D157" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E157" s="40" t="n">
+      <c r="D158" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E158" s="40" t="n">
         <v>0.5</v>
       </c>
-      <c r="F157" s="40" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="41" t="inlineStr">
-        <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
-        </is>
-      </c>
-      <c r="B158" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C158" s="41" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D158" s="41" t="n">
-        <v>3</v>
-      </c>
-      <c r="E158" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F158" s="41" t="n">
-        <v>-3</v>
+      <c r="F158" s="40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="159">
@@ -10867,17 +10991,17 @@
       </c>
       <c r="C159" s="41" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D159" s="41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E159" s="41" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F159" s="41" t="n">
-        <v>-0.6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="160">
@@ -10893,7 +11017,7 @@
       </c>
       <c r="C160" s="41" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D160" s="41" t="n">
@@ -10919,7 +11043,7 @@
       </c>
       <c r="C161" s="41" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D161" s="41" t="n">
@@ -10945,43 +11069,43 @@
       </c>
       <c r="C162" s="41" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D162" s="41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E162" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F162" s="41" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="41" t="inlineStr">
+        <is>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
+        </is>
+      </c>
+      <c r="B163" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C163" s="41" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D163" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="E163" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F163" s="41" t="n">
         <v>-1.8</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="40" t="inlineStr">
-        <is>
-          <t>Mateus Falcao de Souza</t>
-        </is>
-      </c>
-      <c r="B163" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C163" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D163" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E163" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F163" s="40" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="164">
@@ -10997,43 +11121,43 @@
       </c>
       <c r="C164" s="40" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D164" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E164" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F164" s="40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="40" t="inlineStr">
+        <is>
+          <t>Mateus Falcao de Souza</t>
+        </is>
+      </c>
+      <c r="B165" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C165" s="40" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D164" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E164" s="40" t="n">
+      <c r="D165" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" s="40" t="n">
         <v>0.5</v>
       </c>
-      <c r="F164" s="40" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="41" t="inlineStr">
-        <is>
-          <t>Mateus Falcao de Souza</t>
-        </is>
-      </c>
-      <c r="B165" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C165" s="41" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D165" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E165" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F165" s="41" t="n">
-        <v>-1</v>
+      <c r="F165" s="40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="166">
@@ -11049,17 +11173,17 @@
       </c>
       <c r="C166" s="41" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D166" s="41" t="n">
         <v>1</v>
       </c>
       <c r="E166" s="41" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F166" s="41" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="167">
@@ -11075,7 +11199,7 @@
       </c>
       <c r="C167" s="41" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D167" s="41" t="n">
@@ -11101,7 +11225,7 @@
       </c>
       <c r="C168" s="41" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D168" s="41" t="n">
@@ -11127,43 +11251,43 @@
       </c>
       <c r="C169" s="41" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D169" s="41" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="E169" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F169" s="41" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="41" t="inlineStr">
+        <is>
+          <t>Mateus Falcao de Souza</t>
+        </is>
+      </c>
+      <c r="B170" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C170" s="41" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D170" s="41" t="n">
+        <v>23</v>
+      </c>
+      <c r="E170" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F170" s="41" t="n">
         <v>-13.8</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="40" t="inlineStr">
-        <is>
-          <t>Miglidiane Maciel Ajala</t>
-        </is>
-      </c>
-      <c r="B170" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C170" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D170" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E170" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F170" s="40" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="171">
@@ -11179,43 +11303,43 @@
       </c>
       <c r="C171" s="40" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D171" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E171" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F171" s="40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="40" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="B172" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C172" s="40" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D171" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E171" s="40" t="n">
+      <c r="D172" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E172" s="40" t="n">
         <v>0.5</v>
       </c>
-      <c r="F171" s="40" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="41" t="inlineStr">
-        <is>
-          <t>Miglidiane Maciel Ajala</t>
-        </is>
-      </c>
-      <c r="B172" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C172" s="41" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D172" s="41" t="n">
-        <v>2</v>
-      </c>
-      <c r="E172" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F172" s="41" t="n">
-        <v>-2</v>
+      <c r="F172" s="40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="173">
@@ -11231,17 +11355,17 @@
       </c>
       <c r="C173" s="41" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D173" s="41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E173" s="41" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F173" s="41" t="n">
-        <v>-0.6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="174">
@@ -11257,7 +11381,7 @@
       </c>
       <c r="C174" s="41" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D174" s="41" t="n">
@@ -11283,43 +11407,43 @@
       </c>
       <c r="C175" s="41" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D175" s="41" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E175" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F175" s="41" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="41" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="B176" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C176" s="41" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D176" s="41" t="n">
+        <v>5</v>
+      </c>
+      <c r="E176" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F176" s="41" t="n">
         <v>-3</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="40" t="inlineStr">
-        <is>
-          <t>Naime Cristina Freitas</t>
-        </is>
-      </c>
-      <c r="B176" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C176" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D176" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E176" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F176" s="40" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="177">
@@ -11335,7 +11459,7 @@
       </c>
       <c r="C177" s="40" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D177" s="40" t="n">
@@ -11361,95 +11485,95 @@
       </c>
       <c r="C178" s="40" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D178" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E178" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F178" s="40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="40" t="inlineStr">
+        <is>
+          <t>Naime Cristina Freitas</t>
+        </is>
+      </c>
+      <c r="B179" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C179" s="40" t="inlineStr">
+        <is>
           <t>Bônus: pontualidade perfeita no período</t>
         </is>
       </c>
-      <c r="D178" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E178" s="40" t="n">
+      <c r="D179" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E179" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="F178" s="40" t="n">
+      <c r="F179" s="40" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="41" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="41" t="inlineStr">
         <is>
           <t>Naime Cristina Freitas</t>
         </is>
       </c>
-      <c r="B179" s="41" t="inlineStr">
+      <c r="B180" s="41" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C179" s="41" t="inlineStr">
+      <c r="C180" s="41" t="inlineStr">
         <is>
           <t>Dia sem bater a meta diária</t>
         </is>
       </c>
-      <c r="D179" s="41" t="n">
+      <c r="D180" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="E179" s="41" t="n">
+      <c r="E180" s="41" t="n">
         <v>0.5</v>
       </c>
-      <c r="F179" s="41" t="n">
+      <c r="F180" s="41" t="n">
         <v>-2</v>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="40" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="40" t="inlineStr">
         <is>
           <t>Rafael Ramos Recalde</t>
         </is>
       </c>
-      <c r="B180" s="40" t="inlineStr">
+      <c r="B181" s="40" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C180" s="40" t="inlineStr">
+      <c r="C181" s="40" t="inlineStr">
         <is>
           <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
-      <c r="D180" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E180" s="40" t="n">
+      <c r="D181" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E181" s="40" t="n">
         <v>5</v>
       </c>
-      <c r="F180" s="40" t="n">
+      <c r="F181" s="40" t="n">
         <v>5</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="41" t="inlineStr">
-        <is>
-          <t>Rafael Ramos Recalde</t>
-        </is>
-      </c>
-      <c r="B181" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C181" s="41" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D181" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E181" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F181" s="41" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="182">
@@ -11465,17 +11589,17 @@
       </c>
       <c r="C182" s="41" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D182" s="41" t="n">
         <v>1</v>
       </c>
       <c r="E182" s="41" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F182" s="41" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="183">
@@ -11491,7 +11615,7 @@
       </c>
       <c r="C183" s="41" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D183" s="41" t="n">
@@ -11517,43 +11641,43 @@
       </c>
       <c r="C184" s="41" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D184" s="41" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E184" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F184" s="41" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="41" t="inlineStr">
+        <is>
+          <t>Rafael Ramos Recalde</t>
+        </is>
+      </c>
+      <c r="B185" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C185" s="41" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D185" s="41" t="n">
+        <v>7</v>
+      </c>
+      <c r="E185" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F185" s="41" t="n">
         <v>-4.2</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="40" t="inlineStr">
-        <is>
-          <t>Ramona dos Santos Oliveira</t>
-        </is>
-      </c>
-      <c r="B185" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C185" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D185" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E185" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F185" s="40" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="186">
@@ -11569,43 +11693,43 @@
       </c>
       <c r="C186" s="40" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D186" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E186" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F186" s="40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="40" t="inlineStr">
+        <is>
+          <t>Ramona dos Santos Oliveira</t>
+        </is>
+      </c>
+      <c r="B187" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C187" s="40" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D186" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E186" s="40" t="n">
+      <c r="D187" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E187" s="40" t="n">
         <v>0.5</v>
       </c>
-      <c r="F186" s="40" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="41" t="inlineStr">
-        <is>
-          <t>Ramona dos Santos Oliveira</t>
-        </is>
-      </c>
-      <c r="B187" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C187" s="41" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D187" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E187" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F187" s="41" t="n">
-        <v>-1</v>
+      <c r="F187" s="40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="188">
@@ -11621,17 +11745,17 @@
       </c>
       <c r="C188" s="41" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D188" s="41" t="n">
         <v>1</v>
       </c>
       <c r="E188" s="41" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F188" s="41" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="189">
@@ -11647,7 +11771,7 @@
       </c>
       <c r="C189" s="41" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D189" s="41" t="n">
@@ -11673,17 +11797,17 @@
       </c>
       <c r="C190" s="41" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D190" s="41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E190" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F190" s="41" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="191">
@@ -11699,43 +11823,43 @@
       </c>
       <c r="C191" s="41" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D191" s="41" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E191" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F191" s="41" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="41" t="inlineStr">
+        <is>
+          <t>Ramona dos Santos Oliveira</t>
+        </is>
+      </c>
+      <c r="B192" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C192" s="41" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D192" s="41" t="n">
+        <v>21</v>
+      </c>
+      <c r="E192" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F192" s="41" t="n">
         <v>-12.6</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="40" t="inlineStr">
-        <is>
-          <t>Rosalina Beniel Vargas</t>
-        </is>
-      </c>
-      <c r="B192" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C192" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D192" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E192" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F192" s="40" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="193">
@@ -11751,7 +11875,7 @@
       </c>
       <c r="C193" s="40" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D193" s="40" t="n">
@@ -11777,17 +11901,17 @@
       </c>
       <c r="C194" s="40" t="inlineStr">
         <is>
-          <t>Bônus: pontualidade perfeita no período</t>
+          <t>Bônus: nenhuma visita rápida no período</t>
         </is>
       </c>
       <c r="D194" s="40" t="n">
         <v>1</v>
       </c>
       <c r="E194" s="40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F194" s="40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="195">
@@ -11803,69 +11927,69 @@
       </c>
       <c r="C195" s="40" t="inlineStr">
         <is>
+          <t>Bônus: pontualidade perfeita no período</t>
+        </is>
+      </c>
+      <c r="D195" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E195" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="F195" s="40" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="40" t="inlineStr">
+        <is>
+          <t>Rosalina Beniel Vargas</t>
+        </is>
+      </c>
+      <c r="B196" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C196" s="40" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D195" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E195" s="40" t="n">
+      <c r="D196" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E196" s="40" t="n">
         <v>0.5</v>
       </c>
-      <c r="F195" s="40" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="41" t="inlineStr">
+      <c r="F196" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="41" t="inlineStr">
         <is>
           <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
-      <c r="B196" s="41" t="inlineStr">
+      <c r="B197" s="41" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C196" s="41" t="inlineStr">
+      <c r="C197" s="41" t="inlineStr">
         <is>
           <t>Dia sem bater a meta diária</t>
         </is>
       </c>
-      <c r="D196" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E196" s="41" t="n">
+      <c r="D197" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E197" s="41" t="n">
         <v>0.5</v>
       </c>
-      <c r="F196" s="41" t="n">
+      <c r="F197" s="41" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="40" t="inlineStr">
-        <is>
-          <t>Rozana Reis da Silva</t>
-        </is>
-      </c>
-      <c r="B197" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C197" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D197" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E197" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F197" s="40" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="198">
@@ -11881,43 +12005,43 @@
       </c>
       <c r="C198" s="40" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D198" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E198" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F198" s="40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="40" t="inlineStr">
+        <is>
+          <t>Rozana Reis da Silva</t>
+        </is>
+      </c>
+      <c r="B199" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C199" s="40" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D198" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E198" s="40" t="n">
+      <c r="D199" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E199" s="40" t="n">
         <v>0.5</v>
       </c>
-      <c r="F198" s="40" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="41" t="inlineStr">
-        <is>
-          <t>Rozana Reis da Silva</t>
-        </is>
-      </c>
-      <c r="B199" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C199" s="41" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D199" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E199" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F199" s="41" t="n">
-        <v>-1</v>
+      <c r="F199" s="40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="200">
@@ -11933,17 +12057,17 @@
       </c>
       <c r="C200" s="41" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D200" s="41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E200" s="41" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F200" s="41" t="n">
-        <v>-1.2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="201">
@@ -11959,17 +12083,17 @@
       </c>
       <c r="C201" s="41" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D201" s="41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E201" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F201" s="41" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="202">
@@ -11985,43 +12109,43 @@
       </c>
       <c r="C202" s="41" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D202" s="41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E202" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F202" s="41" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="41" t="inlineStr">
+        <is>
+          <t>Rozana Reis da Silva</t>
+        </is>
+      </c>
+      <c r="B203" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C203" s="41" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D203" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E203" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F203" s="41" t="n">
         <v>-1.2</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="40" t="inlineStr">
-        <is>
-          <t>Rozentina Matos de Oliveira</t>
-        </is>
-      </c>
-      <c r="B203" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C203" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D203" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E203" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F203" s="40" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="204">
@@ -12037,7 +12161,7 @@
       </c>
       <c r="C204" s="40" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D204" s="40" t="n">
@@ -12063,43 +12187,43 @@
       </c>
       <c r="C205" s="40" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D205" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E205" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F205" s="40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="40" t="inlineStr">
+        <is>
+          <t>Rozentina Matos de Oliveira</t>
+        </is>
+      </c>
+      <c r="B206" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C206" s="40" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D205" s="40" t="n">
+      <c r="D206" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="E205" s="40" t="n">
+      <c r="E206" s="40" t="n">
         <v>0.5</v>
       </c>
-      <c r="F205" s="40" t="n">
+      <c r="F206" s="40" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="41" t="inlineStr">
-        <is>
-          <t>Rozentina Matos de Oliveira</t>
-        </is>
-      </c>
-      <c r="B206" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C206" s="41" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D206" s="41" t="n">
-        <v>2</v>
-      </c>
-      <c r="E206" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F206" s="41" t="n">
-        <v>-2</v>
       </c>
     </row>
     <row r="207">
@@ -12115,17 +12239,17 @@
       </c>
       <c r="C207" s="41" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D207" s="41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E207" s="41" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F207" s="41" t="n">
-        <v>-0.6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="208">
@@ -12141,7 +12265,7 @@
       </c>
       <c r="C208" s="41" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D208" s="41" t="n">
@@ -12167,7 +12291,7 @@
       </c>
       <c r="C209" s="41" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D209" s="41" t="n">
@@ -12181,45 +12305,45 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="40" t="inlineStr">
-        <is>
-          <t>Selba Ramona Afonso</t>
-        </is>
-      </c>
-      <c r="B210" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C210" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D210" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E210" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F210" s="40" t="n">
-        <v>5</v>
+      <c r="A210" s="41" t="inlineStr">
+        <is>
+          <t>Rozentina Matos de Oliveira</t>
+        </is>
+      </c>
+      <c r="B210" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C210" s="41" t="inlineStr">
+        <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D210" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E210" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F210" s="41" t="n">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="40" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="B211" s="40" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C211" s="40" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D211" s="40" t="n">
@@ -12235,38 +12359,38 @@
     <row r="212">
       <c r="A212" s="40" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="B212" s="40" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C212" s="40" t="inlineStr">
         <is>
-          <t>Dia com meta diária batida</t>
+          <t>Bônus: nenhuma visita rápida no período</t>
         </is>
       </c>
       <c r="D212" s="40" t="n">
         <v>1</v>
       </c>
       <c r="E212" s="40" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="F212" s="40" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="41" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="B213" s="41" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C213" s="41" t="inlineStr">
@@ -12287,17 +12411,17 @@
     <row r="214">
       <c r="A214" s="41" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="B214" s="41" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C214" s="41" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D214" s="41" t="n">
@@ -12313,12 +12437,12 @@
     <row r="215">
       <c r="A215" s="40" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="B215" s="40" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C215" s="40" t="inlineStr">
@@ -12339,12 +12463,12 @@
     <row r="216">
       <c r="A216" s="40" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="B216" s="40" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C216" s="40" t="inlineStr">
@@ -12365,12 +12489,12 @@
     <row r="217">
       <c r="A217" s="40" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="B217" s="40" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C217" s="40" t="inlineStr">
@@ -12391,12 +12515,12 @@
     <row r="218">
       <c r="A218" s="41" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="B218" s="41" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C218" s="41" t="inlineStr">
@@ -12405,81 +12529,81 @@
         </is>
       </c>
       <c r="D218" s="41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E218" s="41" t="n">
         <v>0.5</v>
       </c>
       <c r="F218" s="41" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="41" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="B219" s="41" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C219" s="41" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D219" s="41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E219" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F219" s="41" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="41" t="inlineStr">
+      <c r="A220" s="40" t="inlineStr">
         <is>
           <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
-      <c r="B220" s="41" t="inlineStr">
+      <c r="B220" s="40" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C220" s="41" t="inlineStr">
-        <is>
-          <t>Início tarde após 14h30</t>
-        </is>
-      </c>
-      <c r="D220" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E220" s="41" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F220" s="41" t="n">
-        <v>-0.6</v>
+      <c r="C220" s="40" t="inlineStr">
+        <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D220" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E220" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F220" s="40" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="40" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="B221" s="40" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C221" s="40" t="inlineStr">
         <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
+          <t>Bônus: nenhuma visita rápida no período</t>
         </is>
       </c>
       <c r="D221" s="40" t="n">
@@ -12495,64 +12619,64 @@
     <row r="222">
       <c r="A222" s="40" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="B222" s="40" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C222" s="40" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Dia com meta diária batida</t>
         </is>
       </c>
       <c r="D222" s="40" t="n">
         <v>1</v>
       </c>
       <c r="E222" s="40" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="F222" s="40" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="40" t="inlineStr">
-        <is>
-          <t>Suely Aguiar Alves Luiz</t>
-        </is>
-      </c>
-      <c r="B223" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C223" s="40" t="inlineStr">
-        <is>
-          <t>Dia com meta diária batida</t>
-        </is>
-      </c>
-      <c r="D223" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E223" s="40" t="n">
+      <c r="A223" s="41" t="inlineStr">
+        <is>
+          <t>Silvina Regina de Souza Valiente</t>
+        </is>
+      </c>
+      <c r="B223" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C223" s="41" t="inlineStr">
+        <is>
+          <t>Dia sem bater a meta diária</t>
+        </is>
+      </c>
+      <c r="D223" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E223" s="41" t="n">
         <v>0.5</v>
       </c>
-      <c r="F223" s="40" t="n">
-        <v>1</v>
+      <c r="F223" s="41" t="n">
+        <v>-2</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="41" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="B224" s="41" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C224" s="41" t="inlineStr">
@@ -12561,45 +12685,45 @@
         </is>
       </c>
       <c r="D224" s="41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E224" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F224" s="41" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="41" t="inlineStr">
+        <is>
+          <t>Silvina Regina de Souza Valiente</t>
+        </is>
+      </c>
+      <c r="B225" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C225" s="41" t="inlineStr">
+        <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D225" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E225" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F225" s="41" t="n">
         <v>-0.6</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="40" t="inlineStr">
-        <is>
-          <t>Tania Maria Montania</t>
-        </is>
-      </c>
-      <c r="B225" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C225" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D225" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E225" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F225" s="40" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="40" t="inlineStr">
         <is>
-          <t>Tania Maria Montania</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B226" s="40" t="inlineStr">
@@ -12609,7 +12733,7 @@
       </c>
       <c r="C226" s="40" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D226" s="40" t="n">
@@ -12625,7 +12749,7 @@
     <row r="227">
       <c r="A227" s="40" t="inlineStr">
         <is>
-          <t>Tania Maria Montania</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B227" s="40" t="inlineStr">
@@ -12635,158 +12759,158 @@
       </c>
       <c r="C227" s="40" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D227" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E227" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F227" s="40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="40" t="inlineStr">
+        <is>
+          <t>Suely Aguiar Alves Luiz</t>
+        </is>
+      </c>
+      <c r="B228" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C228" s="40" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D227" s="40" t="n">
-        <v>2</v>
-      </c>
-      <c r="E227" s="40" t="n">
+      <c r="D228" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E228" s="40" t="n">
         <v>0.5</v>
       </c>
-      <c r="F227" s="40" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="41" t="inlineStr">
-        <is>
-          <t>Tania Maria Montania</t>
-        </is>
-      </c>
-      <c r="B228" s="41" t="inlineStr">
+      <c r="F228" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="41" t="inlineStr">
+        <is>
+          <t>Suely Aguiar Alves Luiz</t>
+        </is>
+      </c>
+      <c r="B229" s="41" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C228" s="41" t="inlineStr">
+      <c r="C229" s="41" t="inlineStr">
         <is>
           <t>Início manhã após 08h30</t>
         </is>
       </c>
-      <c r="D228" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E228" s="41" t="n">
+      <c r="D229" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E229" s="41" t="n">
         <v>0.3</v>
       </c>
-      <c r="F228" s="41" t="n">
+      <c r="F229" s="41" t="n">
         <v>-0.6</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="40" t="inlineStr">
-        <is>
-          <t>Tânia Raquel Ortiz dos Santos</t>
-        </is>
-      </c>
-      <c r="B229" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C229" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D229" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E229" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F229" s="40" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="40" t="inlineStr">
         <is>
-          <t>Tânia Raquel Ortiz dos Santos</t>
+          <t>Tania Maria Montania</t>
         </is>
       </c>
       <c r="B230" s="40" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C230" s="40" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D230" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E230" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F230" s="40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="40" t="inlineStr">
+        <is>
+          <t>Tania Maria Montania</t>
+        </is>
+      </c>
+      <c r="B231" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C231" s="40" t="inlineStr">
+        <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D231" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E231" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F231" s="40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="40" t="inlineStr">
+        <is>
+          <t>Tania Maria Montania</t>
+        </is>
+      </c>
+      <c r="B232" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C232" s="40" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D230" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E230" s="40" t="n">
+      <c r="D232" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E232" s="40" t="n">
         <v>0.5</v>
       </c>
-      <c r="F230" s="40" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="41" t="inlineStr">
-        <is>
-          <t>Tânia Raquel Ortiz dos Santos</t>
-        </is>
-      </c>
-      <c r="B231" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C231" s="41" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D231" s="41" t="n">
+      <c r="F232" s="40" t="n">
         <v>2</v>
-      </c>
-      <c r="E231" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F231" s="41" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="41" t="inlineStr">
-        <is>
-          <t>Tânia Raquel Ortiz dos Santos</t>
-        </is>
-      </c>
-      <c r="B232" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C232" s="41" t="inlineStr">
-        <is>
-          <t>Fim tarde antes de 16h00</t>
-        </is>
-      </c>
-      <c r="D232" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E232" s="41" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F232" s="41" t="n">
-        <v>-0.6</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="41" t="inlineStr">
         <is>
-          <t>Tânia Raquel Ortiz dos Santos</t>
+          <t>Tania Maria Montania</t>
         </is>
       </c>
       <c r="B233" s="41" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C233" s="41" t="inlineStr">
@@ -12805,113 +12929,113 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="41" t="inlineStr">
+      <c r="A234" s="40" t="inlineStr">
         <is>
           <t>Tânia Raquel Ortiz dos Santos</t>
         </is>
       </c>
-      <c r="B234" s="41" t="inlineStr">
+      <c r="B234" s="40" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C234" s="41" t="inlineStr">
-        <is>
-          <t>Início tarde após 14h30</t>
-        </is>
-      </c>
-      <c r="D234" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E234" s="41" t="n">
+      <c r="C234" s="40" t="inlineStr">
+        <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D234" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E234" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F234" s="40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="40" t="inlineStr">
+        <is>
+          <t>Tânia Raquel Ortiz dos Santos</t>
+        </is>
+      </c>
+      <c r="B235" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C235" s="40" t="inlineStr">
+        <is>
+          <t>Dia com meta diária batida</t>
+        </is>
+      </c>
+      <c r="D235" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E235" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F235" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="41" t="inlineStr">
+        <is>
+          <t>Tânia Raquel Ortiz dos Santos</t>
+        </is>
+      </c>
+      <c r="B236" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C236" s="41" t="inlineStr">
+        <is>
+          <t>Dia sem bater a meta diária</t>
+        </is>
+      </c>
+      <c r="D236" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E236" s="41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F236" s="41" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="41" t="inlineStr">
+        <is>
+          <t>Tânia Raquel Ortiz dos Santos</t>
+        </is>
+      </c>
+      <c r="B237" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C237" s="41" t="inlineStr">
+        <is>
+          <t>Fim tarde antes de 16h00</t>
+        </is>
+      </c>
+      <c r="D237" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E237" s="41" t="n">
         <v>0.3</v>
       </c>
-      <c r="F234" s="41" t="n">
+      <c r="F237" s="41" t="n">
         <v>-0.6</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="41" t="inlineStr">
-        <is>
-          <t>Tânia Raquel Ortiz dos Santos</t>
-        </is>
-      </c>
-      <c r="B235" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C235" s="41" t="inlineStr">
-        <is>
-          <t>Visita rápida</t>
-        </is>
-      </c>
-      <c r="D235" s="41" t="n">
-        <v>17</v>
-      </c>
-      <c r="E235" s="41" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F235" s="41" t="n">
-        <v>-10.2</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="40" t="inlineStr">
-        <is>
-          <t>Wagner Tarlei Gomes</t>
-        </is>
-      </c>
-      <c r="B236" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C236" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D236" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E236" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F236" s="40" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="40" t="inlineStr">
-        <is>
-          <t>Wagner Tarlei Gomes</t>
-        </is>
-      </c>
-      <c r="B237" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C237" s="40" t="inlineStr">
-        <is>
-          <t>Dia com meta diária batida</t>
-        </is>
-      </c>
-      <c r="D237" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E237" s="40" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F237" s="40" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="41" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Tânia Raquel Ortiz dos Santos</t>
         </is>
       </c>
       <c r="B238" s="41" t="inlineStr">
@@ -12921,7 +13045,7 @@
       </c>
       <c r="C238" s="41" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D238" s="41" t="n">
@@ -12937,7 +13061,7 @@
     <row r="239">
       <c r="A239" s="41" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Tânia Raquel Ortiz dos Santos</t>
         </is>
       </c>
       <c r="B239" s="41" t="inlineStr">
@@ -12947,7 +13071,7 @@
       </c>
       <c r="C239" s="41" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D239" s="41" t="n">
@@ -12963,7 +13087,7 @@
     <row r="240">
       <c r="A240" s="41" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Tânia Raquel Ortiz dos Santos</t>
         </is>
       </c>
       <c r="B240" s="41" t="inlineStr">
@@ -12977,24 +13101,24 @@
         </is>
       </c>
       <c r="D240" s="41" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E240" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F240" s="41" t="n">
-        <v>-4.8</v>
+        <v>-10.2</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="40" t="inlineStr">
         <is>
-          <t>Wesley de Souza Leal</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B241" s="40" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C241" s="40" t="inlineStr">
@@ -13015,69 +13139,69 @@
     <row r="242">
       <c r="A242" s="40" t="inlineStr">
         <is>
-          <t>Wesley de Souza Leal</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B242" s="40" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C242" s="40" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Dia com meta diária batida</t>
         </is>
       </c>
       <c r="D242" s="40" t="n">
         <v>1</v>
       </c>
       <c r="E242" s="40" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="F242" s="40" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="41" t="inlineStr">
         <is>
-          <t>Wesley de Souza Leal</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B243" s="41" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C243" s="41" t="inlineStr">
         <is>
-          <t>Dia sem bater a meta diária</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D243" s="41" t="n">
         <v>1</v>
       </c>
       <c r="E243" s="41" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F243" s="41" t="n">
-        <v>-1</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="41" t="inlineStr">
         <is>
-          <t>Wesley de Souza Leal</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B244" s="41" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C244" s="41" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D244" s="41" t="n">
@@ -13091,35 +13215,35 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="40" t="inlineStr">
-        <is>
-          <t>William Anderson Chamorro Tavares</t>
-        </is>
-      </c>
-      <c r="B245" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C245" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D245" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E245" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F245" s="40" t="n">
-        <v>5</v>
+      <c r="A245" s="41" t="inlineStr">
+        <is>
+          <t>Wagner Tarlei Gomes</t>
+        </is>
+      </c>
+      <c r="B245" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C245" s="41" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D245" s="41" t="n">
+        <v>8</v>
+      </c>
+      <c r="E245" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F245" s="41" t="n">
+        <v>-4.8</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="40" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Wesley de Souza Leal</t>
         </is>
       </c>
       <c r="B246" s="40" t="inlineStr">
@@ -13129,7 +13253,7 @@
       </c>
       <c r="C246" s="40" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D246" s="40" t="n">
@@ -13143,35 +13267,35 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="41" t="inlineStr">
-        <is>
-          <t>William Anderson Chamorro Tavares</t>
-        </is>
-      </c>
-      <c r="B247" s="41" t="inlineStr">
+      <c r="A247" s="40" t="inlineStr">
+        <is>
+          <t>Wesley de Souza Leal</t>
+        </is>
+      </c>
+      <c r="B247" s="40" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C247" s="41" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D247" s="41" t="n">
-        <v>2</v>
-      </c>
-      <c r="E247" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F247" s="41" t="n">
-        <v>-2</v>
+      <c r="C247" s="40" t="inlineStr">
+        <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D247" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E247" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F247" s="40" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="41" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Wesley de Souza Leal</t>
         </is>
       </c>
       <c r="B248" s="41" t="inlineStr">
@@ -13181,23 +13305,23 @@
       </c>
       <c r="C248" s="41" t="inlineStr">
         <is>
-          <t>Fim manhã antes de 10h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D248" s="41" t="n">
         <v>1</v>
       </c>
       <c r="E248" s="41" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F248" s="41" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="41" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Wesley de Souza Leal</t>
         </is>
       </c>
       <c r="B249" s="41" t="inlineStr">
@@ -13207,50 +13331,180 @@
       </c>
       <c r="C249" s="41" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D249" s="41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E249" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F249" s="41" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="40" t="inlineStr">
+        <is>
+          <t>William Anderson Chamorro Tavares</t>
+        </is>
+      </c>
+      <c r="B250" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C250" s="40" t="inlineStr">
+        <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D250" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E250" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F250" s="40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="40" t="inlineStr">
+        <is>
+          <t>William Anderson Chamorro Tavares</t>
+        </is>
+      </c>
+      <c r="B251" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C251" s="40" t="inlineStr">
+        <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D251" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E251" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F251" s="40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="41" t="inlineStr">
+        <is>
+          <t>William Anderson Chamorro Tavares</t>
+        </is>
+      </c>
+      <c r="B252" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C252" s="41" t="inlineStr">
+        <is>
+          <t>Dia sem bater a meta diária</t>
+        </is>
+      </c>
+      <c r="D252" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E252" s="41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F252" s="41" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="41" t="inlineStr">
+        <is>
+          <t>William Anderson Chamorro Tavares</t>
+        </is>
+      </c>
+      <c r="B253" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C253" s="41" t="inlineStr">
+        <is>
+          <t>Fim manhã antes de 10h00</t>
+        </is>
+      </c>
+      <c r="D253" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E253" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F253" s="41" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="41" t="inlineStr">
+        <is>
+          <t>William Anderson Chamorro Tavares</t>
+        </is>
+      </c>
+      <c r="B254" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C254" s="41" t="inlineStr">
+        <is>
+          <t>Início manhã após 08h30</t>
+        </is>
+      </c>
+      <c r="D254" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E254" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F254" s="41" t="n">
         <v>-1.2</v>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" s="41" t="inlineStr">
+    <row r="255">
+      <c r="A255" s="41" t="inlineStr">
         <is>
           <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
-      <c r="B250" s="41" t="inlineStr">
+      <c r="B255" s="41" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C250" s="41" t="inlineStr">
+      <c r="C255" s="41" t="inlineStr">
         <is>
           <t>Início tarde após 14h30</t>
         </is>
       </c>
-      <c r="D250" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E250" s="41" t="n">
+      <c r="D255" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E255" s="41" t="n">
         <v>0.3</v>
       </c>
-      <c r="F250" s="41" t="n">
+      <c r="F255" s="41" t="n">
         <v>-0.6</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:E39"/>
+  <autoFilter ref="A2:E40"/>
   <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A43:F43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13262,7 +13516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N57"/>
+  <dimension ref="A1:N58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -15320,7 +15574,7 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -15330,164 +15584,218 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>434 - VILA AUREA</t>
+          <t>438 - JARDIM PLANALTO</t>
         </is>
       </c>
       <c r="D39" s="4" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>6.39</v>
+        <v>6.78</v>
       </c>
       <c r="F39" s="4" t="n">
         <v>6</v>
       </c>
       <c r="G39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="4" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>🟢 NORMAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Silvina Regina de Souza Valiente</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>434 - VILA AUREA</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G40" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H39" s="4" t="inlineStr">
+      <c r="H40" s="4" t="inlineStr">
         <is>
           <t>Q008, Q020, Q026, Q027, Q028</t>
         </is>
       </c>
-      <c r="I39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="4" t="n">
+      <c r="I40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="L39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="4" t="n">
+      <c r="L40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="4" t="n">
         <v>25.81</v>
       </c>
-      <c r="N39" s="4" t="inlineStr">
+      <c r="N40" s="4" t="inlineStr">
         <is>
           <t>🟢 NORMAL</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>LEGENDA — CLASSIFICAÇÃO (baseada em % de Visitas Rápidas)</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>🟢 NORMAL</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>% Rápidas até 10%</t>
         </is>
       </c>
-      <c r="C43" s="10" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="11" t="inlineStr">
+      <c r="C44" s="10" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>🟡 ATENÇÃO</t>
         </is>
       </c>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>% Rápidas entre 11% e 20%</t>
         </is>
       </c>
-      <c r="C44" s="10" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="12" t="inlineStr">
+      <c r="C45" s="10" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
       </c>
-      <c r="B45" s="9" t="inlineStr">
+      <c r="B46" s="9" t="inlineStr">
         <is>
           <t>% Rápidas acima de 20%</t>
         </is>
       </c>
-      <c r="C45" s="10" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="13" t="inlineStr">
+      <c r="C46" s="10" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="inlineStr">
         <is>
           <t>⚠️ SEQUÊNCIA SUSPEITA</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="45" customHeight="1">
-      <c r="A48" s="14" t="inlineStr">
+    <row r="49" ht="45" customHeight="1">
+      <c r="A49" s="14" t="inlineStr">
         <is>
           <t>Duas ou mais visitas consecutivas do mesmo agente registradas no MESMO MINUTO de chegada são marcadas como suspeitas (o e-Visita não registra segundos, então o critério de negócio de 50s de diferença equivale, na prática, a 'mesmo minuto') — sugere lançamento em lote no sistema, não visita real de campo. Colunas: 'Visitas em Sequência Suspeita' (total de visitas envolvidas) e 'Maior Sequência Suspeita' (maior número de visitas seguidas nessa condição). Na aba 'Visitas Suspeitas', a coluna 'Diferença p/ Anterior (s)*' fica em branco quando o alerta da linha veio do par com a visita SEGUINTE (não da anterior).</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="15" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="15" t="inlineStr">
         <is>
           <t>🍽️ VISITAS NO HORÁRIO DE ALMOÇO</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="70" customHeight="1">
-      <c r="A51" s="14" t="inlineStr">
+    <row r="52" ht="70" customHeight="1">
+      <c r="A52" s="14" t="inlineStr">
         <is>
           <t>Coluna 'Visitas no Almoço (11h15-12h45)' conta as visitas com chegada registrada nesse intervalo — o horário oficial de almoço é 11h15 às 12h45, JÁ COM 15 MINUTOS DE TOLERÂNCIA em cada borda (visitas entre 11h-11h15 ou 12h45-13h não são tratadas como violação, só como 'fora do expediente' genérico) — use para checar se o agente está trabalhando no horário de almoço ou se há erro de lançamento. Essas visitas ficam de fora do cálculo de 'Início/Fim Manhã' e 'Início/Fim Tarde', que usam a primeira chegada e a última saída de cada dia (não a média de todos os horários), para refletir melhor o início e o fim reais do expediente.</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="16" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="16" t="inlineStr">
         <is>
           <t>💰 HORAS TRABALHADAS, HORAS ÚTEIS E CUSTO DA HORA ÚTIL</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" s="14" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" s="14" t="inlineStr">
         <is>
           <t>'Horas Trabalhadas' = jornada total do dia (primeira chegada até a última saída), descontando a sobreposição com o horário de almoço — depois tira-se a média entre os dias/semanas trabalhados, 'Horas Úteis' = soma das durações de visita no dia (tempo realmente dentro de imóveis), sem contar deslocamento entre visitas, 'Custo Hora Útil' = salário mensal do agente (R$ 4863,00, equivalente a 3 salários mínimos federais) dividido pelas horas úteis mensais estimadas (Média Horas Úteis/Dia × 22 dias úteis/mês). Quanto menos tempo o agente passa efetivamente em visita por dia, mais caro fica o custo por hora útil.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="17" t="inlineStr">
-        <is>
-          <t>ℹ️ A lista detalhada de visitas duplicadas (com endereço) está na aba 'Visitas Duplicadas' — use-a para localizar e excluir os registros repetidos.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="17" t="inlineStr">
         <is>
+          <t>ℹ️ A lista detalhada de visitas duplicadas (com endereço) está na aba 'Visitas Duplicadas' — use-a para localizar e excluir os registros repetidos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="17" t="inlineStr">
+        <is>
           <t>ℹ️ Visitas com duração NEGATIVA (saída antes da chegada — provável bug do sistema) foram excluídas do cálculo de Média/Mediana e estão detalhadas na aba 'Visitas Negativas', para investigação junto ao suporte do e-Visita.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:N39"/>
+  <autoFilter ref="A2:N40"/>
   <mergeCells count="13">
-    <mergeCell ref="A42:C42"/>
     <mergeCell ref="B44:C44"/>
-    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A49:C49"/>
     <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A58:C58"/>
     <mergeCell ref="B45:C45"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A55:C55"/>
     <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A52:C52"/>
     <mergeCell ref="A51:C51"/>
-    <mergeCell ref="B43:C43"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/historico/semana_318.xlsx
+++ b/data/historico/semana_318.xlsx
@@ -965,16 +965,16 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E3" s="4" t="n">
         <v>3</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>22.33</v>
+        <v>22</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>5.01</v>
+        <v>5.03</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>5</v>
@@ -1013,10 +1013,10 @@
         <v>1</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>23.86</v>
+        <v>24.14</v>
       </c>
       <c r="V3" s="4" t="n">
         <v>3.14</v>
@@ -1025,11 +1025,11 @@
         <v>9.42</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="Y3" s="4" t="inlineStr">
         <is>
-          <t>R$ 118,42</t>
+          <t>R$ 119,84</t>
         </is>
       </c>
       <c r="Z3" s="4" t="inlineStr">
@@ -1676,317 +1676,317 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Raquel Ortiz dos Santos</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>🔴 CRÍTICO</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>41.46</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="S10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="U10" s="5" t="n">
+        <v>19.61</v>
+      </c>
+      <c r="V10" s="5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="W10" s="5" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="X10" s="5" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="Y10" s="5" t="inlineStr">
+        <is>
+          <t>R$ 292,56</t>
+        </is>
+      </c>
+      <c r="Z10" s="5" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AA10" s="5" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AB10" s="5" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC10" s="5" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>🟢 NORMAL</t>
         </is>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D11" s="4" t="n">
         <v>122</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E11" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F11" s="4" t="n">
         <v>24.4</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>5.45</v>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="I10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="4" t="n">
+      <c r="I11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="N10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="4" t="n">
+      <c r="N11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="4" t="n">
         <v>79</v>
       </c>
-      <c r="S10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="4" t="n">
+      <c r="S11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="4" t="n">
         <v>201</v>
       </c>
-      <c r="U10" s="4" t="n">
+      <c r="U11" s="4" t="n">
         <v>39.3</v>
       </c>
-      <c r="V10" s="4" t="n">
+      <c r="V11" s="4" t="n">
         <v>4.8</v>
       </c>
-      <c r="W10" s="4" t="n">
+      <c r="W11" s="4" t="n">
         <v>23.98</v>
       </c>
-      <c r="X10" s="4" t="n">
+      <c r="X11" s="4" t="n">
         <v>2.22</v>
       </c>
-      <c r="Y10" s="4" t="inlineStr">
+      <c r="Y11" s="4" t="inlineStr">
         <is>
           <t>R$ 99,72</t>
         </is>
       </c>
-      <c r="Z10" s="4" t="inlineStr">
+      <c r="Z11" s="4" t="inlineStr">
         <is>
           <t>08:25</t>
         </is>
       </c>
-      <c r="AA10" s="4" t="inlineStr">
+      <c r="AA11" s="4" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="AB10" s="4" t="inlineStr">
+      <c r="AB11" s="4" t="inlineStr">
         <is>
           <t>14:08</t>
         </is>
       </c>
-      <c r="AC10" s="4" t="inlineStr">
+      <c r="AC11" s="4" t="inlineStr">
         <is>
           <t>16:14</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Tânia Raquel Ortiz dos Santos</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Wagner Tarlei Gomes</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>🔴 CRÍTICO</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>13.67</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="J11" s="5" t="n">
-        <v>41.46</v>
-      </c>
-      <c r="K11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="S11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" s="5" t="n">
-        <v>51</v>
-      </c>
-      <c r="U11" s="5" t="n">
-        <v>19.61</v>
-      </c>
-      <c r="V11" s="5" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="W11" s="5" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="X11" s="5" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="Y11" s="5" t="inlineStr">
-        <is>
-          <t>R$ 292,56</t>
-        </is>
-      </c>
-      <c r="Z11" s="5" t="inlineStr">
-        <is>
-          <t>08:56</t>
-        </is>
-      </c>
-      <c r="AA11" s="5" t="inlineStr">
-        <is>
-          <t>10:47</t>
-        </is>
-      </c>
-      <c r="AB11" s="5" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
-      <c r="AC11" s="5" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Wagner Tarlei Gomes</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>🔴 CRÍTICO</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="H12" s="5" t="n">
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>🟡 ATENÇÃO</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="H12" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="I12" s="5" t="n">
+      <c r="I12" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="J12" s="5" t="n">
-        <v>23.53</v>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="5" t="n">
+      <c r="J12" s="6" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="S12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="U12" s="5" t="n">
-        <v>17.07</v>
-      </c>
-      <c r="V12" s="5" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="W12" s="5" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="X12" s="5" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Y12" s="5" t="inlineStr">
-        <is>
-          <t>R$ 89,01</t>
-        </is>
-      </c>
-      <c r="Z12" s="5" t="inlineStr">
+      <c r="S12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="U12" s="6" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="V12" s="6" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="W12" s="6" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="X12" s="6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y12" s="6" t="inlineStr">
+        <is>
+          <t>R$ 130,03</t>
+        </is>
+      </c>
+      <c r="Z12" s="6" t="inlineStr">
         <is>
           <t>08:41</t>
         </is>
       </c>
-      <c r="AA12" s="5" t="inlineStr">
+      <c r="AA12" s="6" t="inlineStr">
         <is>
           <t>10:27</t>
         </is>
       </c>
-      <c r="AB12" s="5" t="inlineStr">
-        <is>
-          <t>13:22</t>
-        </is>
-      </c>
-      <c r="AC12" s="5" t="inlineStr">
-        <is>
-          <t>15:21</t>
+      <c r="AB12" s="6" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC12" s="6" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
     </row>
@@ -4463,25 +4463,25 @@
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>17</v>
+        <v>14.33</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>2.59</v>
+        <v>3.07</v>
       </c>
       <c r="H37" s="5" t="n">
         <v>2</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>61.76</v>
+        <v>51.16</v>
       </c>
       <c r="K37" s="5" t="n">
         <v>0</v>
@@ -4505,22 +4505,22 @@
         <v>0</v>
       </c>
       <c r="R37" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S37" s="5" t="n">
         <v>0</v>
       </c>
       <c r="T37" s="5" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="U37" s="5" t="n">
-        <v>0</v>
+        <v>20.37</v>
       </c>
       <c r="V37" s="5" t="n">
-        <v>2.75</v>
+        <v>2.27</v>
       </c>
       <c r="W37" s="5" t="n">
-        <v>5.5</v>
+        <v>6.82</v>
       </c>
       <c r="X37" s="5" t="n">
         <v>0.73</v>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="AC37" s="5" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:03</t>
         </is>
       </c>
     </row>
@@ -5211,7 +5211,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D3" s="23" t="n">
         <v>20</v>
@@ -5220,10 +5220,10 @@
         <v>1</v>
       </c>
       <c r="F3" s="23" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G3" s="23" t="n">
-        <v>23.86</v>
+        <v>24.14</v>
       </c>
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
@@ -5405,7 +5405,7 @@
     <row r="10">
       <c r="A10" s="23" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Raquel Ortiz dos Santos</t>
         </is>
       </c>
       <c r="B10" s="23" t="inlineStr">
@@ -5414,19 +5414,19 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>122</v>
+        <v>41</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>79</v>
+        <v>10</v>
       </c>
       <c r="E10" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="23" t="n">
-        <v>201</v>
+        <v>51</v>
       </c>
       <c r="G10" s="23" t="n">
-        <v>39.3</v>
+        <v>19.61</v>
       </c>
       <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="n"/>
@@ -5434,7 +5434,7 @@
     <row r="11">
       <c r="A11" s="23" t="inlineStr">
         <is>
-          <t>Tânia Raquel Ortiz dos Santos</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="B11" s="23" t="inlineStr">
@@ -5443,19 +5443,19 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>41</v>
+        <v>122</v>
       </c>
       <c r="D11" s="23" t="n">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="E11" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="23" t="n">
-        <v>51</v>
+        <v>201</v>
       </c>
       <c r="G11" s="23" t="n">
-        <v>19.61</v>
+        <v>39.3</v>
       </c>
       <c r="H11" s="2" t="n"/>
       <c r="I11" s="2" t="n"/>
@@ -5472,7 +5472,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D12" s="23" t="n">
         <v>7</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="23" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G12" s="23" t="n">
-        <v>17.07</v>
+        <v>14.29</v>
       </c>
       <c r="H12" s="2" t="n"/>
       <c r="I12" s="2" t="n"/>
@@ -6197,19 +6197,19 @@
         </is>
       </c>
       <c r="C37" s="23" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D37" s="23" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E37" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F37" s="23" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="G37" s="23" t="n">
-        <v>0</v>
+        <v>20.37</v>
       </c>
       <c r="H37" s="2" t="n"/>
       <c r="I37" s="2" t="n"/>
@@ -6313,19 +6313,19 @@
         </is>
       </c>
       <c r="C41" s="33" t="n">
-        <v>1403</v>
+        <v>1419</v>
       </c>
       <c r="D41" s="33" t="n">
-        <v>728</v>
+        <v>739</v>
       </c>
       <c r="E41" s="33" t="n">
         <v>2</v>
       </c>
       <c r="F41" s="33" t="n">
-        <v>2133</v>
+        <v>2160</v>
       </c>
       <c r="G41" s="33" t="n">
-        <v>34.22</v>
+        <v>34.31</v>
       </c>
       <c r="H41" s="2" t="n"/>
       <c r="I41" s="2" t="n"/>
@@ -6991,7 +6991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F255"/>
+  <dimension ref="A1:F257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -7672,16 +7672,16 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
@@ -7696,7 +7696,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -7705,7 +7705,7 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>99.8</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
@@ -7720,16 +7720,16 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>99.40000000000001</v>
+        <v>99</v>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -7753,7 +7753,7 @@
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>99</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
@@ -7768,16 +7768,16 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D33" s="4" t="n">
-        <v>98.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Tânia Raquel Ortiz dos Santos</t>
+          <t>Raquel Ortiz dos Santos</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -7883,25 +7883,25 @@
       <c r="F37" s="2" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="n">
+      <c r="A38" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>Ramona dos Santos Oliveira</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>🟢 EXCELENTE</t>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Mateus Falcao de Souza</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>🟡 BOM</t>
         </is>
       </c>
       <c r="F38" s="2" t="n"/>
@@ -7912,16 +7912,16 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Mateus Falcao de Souza</t>
+          <t>Ramona dos Santos Oliveira</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>89.40000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
@@ -11749,13 +11749,13 @@
         </is>
       </c>
       <c r="D188" s="41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E188" s="41" t="n">
         <v>0.5</v>
       </c>
       <c r="F188" s="41" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="189">
@@ -11827,13 +11827,13 @@
         </is>
       </c>
       <c r="D191" s="41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E191" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F191" s="41" t="n">
-        <v>-1.2</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="192">
@@ -11853,24 +11853,24 @@
         </is>
       </c>
       <c r="D192" s="41" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E192" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F192" s="41" t="n">
-        <v>-12.6</v>
+        <v>-13.2</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="40" t="inlineStr">
         <is>
-          <t>Rosalina Beniel Vargas</t>
+          <t>Raquel Ortiz dos Santos</t>
         </is>
       </c>
       <c r="B193" s="40" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C193" s="40" t="inlineStr">
@@ -11891,303 +11891,303 @@
     <row r="194">
       <c r="A194" s="40" t="inlineStr">
         <is>
-          <t>Rosalina Beniel Vargas</t>
+          <t>Raquel Ortiz dos Santos</t>
         </is>
       </c>
       <c r="B194" s="40" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C194" s="40" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Dia com meta diária batida</t>
         </is>
       </c>
       <c r="D194" s="40" t="n">
         <v>1</v>
       </c>
       <c r="E194" s="40" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="F194" s="40" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="40" t="inlineStr">
-        <is>
-          <t>Rosalina Beniel Vargas</t>
-        </is>
-      </c>
-      <c r="B195" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C195" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: pontualidade perfeita no período</t>
-        </is>
-      </c>
-      <c r="D195" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E195" s="40" t="n">
-        <v>3</v>
-      </c>
-      <c r="F195" s="40" t="n">
-        <v>3</v>
+      <c r="A195" s="41" t="inlineStr">
+        <is>
+          <t>Raquel Ortiz dos Santos</t>
+        </is>
+      </c>
+      <c r="B195" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C195" s="41" t="inlineStr">
+        <is>
+          <t>Dia sem bater a meta diária</t>
+        </is>
+      </c>
+      <c r="D195" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E195" s="41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F195" s="41" t="n">
+        <v>-2</v>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="40" t="inlineStr">
-        <is>
-          <t>Rosalina Beniel Vargas</t>
-        </is>
-      </c>
-      <c r="B196" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C196" s="40" t="inlineStr">
-        <is>
-          <t>Dia com meta diária batida</t>
-        </is>
-      </c>
-      <c r="D196" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E196" s="40" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F196" s="40" t="n">
-        <v>1</v>
+      <c r="A196" s="41" t="inlineStr">
+        <is>
+          <t>Raquel Ortiz dos Santos</t>
+        </is>
+      </c>
+      <c r="B196" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C196" s="41" t="inlineStr">
+        <is>
+          <t>Fim tarde antes de 16h00</t>
+        </is>
+      </c>
+      <c r="D196" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E196" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F196" s="41" t="n">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="41" t="inlineStr">
         <is>
+          <t>Raquel Ortiz dos Santos</t>
+        </is>
+      </c>
+      <c r="B197" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C197" s="41" t="inlineStr">
+        <is>
+          <t>Início manhã após 08h30</t>
+        </is>
+      </c>
+      <c r="D197" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E197" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F197" s="41" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="41" t="inlineStr">
+        <is>
+          <t>Raquel Ortiz dos Santos</t>
+        </is>
+      </c>
+      <c r="B198" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C198" s="41" t="inlineStr">
+        <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D198" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E198" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F198" s="41" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="41" t="inlineStr">
+        <is>
+          <t>Raquel Ortiz dos Santos</t>
+        </is>
+      </c>
+      <c r="B199" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C199" s="41" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D199" s="41" t="n">
+        <v>17</v>
+      </c>
+      <c r="E199" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F199" s="41" t="n">
+        <v>-10.2</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="40" t="inlineStr">
+        <is>
           <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
-      <c r="B197" s="41" t="inlineStr">
+      <c r="B200" s="40" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C197" s="41" t="inlineStr">
+      <c r="C200" s="40" t="inlineStr">
+        <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D200" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E200" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F200" s="40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="40" t="inlineStr">
+        <is>
+          <t>Rosalina Beniel Vargas</t>
+        </is>
+      </c>
+      <c r="B201" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C201" s="40" t="inlineStr">
+        <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D201" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E201" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F201" s="40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="40" t="inlineStr">
+        <is>
+          <t>Rosalina Beniel Vargas</t>
+        </is>
+      </c>
+      <c r="B202" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C202" s="40" t="inlineStr">
+        <is>
+          <t>Bônus: pontualidade perfeita no período</t>
+        </is>
+      </c>
+      <c r="D202" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E202" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="F202" s="40" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="40" t="inlineStr">
+        <is>
+          <t>Rosalina Beniel Vargas</t>
+        </is>
+      </c>
+      <c r="B203" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C203" s="40" t="inlineStr">
+        <is>
+          <t>Dia com meta diária batida</t>
+        </is>
+      </c>
+      <c r="D203" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E203" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F203" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="41" t="inlineStr">
+        <is>
+          <t>Rosalina Beniel Vargas</t>
+        </is>
+      </c>
+      <c r="B204" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C204" s="41" t="inlineStr">
         <is>
           <t>Dia sem bater a meta diária</t>
         </is>
       </c>
-      <c r="D197" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E197" s="41" t="n">
+      <c r="D204" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E204" s="41" t="n">
         <v>0.5</v>
       </c>
-      <c r="F197" s="41" t="n">
+      <c r="F204" s="41" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="40" t="inlineStr">
-        <is>
-          <t>Rozana Reis da Silva</t>
-        </is>
-      </c>
-      <c r="B198" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C198" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D198" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E198" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F198" s="40" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="40" t="inlineStr">
-        <is>
-          <t>Rozana Reis da Silva</t>
-        </is>
-      </c>
-      <c r="B199" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C199" s="40" t="inlineStr">
-        <is>
-          <t>Dia com meta diária batida</t>
-        </is>
-      </c>
-      <c r="D199" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E199" s="40" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F199" s="40" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="41" t="inlineStr">
-        <is>
-          <t>Rozana Reis da Silva</t>
-        </is>
-      </c>
-      <c r="B200" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C200" s="41" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D200" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E200" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F200" s="41" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="41" t="inlineStr">
-        <is>
-          <t>Rozana Reis da Silva</t>
-        </is>
-      </c>
-      <c r="B201" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C201" s="41" t="inlineStr">
-        <is>
-          <t>Fim tarde antes de 16h00</t>
-        </is>
-      </c>
-      <c r="D201" s="41" t="n">
-        <v>2</v>
-      </c>
-      <c r="E201" s="41" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F201" s="41" t="n">
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="41" t="inlineStr">
-        <is>
-          <t>Rozana Reis da Silva</t>
-        </is>
-      </c>
-      <c r="B202" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C202" s="41" t="inlineStr">
-        <is>
-          <t>Início manhã após 08h30</t>
-        </is>
-      </c>
-      <c r="D202" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E202" s="41" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F202" s="41" t="n">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="41" t="inlineStr">
-        <is>
-          <t>Rozana Reis da Silva</t>
-        </is>
-      </c>
-      <c r="B203" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C203" s="41" t="inlineStr">
-        <is>
-          <t>Visita rápida</t>
-        </is>
-      </c>
-      <c r="D203" s="41" t="n">
-        <v>2</v>
-      </c>
-      <c r="E203" s="41" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F203" s="41" t="n">
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="40" t="inlineStr">
-        <is>
-          <t>Rozentina Matos de Oliveira</t>
-        </is>
-      </c>
-      <c r="B204" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C204" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D204" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E204" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F204" s="40" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="40" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="B205" s="40" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C205" s="40" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D205" s="40" t="n">
@@ -12203,12 +12203,12 @@
     <row r="206">
       <c r="A206" s="40" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="B206" s="40" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C206" s="40" t="inlineStr">
@@ -12217,24 +12217,24 @@
         </is>
       </c>
       <c r="D206" s="40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E206" s="40" t="n">
         <v>0.5</v>
       </c>
       <c r="F206" s="40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="41" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="B207" s="41" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C207" s="41" t="inlineStr">
@@ -12243,24 +12243,24 @@
         </is>
       </c>
       <c r="D207" s="41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E207" s="41" t="n">
         <v>0.5</v>
       </c>
       <c r="F207" s="41" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="41" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="B208" s="41" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C208" s="41" t="inlineStr">
@@ -12269,24 +12269,24 @@
         </is>
       </c>
       <c r="D208" s="41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E208" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F208" s="41" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="41" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="B209" s="41" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C209" s="41" t="inlineStr">
@@ -12307,38 +12307,38 @@
     <row r="210">
       <c r="A210" s="41" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="B210" s="41" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C210" s="41" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Visita rápida</t>
         </is>
       </c>
       <c r="D210" s="41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E210" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F210" s="41" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="40" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="B211" s="40" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C211" s="40" t="inlineStr">
@@ -12359,12 +12359,12 @@
     <row r="212">
       <c r="A212" s="40" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="B212" s="40" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C212" s="40" t="inlineStr">
@@ -12383,383 +12383,383 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="41" t="inlineStr">
-        <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
-        </is>
-      </c>
-      <c r="B213" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C213" s="41" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D213" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E213" s="41" t="n">
+      <c r="A213" s="40" t="inlineStr">
+        <is>
+          <t>Rozentina Matos de Oliveira</t>
+        </is>
+      </c>
+      <c r="B213" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C213" s="40" t="inlineStr">
+        <is>
+          <t>Dia com meta diária batida</t>
+        </is>
+      </c>
+      <c r="D213" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="E213" s="40" t="n">
         <v>0.5</v>
       </c>
-      <c r="F213" s="41" t="n">
-        <v>-1</v>
+      <c r="F213" s="40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="41" t="inlineStr">
         <is>
+          <t>Rozentina Matos de Oliveira</t>
+        </is>
+      </c>
+      <c r="B214" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C214" s="41" t="inlineStr">
+        <is>
+          <t>Dia sem bater a meta diária</t>
+        </is>
+      </c>
+      <c r="D214" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E214" s="41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F214" s="41" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="41" t="inlineStr">
+        <is>
+          <t>Rozentina Matos de Oliveira</t>
+        </is>
+      </c>
+      <c r="B215" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C215" s="41" t="inlineStr">
+        <is>
+          <t>Fim tarde antes de 16h00</t>
+        </is>
+      </c>
+      <c r="D215" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E215" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F215" s="41" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="41" t="inlineStr">
+        <is>
+          <t>Rozentina Matos de Oliveira</t>
+        </is>
+      </c>
+      <c r="B216" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C216" s="41" t="inlineStr">
+        <is>
+          <t>Início manhã após 08h30</t>
+        </is>
+      </c>
+      <c r="D216" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E216" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F216" s="41" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="41" t="inlineStr">
+        <is>
+          <t>Rozentina Matos de Oliveira</t>
+        </is>
+      </c>
+      <c r="B217" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C217" s="41" t="inlineStr">
+        <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D217" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E217" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F217" s="41" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="40" t="inlineStr">
+        <is>
           <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
-      <c r="B214" s="41" t="inlineStr">
+      <c r="B218" s="40" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C214" s="41" t="inlineStr">
+      <c r="C218" s="40" t="inlineStr">
+        <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D218" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E218" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F218" s="40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="40" t="inlineStr">
+        <is>
+          <t>Sara Eliane Talaveira de Oliveira</t>
+        </is>
+      </c>
+      <c r="B219" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C219" s="40" t="inlineStr">
+        <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D219" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E219" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F219" s="40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="41" t="inlineStr">
+        <is>
+          <t>Sara Eliane Talaveira de Oliveira</t>
+        </is>
+      </c>
+      <c r="B220" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C220" s="41" t="inlineStr">
+        <is>
+          <t>Dia sem bater a meta diária</t>
+        </is>
+      </c>
+      <c r="D220" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E220" s="41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F220" s="41" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="41" t="inlineStr">
+        <is>
+          <t>Sara Eliane Talaveira de Oliveira</t>
+        </is>
+      </c>
+      <c r="B221" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C221" s="41" t="inlineStr">
         <is>
           <t>Início manhã após 08h30</t>
         </is>
       </c>
-      <c r="D214" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E214" s="41" t="n">
+      <c r="D221" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E221" s="41" t="n">
         <v>0.3</v>
       </c>
-      <c r="F214" s="41" t="n">
+      <c r="F221" s="41" t="n">
         <v>-0.6</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="40" t="inlineStr">
-        <is>
-          <t>Selba Ramona Afonso</t>
-        </is>
-      </c>
-      <c r="B215" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C215" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D215" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E215" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F215" s="40" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="40" t="inlineStr">
-        <is>
-          <t>Selba Ramona Afonso</t>
-        </is>
-      </c>
-      <c r="B216" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C216" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
-        </is>
-      </c>
-      <c r="D216" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E216" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F216" s="40" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="40" t="inlineStr">
-        <is>
-          <t>Selba Ramona Afonso</t>
-        </is>
-      </c>
-      <c r="B217" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C217" s="40" t="inlineStr">
-        <is>
-          <t>Dia com meta diária batida</t>
-        </is>
-      </c>
-      <c r="D217" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E217" s="40" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F217" s="40" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="41" t="inlineStr">
-        <is>
-          <t>Selba Ramona Afonso</t>
-        </is>
-      </c>
-      <c r="B218" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C218" s="41" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D218" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E218" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F218" s="41" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="41" t="inlineStr">
-        <is>
-          <t>Selba Ramona Afonso</t>
-        </is>
-      </c>
-      <c r="B219" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C219" s="41" t="inlineStr">
-        <is>
-          <t>Fim tarde antes de 16h00</t>
-        </is>
-      </c>
-      <c r="D219" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E219" s="41" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F219" s="41" t="n">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="40" t="inlineStr">
-        <is>
-          <t>Silvina Regina de Souza Valiente</t>
-        </is>
-      </c>
-      <c r="B220" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C220" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D220" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E220" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F220" s="40" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="40" t="inlineStr">
-        <is>
-          <t>Silvina Regina de Souza Valiente</t>
-        </is>
-      </c>
-      <c r="B221" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C221" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
-        </is>
-      </c>
-      <c r="D221" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E221" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F221" s="40" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="40" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="B222" s="40" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C222" s="40" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D222" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E222" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F222" s="40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="40" t="inlineStr">
+        <is>
+          <t>Selba Ramona Afonso</t>
+        </is>
+      </c>
+      <c r="B223" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C223" s="40" t="inlineStr">
+        <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D223" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E223" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F223" s="40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="40" t="inlineStr">
+        <is>
+          <t>Selba Ramona Afonso</t>
+        </is>
+      </c>
+      <c r="B224" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C224" s="40" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D222" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E222" s="40" t="n">
+      <c r="D224" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E224" s="40" t="n">
         <v>0.5</v>
       </c>
-      <c r="F222" s="40" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="41" t="inlineStr">
-        <is>
-          <t>Silvina Regina de Souza Valiente</t>
-        </is>
-      </c>
-      <c r="B223" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C223" s="41" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D223" s="41" t="n">
-        <v>2</v>
-      </c>
-      <c r="E223" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F223" s="41" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="41" t="inlineStr">
-        <is>
-          <t>Silvina Regina de Souza Valiente</t>
-        </is>
-      </c>
-      <c r="B224" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C224" s="41" t="inlineStr">
-        <is>
-          <t>Início manhã após 08h30</t>
-        </is>
-      </c>
-      <c r="D224" s="41" t="n">
-        <v>2</v>
-      </c>
-      <c r="E224" s="41" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F224" s="41" t="n">
-        <v>-1.2</v>
+      <c r="F224" s="40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="41" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="B225" s="41" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C225" s="41" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D225" s="41" t="n">
         <v>1</v>
       </c>
       <c r="E225" s="41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F225" s="41" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="41" t="inlineStr">
+        <is>
+          <t>Selba Ramona Afonso</t>
+        </is>
+      </c>
+      <c r="B226" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C226" s="41" t="inlineStr">
+        <is>
+          <t>Fim tarde antes de 16h00</t>
+        </is>
+      </c>
+      <c r="D226" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E226" s="41" t="n">
         <v>0.3</v>
       </c>
-      <c r="F225" s="41" t="n">
+      <c r="F226" s="41" t="n">
         <v>-0.6</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="40" t="inlineStr">
-        <is>
-          <t>Suely Aguiar Alves Luiz</t>
-        </is>
-      </c>
-      <c r="B226" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C226" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D226" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E226" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F226" s="40" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="40" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="B227" s="40" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C227" s="40" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D227" s="40" t="n">
@@ -12775,173 +12775,173 @@
     <row r="228">
       <c r="A228" s="40" t="inlineStr">
         <is>
+          <t>Silvina Regina de Souza Valiente</t>
+        </is>
+      </c>
+      <c r="B228" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C228" s="40" t="inlineStr">
+        <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D228" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E228" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F228" s="40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="40" t="inlineStr">
+        <is>
+          <t>Silvina Regina de Souza Valiente</t>
+        </is>
+      </c>
+      <c r="B229" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C229" s="40" t="inlineStr">
+        <is>
+          <t>Dia com meta diária batida</t>
+        </is>
+      </c>
+      <c r="D229" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E229" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F229" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="41" t="inlineStr">
+        <is>
+          <t>Silvina Regina de Souza Valiente</t>
+        </is>
+      </c>
+      <c r="B230" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C230" s="41" t="inlineStr">
+        <is>
+          <t>Dia sem bater a meta diária</t>
+        </is>
+      </c>
+      <c r="D230" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E230" s="41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F230" s="41" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="41" t="inlineStr">
+        <is>
+          <t>Silvina Regina de Souza Valiente</t>
+        </is>
+      </c>
+      <c r="B231" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C231" s="41" t="inlineStr">
+        <is>
+          <t>Início manhã após 08h30</t>
+        </is>
+      </c>
+      <c r="D231" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E231" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F231" s="41" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="41" t="inlineStr">
+        <is>
+          <t>Silvina Regina de Souza Valiente</t>
+        </is>
+      </c>
+      <c r="B232" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C232" s="41" t="inlineStr">
+        <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D232" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E232" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F232" s="41" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="40" t="inlineStr">
+        <is>
           <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
-      <c r="B228" s="40" t="inlineStr">
+      <c r="B233" s="40" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C228" s="40" t="inlineStr">
-        <is>
-          <t>Dia com meta diária batida</t>
-        </is>
-      </c>
-      <c r="D228" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E228" s="40" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F228" s="40" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="41" t="inlineStr">
-        <is>
-          <t>Suely Aguiar Alves Luiz</t>
-        </is>
-      </c>
-      <c r="B229" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C229" s="41" t="inlineStr">
-        <is>
-          <t>Início manhã após 08h30</t>
-        </is>
-      </c>
-      <c r="D229" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E229" s="41" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F229" s="41" t="n">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="40" t="inlineStr">
-        <is>
-          <t>Tania Maria Montania</t>
-        </is>
-      </c>
-      <c r="B230" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C230" s="40" t="inlineStr">
+      <c r="C233" s="40" t="inlineStr">
         <is>
           <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
-      <c r="D230" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E230" s="40" t="n">
+      <c r="D233" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E233" s="40" t="n">
         <v>5</v>
       </c>
-      <c r="F230" s="40" t="n">
+      <c r="F233" s="40" t="n">
         <v>5</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="40" t="inlineStr">
-        <is>
-          <t>Tania Maria Montania</t>
-        </is>
-      </c>
-      <c r="B231" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C231" s="40" t="inlineStr">
-        <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
-        </is>
-      </c>
-      <c r="D231" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E231" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="F231" s="40" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="40" t="inlineStr">
-        <is>
-          <t>Tania Maria Montania</t>
-        </is>
-      </c>
-      <c r="B232" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C232" s="40" t="inlineStr">
-        <is>
-          <t>Dia com meta diária batida</t>
-        </is>
-      </c>
-      <c r="D232" s="40" t="n">
-        <v>2</v>
-      </c>
-      <c r="E232" s="40" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F232" s="40" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="41" t="inlineStr">
-        <is>
-          <t>Tania Maria Montania</t>
-        </is>
-      </c>
-      <c r="B233" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C233" s="41" t="inlineStr">
-        <is>
-          <t>Início manhã após 08h30</t>
-        </is>
-      </c>
-      <c r="D233" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E233" s="41" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F233" s="41" t="n">
-        <v>-0.6</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="40" t="inlineStr">
         <is>
-          <t>Tânia Raquel Ortiz dos Santos</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B234" s="40" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C234" s="40" t="inlineStr">
         <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
+          <t>Bônus: nenhuma visita rápida no período</t>
         </is>
       </c>
       <c r="D234" s="40" t="n">
@@ -12957,12 +12957,12 @@
     <row r="235">
       <c r="A235" s="40" t="inlineStr">
         <is>
-          <t>Tânia Raquel Ortiz dos Santos</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B235" s="40" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C235" s="40" t="inlineStr">
@@ -12983,131 +12983,131 @@
     <row r="236">
       <c r="A236" s="41" t="inlineStr">
         <is>
-          <t>Tânia Raquel Ortiz dos Santos</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B236" s="41" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C236" s="41" t="inlineStr">
         <is>
-          <t>Dia sem bater a meta diária</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D236" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E236" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F236" s="41" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="40" t="inlineStr">
+        <is>
+          <t>Tania Maria Montania</t>
+        </is>
+      </c>
+      <c r="B237" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C237" s="40" t="inlineStr">
+        <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D237" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E237" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F237" s="40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="40" t="inlineStr">
+        <is>
+          <t>Tania Maria Montania</t>
+        </is>
+      </c>
+      <c r="B238" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C238" s="40" t="inlineStr">
+        <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D238" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E238" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F238" s="40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="40" t="inlineStr">
+        <is>
+          <t>Tania Maria Montania</t>
+        </is>
+      </c>
+      <c r="B239" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C239" s="40" t="inlineStr">
+        <is>
+          <t>Dia com meta diária batida</t>
+        </is>
+      </c>
+      <c r="D239" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="E236" s="41" t="n">
+      <c r="E239" s="40" t="n">
         <v>0.5</v>
       </c>
-      <c r="F236" s="41" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="41" t="inlineStr">
-        <is>
-          <t>Tânia Raquel Ortiz dos Santos</t>
-        </is>
-      </c>
-      <c r="B237" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C237" s="41" t="inlineStr">
-        <is>
-          <t>Fim tarde antes de 16h00</t>
-        </is>
-      </c>
-      <c r="D237" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E237" s="41" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F237" s="41" t="n">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="41" t="inlineStr">
-        <is>
-          <t>Tânia Raquel Ortiz dos Santos</t>
-        </is>
-      </c>
-      <c r="B238" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C238" s="41" t="inlineStr">
-        <is>
-          <t>Início manhã após 08h30</t>
-        </is>
-      </c>
-      <c r="D238" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E238" s="41" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F238" s="41" t="n">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="41" t="inlineStr">
-        <is>
-          <t>Tânia Raquel Ortiz dos Santos</t>
-        </is>
-      </c>
-      <c r="B239" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C239" s="41" t="inlineStr">
-        <is>
-          <t>Início tarde após 14h30</t>
-        </is>
-      </c>
-      <c r="D239" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E239" s="41" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F239" s="41" t="n">
-        <v>-0.6</v>
+      <c r="F239" s="40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="41" t="inlineStr">
         <is>
-          <t>Tânia Raquel Ortiz dos Santos</t>
+          <t>Tania Maria Montania</t>
         </is>
       </c>
       <c r="B240" s="41" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C240" s="41" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D240" s="41" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E240" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F240" s="41" t="n">
-        <v>-10.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="241">
@@ -13175,17 +13175,17 @@
       </c>
       <c r="C243" s="41" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D243" s="41" t="n">
         <v>1</v>
       </c>
       <c r="E243" s="41" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F243" s="41" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="244">
@@ -13201,7 +13201,7 @@
       </c>
       <c r="C244" s="41" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D244" s="41" t="n">
@@ -13227,225 +13227,225 @@
       </c>
       <c r="C245" s="41" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D245" s="41" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E245" s="41" t="n">
         <v>0.3</v>
       </c>
       <c r="F245" s="41" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="41" t="inlineStr">
+        <is>
+          <t>Wagner Tarlei Gomes</t>
+        </is>
+      </c>
+      <c r="B246" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C246" s="41" t="inlineStr">
+        <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D246" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E246" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F246" s="41" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="41" t="inlineStr">
+        <is>
+          <t>Wagner Tarlei Gomes</t>
+        </is>
+      </c>
+      <c r="B247" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C247" s="41" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D247" s="41" t="n">
+        <v>8</v>
+      </c>
+      <c r="E247" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F247" s="41" t="n">
         <v>-4.8</v>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="40" t="inlineStr">
+    <row r="248">
+      <c r="A248" s="40" t="inlineStr">
         <is>
           <t>Wesley de Souza Leal</t>
         </is>
       </c>
-      <c r="B246" s="40" t="inlineStr">
+      <c r="B248" s="40" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C246" s="40" t="inlineStr">
+      <c r="C248" s="40" t="inlineStr">
         <is>
           <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
-      <c r="D246" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E246" s="40" t="n">
+      <c r="D248" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E248" s="40" t="n">
         <v>5</v>
       </c>
-      <c r="F246" s="40" t="n">
+      <c r="F248" s="40" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" s="40" t="inlineStr">
+    <row r="249">
+      <c r="A249" s="40" t="inlineStr">
         <is>
           <t>Wesley de Souza Leal</t>
         </is>
       </c>
-      <c r="B247" s="40" t="inlineStr">
+      <c r="B249" s="40" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C247" s="40" t="inlineStr">
+      <c r="C249" s="40" t="inlineStr">
         <is>
           <t>Bônus: nenhuma visita rápida no período</t>
         </is>
       </c>
-      <c r="D247" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E247" s="40" t="n">
+      <c r="D249" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E249" s="40" t="n">
         <v>5</v>
       </c>
-      <c r="F247" s="40" t="n">
+      <c r="F249" s="40" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" s="41" t="inlineStr">
+    <row r="250">
+      <c r="A250" s="41" t="inlineStr">
         <is>
           <t>Wesley de Souza Leal</t>
         </is>
       </c>
-      <c r="B248" s="41" t="inlineStr">
+      <c r="B250" s="41" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C248" s="41" t="inlineStr">
+      <c r="C250" s="41" t="inlineStr">
         <is>
           <t>Dia sem bater a meta diária</t>
         </is>
       </c>
-      <c r="D248" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E248" s="41" t="n">
+      <c r="D250" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E250" s="41" t="n">
         <v>0.5</v>
       </c>
-      <c r="F248" s="41" t="n">
+      <c r="F250" s="41" t="n">
         <v>-1</v>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" s="41" t="inlineStr">
+    <row r="251">
+      <c r="A251" s="41" t="inlineStr">
         <is>
           <t>Wesley de Souza Leal</t>
         </is>
       </c>
-      <c r="B249" s="41" t="inlineStr">
+      <c r="B251" s="41" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C249" s="41" t="inlineStr">
+      <c r="C251" s="41" t="inlineStr">
         <is>
           <t>Início tarde após 14h30</t>
         </is>
       </c>
-      <c r="D249" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E249" s="41" t="n">
+      <c r="D251" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E251" s="41" t="n">
         <v>0.3</v>
       </c>
-      <c r="F249" s="41" t="n">
+      <c r="F251" s="41" t="n">
         <v>-0.6</v>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" s="40" t="inlineStr">
+    <row r="252">
+      <c r="A252" s="40" t="inlineStr">
         <is>
           <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
-      <c r="B250" s="40" t="inlineStr">
+      <c r="B252" s="40" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C250" s="40" t="inlineStr">
+      <c r="C252" s="40" t="inlineStr">
         <is>
           <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
-      <c r="D250" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E250" s="40" t="n">
+      <c r="D252" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E252" s="40" t="n">
         <v>5</v>
       </c>
-      <c r="F250" s="40" t="n">
+      <c r="F252" s="40" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" s="40" t="inlineStr">
+    <row r="253">
+      <c r="A253" s="40" t="inlineStr">
         <is>
           <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
-      <c r="B251" s="40" t="inlineStr">
+      <c r="B253" s="40" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C251" s="40" t="inlineStr">
+      <c r="C253" s="40" t="inlineStr">
         <is>
           <t>Bônus: nenhuma visita rápida no período</t>
         </is>
       </c>
-      <c r="D251" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E251" s="40" t="n">
+      <c r="D253" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E253" s="40" t="n">
         <v>5</v>
       </c>
-      <c r="F251" s="40" t="n">
+      <c r="F253" s="40" t="n">
         <v>5</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="41" t="inlineStr">
-        <is>
-          <t>William Anderson Chamorro Tavares</t>
-        </is>
-      </c>
-      <c r="B252" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C252" s="41" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D252" s="41" t="n">
-        <v>2</v>
-      </c>
-      <c r="E252" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F252" s="41" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="41" t="inlineStr">
-        <is>
-          <t>William Anderson Chamorro Tavares</t>
-        </is>
-      </c>
-      <c r="B253" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C253" s="41" t="inlineStr">
-        <is>
-          <t>Fim manhã antes de 10h00</t>
-        </is>
-      </c>
-      <c r="D253" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E253" s="41" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F253" s="41" t="n">
-        <v>-0.6</v>
       </c>
     </row>
     <row r="254">
@@ -13461,17 +13461,17 @@
       </c>
       <c r="C254" s="41" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D254" s="41" t="n">
         <v>2</v>
       </c>
       <c r="E254" s="41" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F254" s="41" t="n">
-        <v>-1.2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="255">
@@ -13487,7 +13487,7 @@
       </c>
       <c r="C255" s="41" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D255" s="41" t="n">
@@ -13497,6 +13497,58 @@
         <v>0.3</v>
       </c>
       <c r="F255" s="41" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="41" t="inlineStr">
+        <is>
+          <t>William Anderson Chamorro Tavares</t>
+        </is>
+      </c>
+      <c r="B256" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C256" s="41" t="inlineStr">
+        <is>
+          <t>Início manhã após 08h30</t>
+        </is>
+      </c>
+      <c r="D256" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E256" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F256" s="41" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="41" t="inlineStr">
+        <is>
+          <t>William Anderson Chamorro Tavares</t>
+        </is>
+      </c>
+      <c r="B257" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C257" s="41" t="inlineStr">
+        <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D257" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E257" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F257" s="41" t="n">
         <v>-0.6</v>
       </c>
     </row>
@@ -13644,10 +13696,10 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>5.01</v>
+        <v>5.03</v>
       </c>
       <c r="F3" s="4" t="n">
         <v>5</v>
@@ -13673,7 +13725,7 @@
         <v>1</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>23.86</v>
+        <v>24.14</v>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
@@ -14006,164 +14058,164 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Raquel Ortiz dos Santos</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>406 - JARDIM PRIMAVERA</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Q001, Q003, Q005, Q011, Q034, Q035, Q037, Q039, Q040, Q041</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>41.46</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>19.61</v>
+      </c>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>🔴 CRÍTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>408 - PARQUE DE EXPOSIÇÕES</t>
         </is>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D11" s="4" t="n">
         <v>122</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E11" s="4" t="n">
         <v>5.45</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F11" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>Q001, Q003, Q005, Q006, Q010, Q017, Q019, Q021, Q022, Q023, Q024, Q027, Q028, Q029, Q030, Q031, Q032</t>
         </is>
       </c>
-      <c r="I10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="4" t="n">
+      <c r="I11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="4" t="n">
         <v>79</v>
       </c>
-      <c r="L10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="4" t="n">
+      <c r="L11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="4" t="n">
         <v>39.3</v>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>🟢 NORMAL</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Tânia Raquel Ortiz dos Santos</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Wagner Tarlei Gomes</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>406 - JARDIM PRIMAVERA</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>Q001, Q003, Q005, Q011, Q034, Q035, Q037, Q039, Q040, Q041</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="J11" s="5" t="n">
-        <v>41.46</v>
-      </c>
-      <c r="K11" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="5" t="n">
-        <v>19.61</v>
-      </c>
-      <c r="N11" s="5" t="inlineStr">
-        <is>
-          <t>🔴 CRÍTICO</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Wagner Tarlei Gomes</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>400 - JULIA CARDINAL</t>
         </is>
       </c>
-      <c r="D12" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="F12" s="5" t="n">
+      <c r="D12" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="F12" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="G12" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>Q004, Q025, Q030</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="n">
+      <c r="G12" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Q004, Q005, Q025, Q030</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="J12" s="5" t="n">
-        <v>23.53</v>
-      </c>
-      <c r="K12" s="5" t="n">
+      <c r="J12" s="6" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="K12" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="L12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v>17.07</v>
-      </c>
-      <c r="N12" s="5" t="inlineStr">
-        <is>
-          <t>🔴 CRÍTICO</t>
+      <c r="L12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="6" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="N12" s="6" t="inlineStr">
+        <is>
+          <t>🟡 ATENÇÃO</t>
         </is>
       </c>
     </row>
@@ -15480,36 +15532,36 @@
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>2.59</v>
+        <v>3.07</v>
       </c>
       <c r="F37" s="5" t="n">
         <v>2</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Q004, Q018, Q019, Q020</t>
+          <t>Q004, Q011, Q014, Q018, Q019, Q020</t>
         </is>
       </c>
       <c r="I37" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>61.76</v>
+        <v>51.16</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L37" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>0</v>
+        <v>20.37</v>
       </c>
       <c r="N37" s="5" t="inlineStr">
         <is>
@@ -16680,47 +16732,47 @@
     <row r="8">
       <c r="A8" s="23" t="inlineStr">
         <is>
-          <t>Gisele Olimpia Torres</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="B8" s="23" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>16759717</t>
+          <t>16758244</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
         <is>
-          <t>421 - JARDIM IPANEMA</t>
+          <t>408 - PARQUE DE EXPOSIÇÕES</t>
         </is>
       </c>
       <c r="E8" s="23" t="inlineStr">
         <is>
-          <t>Q035</t>
+          <t>Q027</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
         <is>
-          <t>Rua BALTAZAR SALDANHA</t>
+          <t>Avenida PROCURADOR DR. WILSON DIAS DE PINHO</t>
         </is>
       </c>
       <c r="G8" s="23" t="inlineStr">
         <is>
-          <t>779 - OU</t>
+          <t>175 - 1 - C</t>
         </is>
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
-          <t>05/08/2026 09:03</t>
+          <t>05/08/2026 07:41</t>
         </is>
       </c>
       <c r="I8" s="23" t="inlineStr">
         <is>
-          <t>05/08/2026 09:22</t>
+          <t>05/08/2026 08:00</t>
         </is>
       </c>
       <c r="J8" s="23" t="n">
@@ -16730,47 +16782,47 @@
     <row r="9">
       <c r="A9" s="23" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Gisele Olimpia Torres</t>
         </is>
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
         <is>
-          <t>16758244</t>
+          <t>16759717</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
         <is>
-          <t>408 - PARQUE DE EXPOSIÇÕES</t>
+          <t>421 - JARDIM IPANEMA</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q035</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t>Avenida PROCURADOR DR. WILSON DIAS DE PINHO</t>
+          <t>Rua BALTAZAR SALDANHA</t>
         </is>
       </c>
       <c r="G9" s="23" t="inlineStr">
         <is>
-          <t>175 - 1 - C</t>
+          <t>779 - OU</t>
         </is>
       </c>
       <c r="H9" s="23" t="inlineStr">
         <is>
-          <t>05/08/2026 07:41</t>
+          <t>05/08/2026 09:03</t>
         </is>
       </c>
       <c r="I9" s="23" t="inlineStr">
         <is>
-          <t>05/08/2026 08:00</t>
+          <t>05/08/2026 09:22</t>
         </is>
       </c>
       <c r="J9" s="23" t="n">
@@ -16880,47 +16932,47 @@
     <row r="12">
       <c r="A12" s="23" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>16757326</t>
+          <t>16739131</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
         <is>
-          <t>434 - VILA AUREA</t>
+          <t>405 - ALTOS DA GLÓRIA</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q034</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
         <is>
-          <t>Rua RECIFE</t>
+          <t>Rua BARRA BONITA</t>
         </is>
       </c>
       <c r="G12" s="23" t="inlineStr">
         <is>
-          <t>168 - R</t>
+          <t>50 - R</t>
         </is>
       </c>
       <c r="H12" s="23" t="inlineStr">
         <is>
-          <t>05/08/2026 14:36</t>
+          <t>04/08/2026 15:37</t>
         </is>
       </c>
       <c r="I12" s="23" t="inlineStr">
         <is>
-          <t>05/08/2026 14:53</t>
+          <t>04/08/2026 15:54</t>
         </is>
       </c>
       <c r="J12" s="23" t="n">
@@ -16930,47 +16982,47 @@
     <row r="13">
       <c r="A13" s="23" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
-          <t>16739131</t>
+          <t>16760781</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
         <is>
-          <t>405 - ALTOS DA GLÓRIA</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
         <is>
-          <t>Q034</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t>Rua BARRA BONITA</t>
+          <t>Rua JOAQUIM PEREIRA TEIXEIRA</t>
         </is>
       </c>
       <c r="G13" s="23" t="inlineStr">
         <is>
-          <t>50 - R</t>
+          <t>355 - 1 - R</t>
         </is>
       </c>
       <c r="H13" s="23" t="inlineStr">
         <is>
-          <t>04/08/2026 15:37</t>
+          <t>05/08/2026 13:52</t>
         </is>
       </c>
       <c r="I13" s="23" t="inlineStr">
         <is>
-          <t>04/08/2026 15:54</t>
+          <t>05/08/2026 14:09</t>
         </is>
       </c>
       <c r="J13" s="23" t="n">
@@ -16980,47 +17032,47 @@
     <row r="14">
       <c r="A14" s="23" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>16760781</t>
+          <t>16757326</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>434 - VILA AUREA</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q027</t>
         </is>
       </c>
       <c r="F14" s="23" t="inlineStr">
         <is>
-          <t>Rua JOAQUIM PEREIRA TEIXEIRA</t>
+          <t>Rua RECIFE</t>
         </is>
       </c>
       <c r="G14" s="23" t="inlineStr">
         <is>
-          <t>355 - 1 - R</t>
+          <t>168 - R</t>
         </is>
       </c>
       <c r="H14" s="23" t="inlineStr">
         <is>
-          <t>05/08/2026 13:52</t>
+          <t>05/08/2026 14:36</t>
         </is>
       </c>
       <c r="I14" s="23" t="inlineStr">
         <is>
-          <t>05/08/2026 14:09</t>
+          <t>05/08/2026 14:53</t>
         </is>
       </c>
       <c r="J14" s="23" t="n">

--- a/data/historico/semana_318.xlsx
+++ b/data/historico/semana_318.xlsx
@@ -30,7 +30,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Visitas Acima de 15min'!$A$2:$J$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$F$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$E$40</definedName>
@@ -16842,7 +16842,7 @@
       </c>
       <c r="C7" s="26" t="inlineStr">
         <is>
-          <t>16762591</t>
+          <t>16783019</t>
         </is>
       </c>
       <c r="D7" s="25" t="inlineStr">
@@ -16852,27 +16852,27 @@
       </c>
       <c r="E7" s="25" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q029</t>
         </is>
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>Rua ROBERTO BUENO DA SILVA</t>
+          <t>Rua MONTEVIDEO</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>486 - OU</t>
+          <t>301 - R</t>
         </is>
       </c>
       <c r="H7" s="25" t="inlineStr">
         <is>
-          <t>05/08/2026 08:45</t>
+          <t>06/08/2026 16:07</t>
         </is>
       </c>
       <c r="I7" s="25" t="inlineStr">
         <is>
-          <t>05/08/2026 09:05</t>
+          <t>06/08/2026 16:27</t>
         </is>
       </c>
       <c r="J7" s="25" t="n">
@@ -16892,7 +16892,7 @@
       </c>
       <c r="C8" s="26" t="inlineStr">
         <is>
-          <t>16783019</t>
+          <t>16762591</t>
         </is>
       </c>
       <c r="D8" s="25" t="inlineStr">
@@ -16902,27 +16902,27 @@
       </c>
       <c r="E8" s="25" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q027</t>
         </is>
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>Rua MONTEVIDEO</t>
+          <t>Rua ROBERTO BUENO DA SILVA</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>301 - R</t>
+          <t>486 - OU</t>
         </is>
       </c>
       <c r="H8" s="25" t="inlineStr">
         <is>
-          <t>06/08/2026 16:07</t>
+          <t>05/08/2026 08:45</t>
         </is>
       </c>
       <c r="I8" s="25" t="inlineStr">
         <is>
-          <t>06/08/2026 16:27</t>
+          <t>05/08/2026 09:05</t>
         </is>
       </c>
       <c r="J8" s="25" t="n">
@@ -17892,15 +17892,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -17914,43 +17915,49 @@
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="33" t="inlineStr">
         <is>
+          <t>ID Agente</t>
+        </is>
+      </c>
+      <c r="B2" s="33" t="inlineStr">
+        <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="B2" s="33" t="inlineStr">
+      <c r="C2" s="33" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="C2" s="33" t="inlineStr">
+      <c r="D2" s="33" t="inlineStr">
         <is>
           <t>Dia</t>
         </is>
       </c>
-      <c r="D2" s="33" t="inlineStr">
+      <c r="E2" s="33" t="inlineStr">
         <is>
           <t>Dia da Semana</t>
         </is>
       </c>
-      <c r="E2" s="33" t="inlineStr">
+      <c r="F2" s="33" t="inlineStr">
         <is>
           <t>Turno</t>
         </is>
       </c>
-      <c r="F2" s="33" t="inlineStr">
+      <c r="G2" s="33" t="inlineStr">
         <is>
           <t>Observação</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:F2"/>
+  <autoFilter ref="A2:G2"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/historico/semana_318.xlsx
+++ b/data/historico/semana_318.xlsx
@@ -22,8 +22,8 @@
     <sheet name="Ranking" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumo Geral'!$A$2:$AC$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Por Área'!$A$2:$N$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumo Geral'!$A$2:$AC$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Por Área'!$A$2:$N$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Visitas Duplicadas'!$A$2:$J$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Visitas Suspeitas'!$A$2:$K$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Visitas Negativas'!$A$2:$K$3</definedName>
@@ -33,7 +33,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$E$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$E$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -746,7 +746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC58"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -3695,16 +3695,16 @@
         <v>0</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="S29" s="4" t="n">
         <v>0</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>62.5</v>
+        <v>62.18</v>
       </c>
       <c r="V29" s="4" t="n">
         <v>4.79</v>
@@ -4872,123 +4872,220 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="7" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Walquiria Araujo Flores</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>🔴 CRÍTICO</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>21.05</v>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="S41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="U41" s="5" t="n">
+        <v>17.39</v>
+      </c>
+      <c r="V41" s="5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W41" s="5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X41" s="5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y41" s="5" t="inlineStr">
+        <is>
+          <t>R$ 195,04</t>
+        </is>
+      </c>
+      <c r="Z41" s="5" t="n"/>
+      <c r="AA41" s="5" t="n"/>
+      <c r="AB41" s="5" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC41" s="5" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>LEGENDA — CLASSIFICAÇÃO (baseada em % de Visitas Rápidas)</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>🟢 NORMAL</t>
         </is>
       </c>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>% Rápidas até 10%</t>
         </is>
       </c>
-      <c r="C44" s="10" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+      <c r="C45" s="10" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>🟡 ATENÇÃO</t>
         </is>
       </c>
-      <c r="B45" s="9" t="inlineStr">
+      <c r="B46" s="9" t="inlineStr">
         <is>
           <t>% Rápidas entre 11% e 20%</t>
         </is>
       </c>
-      <c r="C45" s="10" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="12" t="inlineStr">
+      <c r="C46" s="10" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
       </c>
-      <c r="B46" s="9" t="inlineStr">
+      <c r="B47" s="9" t="inlineStr">
         <is>
           <t>% Rápidas acima de 20%</t>
         </is>
       </c>
-      <c r="C46" s="10" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="13" t="inlineStr">
+      <c r="C47" s="10" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="13" t="inlineStr">
         <is>
           <t>⚠️ SEQUÊNCIA SUSPEITA</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="45" customHeight="1">
-      <c r="A49" s="14" t="inlineStr">
+    <row r="50" ht="45" customHeight="1">
+      <c r="A50" s="14" t="inlineStr">
         <is>
           <t>Duas ou mais visitas consecutivas do mesmo agente registradas no MESMO MINUTO de chegada são marcadas como suspeitas (o e-Visita não registra segundos, então o critério de negócio de 50s de diferença equivale, na prática, a 'mesmo minuto') — sugere lançamento em lote no sistema, não visita real de campo. Colunas: 'Visitas em Sequência Suspeita' (total de visitas envolvidas) e 'Maior Sequência Suspeita' (maior número de visitas seguidas nessa condição). Na aba 'Visitas Suspeitas', a coluna 'Diferença p/ Anterior (s)*' fica em branco quando o alerta da linha veio do par com a visita SEGUINTE (não da anterior).</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="15" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="15" t="inlineStr">
         <is>
           <t>🍽️ VISITAS NO HORÁRIO DE ALMOÇO</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="70" customHeight="1">
-      <c r="A52" s="14" t="inlineStr">
+    <row r="53" ht="70" customHeight="1">
+      <c r="A53" s="14" t="inlineStr">
         <is>
           <t>Coluna 'Visitas no Almoço (11h15-12h45)' conta as visitas com chegada registrada nesse intervalo — o horário oficial de almoço é 11h15 às 12h45, JÁ COM 15 MINUTOS DE TOLERÂNCIA em cada borda (visitas entre 11h-11h15 ou 12h45-13h não são tratadas como violação, só como 'fora do expediente' genérico) — use para checar se o agente está trabalhando no horário de almoço ou se há erro de lançamento. Essas visitas ficam de fora do cálculo de 'Início/Fim Manhã' e 'Início/Fim Tarde', que usam a primeira chegada e a última saída de cada dia (não a média de todos os horários), para refletir melhor o início e o fim reais do expediente.</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="16" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="16" t="inlineStr">
         <is>
           <t>💰 HORAS TRABALHADAS, HORAS ÚTEIS E CUSTO DA HORA ÚTIL</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" s="14" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" s="14" t="inlineStr">
         <is>
           <t>'Horas Trabalhadas' = jornada total do dia (primeira chegada até a última saída), descontando a sobreposição com o horário de almoço — depois tira-se a média entre os dias/semanas trabalhados, 'Horas Úteis' = soma das durações de visita no dia (tempo realmente dentro de imóveis), sem contar deslocamento entre visitas, 'Custo Hora Útil' = salário mensal do agente (R$ 4863,00, equivalente a 3 salários mínimos federais) dividido pelas horas úteis mensais estimadas (Média Horas Úteis/Dia × 22 dias úteis/mês). Quanto menos tempo o agente passa efetivamente em visita por dia, mais caro fica o custo por hora útil.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="17" t="inlineStr">
-        <is>
-          <t>ℹ️ A lista detalhada de visitas duplicadas (com endereço) está na aba 'Visitas Duplicadas' — use-a para localizar e excluir os registros repetidos.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="17" t="inlineStr">
         <is>
+          <t>ℹ️ A lista detalhada de visitas duplicadas (com endereço) está na aba 'Visitas Duplicadas' — use-a para localizar e excluir os registros repetidos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="17" t="inlineStr">
+        <is>
           <t>ℹ️ Visitas com duração NEGATIVA (saída antes da chegada — provável bug do sistema) foram excluídas do cálculo de Média/Mediana e estão detalhadas na aba 'Visitas Negativas', para investigação junto ao suporte do e-Visita.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AC40"/>
+  <autoFilter ref="A2:AC41"/>
   <mergeCells count="13">
-    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B47:C47"/>
     <mergeCell ref="A1:AC1"/>
+    <mergeCell ref="A44:C44"/>
     <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A57:C57"/>
     <mergeCell ref="A58:C58"/>
     <mergeCell ref="B45:C45"/>
     <mergeCell ref="B46:C46"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A53:C53"/>
     <mergeCell ref="A55:C55"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A59:C59"/>
     <mergeCell ref="A52:C52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5145,7 +5242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -5982,16 +6079,16 @@
         <v>45</v>
       </c>
       <c r="D29" s="25" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E29" s="25" t="n">
         <v>0</v>
       </c>
       <c r="F29" s="25" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G29" s="25" t="n">
-        <v>62.5</v>
+        <v>62.18</v>
       </c>
       <c r="H29" s="2" t="n"/>
       <c r="I29" s="2" t="n"/>
@@ -6316,42 +6413,60 @@
       <c r="I40" s="2" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="22" t="inlineStr">
-        <is>
-          <t>TOTAL GERAL</t>
-        </is>
-      </c>
-      <c r="B41" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C41" s="22" t="n">
-        <v>1437</v>
-      </c>
-      <c r="D41" s="22" t="n">
-        <v>740</v>
-      </c>
-      <c r="E41" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="F41" s="22" t="n">
-        <v>2179</v>
-      </c>
-      <c r="G41" s="22" t="n">
-        <v>34.05</v>
+      <c r="A41" s="25" t="inlineStr">
+        <is>
+          <t>Walquiria Araujo Flores</t>
+        </is>
+      </c>
+      <c r="B41" s="25" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C41" s="25" t="n">
+        <v>19</v>
+      </c>
+      <c r="D41" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="25" t="n">
+        <v>23</v>
+      </c>
+      <c r="G41" s="25" t="n">
+        <v>17.39</v>
       </c>
       <c r="H41" s="2" t="n"/>
       <c r="I41" s="2" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n"/>
-      <c r="B42" s="2" t="n"/>
-      <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="n"/>
-      <c r="E42" s="2" t="n"/>
-      <c r="F42" s="2" t="n"/>
-      <c r="G42" s="2" t="n"/>
+      <c r="A42" s="22" t="inlineStr">
+        <is>
+          <t>TOTAL GERAL</t>
+        </is>
+      </c>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C42" s="22" t="n">
+        <v>1456</v>
+      </c>
+      <c r="D42" s="22" t="n">
+        <v>743</v>
+      </c>
+      <c r="E42" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" s="22" t="n">
+        <v>2201</v>
+      </c>
+      <c r="G42" s="22" t="n">
+        <v>33.85</v>
+      </c>
       <c r="H42" s="2" t="n"/>
       <c r="I42" s="2" t="n"/>
     </row>
@@ -6367,11 +6482,7 @@
       <c r="I43" s="2" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="37" t="inlineStr">
-        <is>
-          <t>DETALHE — IMÓVEIS COM VISITA RECUSADA PELO MORADOR</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="n"/>
       <c r="B44" s="2" t="n"/>
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="n"/>
@@ -6382,141 +6493,156 @@
       <c r="I44" s="2" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="38" t="inlineStr">
+      <c r="A45" s="37" t="inlineStr">
+        <is>
+          <t>DETALHE — IMÓVEIS COM VISITA RECUSADA PELO MORADOR</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n"/>
+      <c r="E45" s="2" t="n"/>
+      <c r="F45" s="2" t="n"/>
+      <c r="G45" s="2" t="n"/>
+      <c r="H45" s="2" t="n"/>
+      <c r="I45" s="2" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="38" t="inlineStr">
         <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="B45" s="38" t="inlineStr">
+      <c r="B46" s="38" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="C45" s="38" t="inlineStr">
+      <c r="C46" s="38" t="inlineStr">
         <is>
           <t>ID Visita</t>
         </is>
       </c>
-      <c r="D45" s="38" t="inlineStr">
+      <c r="D46" s="38" t="inlineStr">
         <is>
           <t>Área</t>
         </is>
       </c>
-      <c r="E45" s="38" t="inlineStr">
+      <c r="E46" s="38" t="inlineStr">
         <is>
           <t>Quarteirão</t>
         </is>
       </c>
-      <c r="F45" s="38" t="inlineStr">
+      <c r="F46" s="38" t="inlineStr">
         <is>
           <t>Logradouro</t>
         </is>
       </c>
-      <c r="G45" s="38" t="inlineStr">
+      <c r="G46" s="38" t="inlineStr">
         <is>
           <t>Imóvel</t>
         </is>
       </c>
-      <c r="H45" s="38" t="inlineStr">
+      <c r="H46" s="38" t="inlineStr">
         <is>
           <t>Data Chegada</t>
         </is>
       </c>
-      <c r="I45" s="38" t="inlineStr">
+      <c r="I46" s="38" t="inlineStr">
         <is>
           <t>Data Saída</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="39" t="inlineStr">
-        <is>
-          <t>Adriana de Jesus Saraiva</t>
-        </is>
-      </c>
-      <c r="B46" s="39" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C46" s="40" t="inlineStr">
-        <is>
-          <t>16731309</t>
-        </is>
-      </c>
-      <c r="D46" s="39" t="inlineStr">
-        <is>
-          <t>404 - JARDIM DOS ESTADOS</t>
-        </is>
-      </c>
-      <c r="E46" s="39" t="inlineStr">
-        <is>
-          <t>Q011</t>
-        </is>
-      </c>
-      <c r="F46" s="39" t="inlineStr">
-        <is>
-          <t>Rua JOÃO BREMBATI CALVOSO</t>
-        </is>
-      </c>
-      <c r="G46" s="39" t="inlineStr">
-        <is>
-          <t>838 - R</t>
-        </is>
-      </c>
-      <c r="H46" s="39" t="inlineStr">
-        <is>
-          <t>04/08/2026 14:43</t>
-        </is>
-      </c>
-      <c r="I46" s="39" t="inlineStr">
-        <is>
-          <t>04/08/2026 14:43</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="39" t="inlineStr">
         <is>
+          <t>Adriana de Jesus Saraiva</t>
+        </is>
+      </c>
+      <c r="B47" s="39" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C47" s="40" t="inlineStr">
+        <is>
+          <t>16731309</t>
+        </is>
+      </c>
+      <c r="D47" s="39" t="inlineStr">
+        <is>
+          <t>404 - JARDIM DOS ESTADOS</t>
+        </is>
+      </c>
+      <c r="E47" s="39" t="inlineStr">
+        <is>
+          <t>Q011</t>
+        </is>
+      </c>
+      <c r="F47" s="39" t="inlineStr">
+        <is>
+          <t>Rua JOÃO BREMBATI CALVOSO</t>
+        </is>
+      </c>
+      <c r="G47" s="39" t="inlineStr">
+        <is>
+          <t>838 - R</t>
+        </is>
+      </c>
+      <c r="H47" s="39" t="inlineStr">
+        <is>
+          <t>04/08/2026 14:43</t>
+        </is>
+      </c>
+      <c r="I47" s="39" t="inlineStr">
+        <is>
+          <t>04/08/2026 14:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="39" t="inlineStr">
+        <is>
           <t>Gisele Olimpia Torres</t>
         </is>
       </c>
-      <c r="B47" s="39" t="inlineStr">
+      <c r="B48" s="39" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C47" s="40" t="inlineStr">
+      <c r="C48" s="40" t="inlineStr">
         <is>
           <t>16759761</t>
         </is>
       </c>
-      <c r="D47" s="39" t="inlineStr">
+      <c r="D48" s="39" t="inlineStr">
         <is>
           <t>421 - JARDIM IPANEMA</t>
         </is>
       </c>
-      <c r="E47" s="39" t="inlineStr">
+      <c r="E48" s="39" t="inlineStr">
         <is>
           <t>Q020</t>
         </is>
       </c>
-      <c r="F47" s="39" t="inlineStr">
+      <c r="F48" s="39" t="inlineStr">
         <is>
           <t>Rua HUMAITA</t>
         </is>
       </c>
-      <c r="G47" s="39" t="inlineStr">
+      <c r="G48" s="39" t="inlineStr">
         <is>
           <t>359 - R</t>
         </is>
       </c>
-      <c r="H47" s="39" t="inlineStr">
+      <c r="H48" s="39" t="inlineStr">
         <is>
           <t>05/08/2026 15:52</t>
         </is>
       </c>
-      <c r="I47" s="39" t="inlineStr">
+      <c r="I48" s="39" t="inlineStr">
         <is>
           <t>05/08/2026 15:52</t>
         </is>
@@ -6524,12 +6650,12 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A45:I45"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A44:I44"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7005,7 +7131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F260"/>
+  <dimension ref="A1:F265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -7614,16 +7740,16 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Adriano Ricardo Thiel</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>100.4</v>
+        <v>101</v>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
@@ -7638,16 +7764,16 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Adriano Ricardo Thiel</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D27" s="4" t="n">
-        <v>100.2</v>
+        <v>100.4</v>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
@@ -7662,16 +7788,16 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>99.8</v>
+        <v>100.2</v>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
@@ -7686,7 +7812,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -7695,7 +7821,7 @@
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>99.40000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
@@ -7710,16 +7836,16 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>99</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
@@ -7734,7 +7860,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -7743,7 +7869,7 @@
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>98.59999999999999</v>
+        <v>99</v>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
@@ -7758,16 +7884,16 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>98.40000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
@@ -7782,7 +7908,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Adriana de Jesus Saraiva</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -7791,7 +7917,7 @@
         </is>
       </c>
       <c r="D33" s="4" t="n">
-        <v>97.40000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
@@ -7806,7 +7932,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>Adriana de Jesus Saraiva</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -7815,7 +7941,7 @@
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>96.8</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
@@ -7830,16 +7956,16 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Gisele Olimpia Torres</t>
+          <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D35" s="4" t="n">
-        <v>95.40000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -7854,16 +7980,16 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Raquel Ortiz dos Santos</t>
+          <t>Gisele Olimpia Torres</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>92</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
@@ -7878,44 +8004,44 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
+          <t>Raquel Ortiz dos Santos</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>🟢 EXCELENTE</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
           <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D38" s="4" t="n">
         <v>90.8</v>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>Mateus Falcao de Souza</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>🟡 BOM</t>
         </is>
       </c>
       <c r="F38" s="2" t="n"/>
@@ -7926,16 +8052,16 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Ramona dos Santos Oliveira</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>87.8</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
@@ -7950,30 +8076,46 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
+          <t>Ramona dos Santos Oliveira</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>🟡 BOM</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
           <t>Anderson Jose de Santana</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D41" s="6" t="n">
         <v>83.8</v>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="E41" s="6" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
       </c>
-      <c r="F40" s="2" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="2" t="n"/>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n"/>
-      <c r="E41" s="2" t="n"/>
       <c r="F41" s="2" t="n"/>
     </row>
     <row r="42">
@@ -7985,11 +8127,7 @@
       <c r="F42" s="2" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="42" t="inlineStr">
-        <is>
-          <t>DETALHAMENTO — TODOS OS CRITÉRIOS APLICADOS POR AGENTE</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="n"/>
       <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n"/>
@@ -7997,61 +8135,47 @@
       <c r="F43" s="2" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="A44" s="42" t="inlineStr">
+        <is>
+          <t>DETALHAMENTO — TODOS OS CRITÉRIOS APLICADOS POR AGENTE</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="n"/>
+      <c r="F44" s="2" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>Critério</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>Quantidade</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>Peso (pontos/ocorrência)</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>Pontos Aplicados</t>
         </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="43" t="inlineStr">
-        <is>
-          <t>Adriana de Jesus Saraiva</t>
-        </is>
-      </c>
-      <c r="B45" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C45" s="43" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D45" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="F45" s="43" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="46">
@@ -8067,43 +8191,43 @@
       </c>
       <c r="C46" s="43" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D46" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F46" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="43" t="inlineStr">
+        <is>
+          <t>Adriana de Jesus Saraiva</t>
+        </is>
+      </c>
+      <c r="B47" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C47" s="43" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D46" s="43" t="n">
+      <c r="D47" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="E46" s="43" t="n">
+      <c r="E47" s="43" t="n">
         <v>0.5</v>
       </c>
-      <c r="F46" s="43" t="n">
+      <c r="F47" s="43" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="44" t="inlineStr">
-        <is>
-          <t>Adriana de Jesus Saraiva</t>
-        </is>
-      </c>
-      <c r="B47" s="44" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C47" s="44" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D47" s="44" t="n">
-        <v>3</v>
-      </c>
-      <c r="E47" s="44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F47" s="44" t="n">
-        <v>-3</v>
       </c>
     </row>
     <row r="48">
@@ -8119,17 +8243,17 @@
       </c>
       <c r="C48" s="44" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D48" s="44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E48" s="44" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F48" s="44" t="n">
-        <v>-0.6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="49">
@@ -8145,17 +8269,17 @@
       </c>
       <c r="C49" s="44" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D49" s="44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E49" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="F49" s="44" t="n">
-        <v>-1.8</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="50">
@@ -8171,17 +8295,17 @@
       </c>
       <c r="C50" s="44" t="inlineStr">
         <is>
-          <t>Visita fora do expediente/fim de semana</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D50" s="44" t="n">
         <v>3</v>
       </c>
       <c r="E50" s="44" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F50" s="44" t="n">
-        <v>-3</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="51">
@@ -8197,43 +8321,43 @@
       </c>
       <c r="C51" s="44" t="inlineStr">
         <is>
+          <t>Visita fora do expediente/fim de semana</t>
+        </is>
+      </c>
+      <c r="D51" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="E51" s="44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F51" s="44" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="44" t="inlineStr">
+        <is>
+          <t>Adriana de Jesus Saraiva</t>
+        </is>
+      </c>
+      <c r="B52" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C52" s="44" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D51" s="44" t="n">
+      <c r="D52" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="E51" s="44" t="n">
+      <c r="E52" s="44" t="n">
         <v>0.3</v>
       </c>
-      <c r="F51" s="44" t="n">
+      <c r="F52" s="44" t="n">
         <v>-1.2</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="43" t="inlineStr">
-        <is>
-          <t>Adriano Ricardo Thiel</t>
-        </is>
-      </c>
-      <c r="B52" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C52" s="43" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D52" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="F52" s="43" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="53">
@@ -8249,43 +8373,43 @@
       </c>
       <c r="C53" s="43" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D53" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F53" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="43" t="inlineStr">
+        <is>
+          <t>Adriano Ricardo Thiel</t>
+        </is>
+      </c>
+      <c r="B54" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C54" s="43" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D53" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" s="43" t="n">
+      <c r="D54" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" s="43" t="n">
         <v>0.5</v>
       </c>
-      <c r="F53" s="43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="44" t="inlineStr">
-        <is>
-          <t>Adriano Ricardo Thiel</t>
-        </is>
-      </c>
-      <c r="B54" s="44" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C54" s="44" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D54" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="E54" s="44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F54" s="44" t="n">
-        <v>-2</v>
+      <c r="F54" s="43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -8301,17 +8425,17 @@
       </c>
       <c r="C55" s="44" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D55" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" s="44" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F55" s="44" t="n">
-        <v>-0.6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="56">
@@ -8327,7 +8451,7 @@
       </c>
       <c r="C56" s="44" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D56" s="44" t="n">
@@ -8353,7 +8477,7 @@
       </c>
       <c r="C57" s="44" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D57" s="44" t="n">
@@ -8379,43 +8503,43 @@
       </c>
       <c r="C58" s="44" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D58" s="44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E58" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="F58" s="44" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="44" t="inlineStr">
+        <is>
+          <t>Adriano Ricardo Thiel</t>
+        </is>
+      </c>
+      <c r="B59" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C59" s="44" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D59" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="E59" s="44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F59" s="44" t="n">
         <v>-1.8</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="43" t="inlineStr">
-        <is>
-          <t>Ana Gabriela Silva Garcete</t>
-        </is>
-      </c>
-      <c r="B59" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C59" s="43" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D59" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E59" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="F59" s="43" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="60">
@@ -8431,7 +8555,7 @@
       </c>
       <c r="C60" s="43" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D60" s="43" t="n">
@@ -8457,43 +8581,43 @@
       </c>
       <c r="C61" s="43" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D61" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F61" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="43" t="inlineStr">
+        <is>
+          <t>Ana Gabriela Silva Garcete</t>
+        </is>
+      </c>
+      <c r="B62" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C62" s="43" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D61" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" s="43" t="n">
+      <c r="D62" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="43" t="n">
         <v>0.5</v>
       </c>
-      <c r="F61" s="43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="44" t="inlineStr">
-        <is>
-          <t>Ana Gabriela Silva Garcete</t>
-        </is>
-      </c>
-      <c r="B62" s="44" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C62" s="44" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D62" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" s="44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F62" s="44" t="n">
-        <v>-1</v>
+      <c r="F62" s="43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -8509,17 +8633,17 @@
       </c>
       <c r="C63" s="44" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D63" s="44" t="n">
         <v>1</v>
       </c>
       <c r="E63" s="44" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F63" s="44" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="64">
@@ -8535,7 +8659,7 @@
       </c>
       <c r="C64" s="44" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D64" s="44" t="n">
@@ -8549,29 +8673,29 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="43" t="inlineStr">
-        <is>
-          <t>Anderson Jose de Santana</t>
-        </is>
-      </c>
-      <c r="B65" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C65" s="43" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D65" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="F65" s="43" t="n">
-        <v>5</v>
+      <c r="A65" s="44" t="inlineStr">
+        <is>
+          <t>Ana Gabriela Silva Garcete</t>
+        </is>
+      </c>
+      <c r="B65" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C65" s="44" t="inlineStr">
+        <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D65" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F65" s="44" t="n">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="66">
@@ -8587,43 +8711,43 @@
       </c>
       <c r="C66" s="43" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D66" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F66" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="43" t="inlineStr">
+        <is>
+          <t>Anderson Jose de Santana</t>
+        </is>
+      </c>
+      <c r="B67" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C67" s="43" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D66" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E66" s="43" t="n">
+      <c r="D67" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" s="43" t="n">
         <v>0.5</v>
       </c>
-      <c r="F66" s="43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="44" t="inlineStr">
-        <is>
-          <t>Anderson Jose de Santana</t>
-        </is>
-      </c>
-      <c r="B67" s="44" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C67" s="44" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D67" s="44" t="n">
-        <v>3</v>
-      </c>
-      <c r="E67" s="44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F67" s="44" t="n">
-        <v>-3</v>
+      <c r="F67" s="43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -8639,17 +8763,17 @@
       </c>
       <c r="C68" s="44" t="inlineStr">
         <is>
-          <t>Fim manhã antes de 10h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D68" s="44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E68" s="44" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F68" s="44" t="n">
-        <v>-0.6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="69">
@@ -8665,17 +8789,17 @@
       </c>
       <c r="C69" s="44" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D69" s="44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E69" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="F69" s="44" t="n">
-        <v>-1.8</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="70">
@@ -8691,17 +8815,17 @@
       </c>
       <c r="C70" s="44" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D70" s="44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E70" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="F70" s="44" t="n">
-        <v>-0.6</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="71">
@@ -8717,43 +8841,43 @@
       </c>
       <c r="C71" s="44" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D71" s="44" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="E71" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="F71" s="44" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="44" t="inlineStr">
+        <is>
+          <t>Anderson Jose de Santana</t>
+        </is>
+      </c>
+      <c r="B72" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C72" s="44" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D72" s="44" t="n">
+        <v>27</v>
+      </c>
+      <c r="E72" s="44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F72" s="44" t="n">
         <v>-16.2</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="43" t="inlineStr">
-        <is>
-          <t>Bianca Afonso Narbaez</t>
-        </is>
-      </c>
-      <c r="B72" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C72" s="43" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D72" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E72" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="F72" s="43" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="73">
@@ -8769,7 +8893,7 @@
       </c>
       <c r="C73" s="43" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D73" s="43" t="n">
@@ -8795,69 +8919,69 @@
       </c>
       <c r="C74" s="43" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D74" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F74" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="43" t="inlineStr">
+        <is>
+          <t>Bianca Afonso Narbaez</t>
+        </is>
+      </c>
+      <c r="B75" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C75" s="43" t="inlineStr">
+        <is>
           <t>Bônus: pontualidade perfeita no período</t>
         </is>
       </c>
-      <c r="D74" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E74" s="43" t="n">
+      <c r="D75" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="F74" s="43" t="n">
+      <c r="F75" s="43" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="44" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="44" t="inlineStr">
         <is>
           <t>Bianca Afonso Narbaez</t>
         </is>
       </c>
-      <c r="B75" s="44" t="inlineStr">
+      <c r="B76" s="44" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C75" s="44" t="inlineStr">
+      <c r="C76" s="44" t="inlineStr">
         <is>
           <t>Dia sem bater a meta diária</t>
         </is>
       </c>
-      <c r="D75" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E75" s="44" t="n">
+      <c r="D76" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" s="44" t="n">
         <v>0.5</v>
       </c>
-      <c r="F75" s="44" t="n">
+      <c r="F76" s="44" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="43" t="inlineStr">
-        <is>
-          <t>Carlos Alberto Albiero</t>
-        </is>
-      </c>
-      <c r="B76" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C76" s="43" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D76" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E76" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="F76" s="43" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="77">
@@ -8873,7 +8997,7 @@
       </c>
       <c r="C77" s="43" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D77" s="43" t="n">
@@ -8887,29 +9011,29 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="44" t="inlineStr">
+      <c r="A78" s="43" t="inlineStr">
         <is>
           <t>Carlos Alberto Albiero</t>
         </is>
       </c>
-      <c r="B78" s="44" t="inlineStr">
+      <c r="B78" s="43" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C78" s="44" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D78" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="E78" s="44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F78" s="44" t="n">
-        <v>-2</v>
+      <c r="C78" s="43" t="inlineStr">
+        <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D78" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F78" s="43" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="79">
@@ -8925,17 +9049,17 @@
       </c>
       <c r="C79" s="44" t="inlineStr">
         <is>
-          <t>Fim manhã antes de 10h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D79" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E79" s="44" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F79" s="44" t="n">
-        <v>-0.6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="80">
@@ -8951,7 +9075,7 @@
       </c>
       <c r="C80" s="44" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D80" s="44" t="n">
@@ -8965,29 +9089,29 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="43" t="inlineStr">
-        <is>
-          <t>Cicero Isrrael Sanabria</t>
-        </is>
-      </c>
-      <c r="B81" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C81" s="43" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D81" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E81" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="F81" s="43" t="n">
-        <v>5</v>
+      <c r="A81" s="44" t="inlineStr">
+        <is>
+          <t>Carlos Alberto Albiero</t>
+        </is>
+      </c>
+      <c r="B81" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C81" s="44" t="inlineStr">
+        <is>
+          <t>Início manhã após 08h30</t>
+        </is>
+      </c>
+      <c r="D81" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F81" s="44" t="n">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="82">
@@ -9003,7 +9127,7 @@
       </c>
       <c r="C82" s="43" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D82" s="43" t="n">
@@ -9017,29 +9141,29 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="44" t="inlineStr">
+      <c r="A83" s="43" t="inlineStr">
         <is>
           <t>Cicero Isrrael Sanabria</t>
         </is>
       </c>
-      <c r="B83" s="44" t="inlineStr">
+      <c r="B83" s="43" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C83" s="44" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D83" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="E83" s="44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F83" s="44" t="n">
-        <v>-2</v>
+      <c r="C83" s="43" t="inlineStr">
+        <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D83" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F83" s="43" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="84">
@@ -9055,17 +9179,17 @@
       </c>
       <c r="C84" s="44" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D84" s="44" t="n">
         <v>2</v>
       </c>
       <c r="E84" s="44" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F84" s="44" t="n">
-        <v>-1.2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="85">
@@ -9081,43 +9205,43 @@
       </c>
       <c r="C85" s="44" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D85" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="F85" s="44" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="44" t="inlineStr">
+        <is>
+          <t>Cicero Isrrael Sanabria</t>
+        </is>
+      </c>
+      <c r="B86" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C86" s="44" t="inlineStr">
+        <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D86" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" s="44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F86" s="44" t="n">
         <v>-0.6</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="43" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B86" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C86" s="43" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D86" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E86" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="F86" s="43" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="87">
@@ -9133,7 +9257,7 @@
       </c>
       <c r="C87" s="43" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D87" s="43" t="n">
@@ -9147,29 +9271,29 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="44" t="inlineStr">
+      <c r="A88" s="43" t="inlineStr">
         <is>
           <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
-      <c r="B88" s="44" t="inlineStr">
+      <c r="B88" s="43" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C88" s="44" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D88" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="E88" s="44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F88" s="44" t="n">
-        <v>-2</v>
+      <c r="C88" s="43" t="inlineStr">
+        <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D88" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F88" s="43" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="89">
@@ -9185,43 +9309,43 @@
       </c>
       <c r="C89" s="44" t="inlineStr">
         <is>
+          <t>Dia sem bater a meta diária</t>
+        </is>
+      </c>
+      <c r="D89" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="E89" s="44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F89" s="44" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="44" t="inlineStr">
+        <is>
+          <t>Claine Luisa Figueiredo Torraca</t>
+        </is>
+      </c>
+      <c r="B90" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C90" s="44" t="inlineStr">
+        <is>
           <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
-      <c r="D89" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E89" s="44" t="n">
+      <c r="D90" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" s="44" t="n">
         <v>0.3</v>
       </c>
-      <c r="F89" s="44" t="n">
+      <c r="F90" s="44" t="n">
         <v>-0.6</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="43" t="inlineStr">
-        <is>
-          <t>Cris Milene Cardenas da Silva</t>
-        </is>
-      </c>
-      <c r="B90" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C90" s="43" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D90" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E90" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="F90" s="43" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="91">
@@ -9237,7 +9361,7 @@
       </c>
       <c r="C91" s="43" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D91" s="43" t="n">
@@ -9263,43 +9387,43 @@
       </c>
       <c r="C92" s="43" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D92" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F92" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="43" t="inlineStr">
+        <is>
+          <t>Cris Milene Cardenas da Silva</t>
+        </is>
+      </c>
+      <c r="B93" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C93" s="43" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D92" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E92" s="43" t="n">
+      <c r="D93" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" s="43" t="n">
         <v>0.5</v>
       </c>
-      <c r="F92" s="43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="44" t="inlineStr">
-        <is>
-          <t>Cris Milene Cardenas da Silva</t>
-        </is>
-      </c>
-      <c r="B93" s="44" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C93" s="44" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D93" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E93" s="44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F93" s="44" t="n">
-        <v>-1</v>
+      <c r="F93" s="43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -9315,43 +9439,43 @@
       </c>
       <c r="C94" s="44" t="inlineStr">
         <is>
+          <t>Dia sem bater a meta diária</t>
+        </is>
+      </c>
+      <c r="D94" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" s="44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F94" s="44" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="44" t="inlineStr">
+        <is>
+          <t>Cris Milene Cardenas da Silva</t>
+        </is>
+      </c>
+      <c r="B95" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C95" s="44" t="inlineStr">
+        <is>
           <t>Início manhã após 08h30</t>
         </is>
       </c>
-      <c r="D94" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E94" s="44" t="n">
+      <c r="D95" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" s="44" t="n">
         <v>0.3</v>
       </c>
-      <c r="F94" s="44" t="n">
+      <c r="F95" s="44" t="n">
         <v>-0.6</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="43" t="inlineStr">
-        <is>
-          <t>Emidio Rainer Vilhalba</t>
-        </is>
-      </c>
-      <c r="B95" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C95" s="43" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D95" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E95" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="F95" s="43" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="96">
@@ -9367,7 +9491,7 @@
       </c>
       <c r="C96" s="43" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D96" s="43" t="n">
@@ -9381,29 +9505,29 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="44" t="inlineStr">
+      <c r="A97" s="43" t="inlineStr">
         <is>
           <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
-      <c r="B97" s="44" t="inlineStr">
+      <c r="B97" s="43" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C97" s="44" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D97" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E97" s="44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F97" s="44" t="n">
-        <v>-1</v>
+      <c r="C97" s="43" t="inlineStr">
+        <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D97" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F97" s="43" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="98">
@@ -9419,43 +9543,43 @@
       </c>
       <c r="C98" s="44" t="inlineStr">
         <is>
+          <t>Dia sem bater a meta diária</t>
+        </is>
+      </c>
+      <c r="D98" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" s="44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F98" s="44" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="44" t="inlineStr">
+        <is>
+          <t>Emidio Rainer Vilhalba</t>
+        </is>
+      </c>
+      <c r="B99" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C99" s="44" t="inlineStr">
+        <is>
           <t>Início tarde após 14h30</t>
         </is>
       </c>
-      <c r="D98" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E98" s="44" t="n">
+      <c r="D99" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" s="44" t="n">
         <v>0.3</v>
       </c>
-      <c r="F98" s="44" t="n">
+      <c r="F99" s="44" t="n">
         <v>-0.6</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="43" t="inlineStr">
-        <is>
-          <t>Evelyn Santana Santos Oliveira</t>
-        </is>
-      </c>
-      <c r="B99" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C99" s="43" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D99" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E99" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="F99" s="43" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="100">
@@ -9471,7 +9595,7 @@
       </c>
       <c r="C100" s="43" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D100" s="43" t="n">
@@ -9485,29 +9609,29 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="44" t="inlineStr">
+      <c r="A101" s="43" t="inlineStr">
         <is>
           <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
-      <c r="B101" s="44" t="inlineStr">
+      <c r="B101" s="43" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C101" s="44" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D101" s="44" t="n">
-        <v>4</v>
-      </c>
-      <c r="E101" s="44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F101" s="44" t="n">
-        <v>-4</v>
+      <c r="C101" s="43" t="inlineStr">
+        <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D101" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F101" s="43" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="102">
@@ -9523,17 +9647,17 @@
       </c>
       <c r="C102" s="44" t="inlineStr">
         <is>
-          <t>Fim manhã antes de 10h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D102" s="44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E102" s="44" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F102" s="44" t="n">
-        <v>-0.6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="103">
@@ -9549,17 +9673,17 @@
       </c>
       <c r="C103" s="44" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D103" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E103" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="F103" s="44" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="104">
@@ -9575,7 +9699,7 @@
       </c>
       <c r="C104" s="44" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D104" s="44" t="n">
@@ -9601,43 +9725,43 @@
       </c>
       <c r="C105" s="44" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D105" s="44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E105" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="F105" s="44" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="44" t="inlineStr">
+        <is>
+          <t>Evelyn Santana Santos Oliveira</t>
+        </is>
+      </c>
+      <c r="B106" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C106" s="44" t="inlineStr">
+        <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D106" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="E106" s="44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F106" s="44" t="n">
         <v>-1.8</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="43" t="inlineStr">
-        <is>
-          <t>Fabiana de Figueredo Vieira</t>
-        </is>
-      </c>
-      <c r="B106" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C106" s="43" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D106" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E106" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="F106" s="43" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="107">
@@ -9653,7 +9777,7 @@
       </c>
       <c r="C107" s="43" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D107" s="43" t="n">
@@ -9679,17 +9803,17 @@
       </c>
       <c r="C108" s="43" t="inlineStr">
         <is>
-          <t>Bônus: pontualidade perfeita no período</t>
+          <t>Bônus: nenhuma visita rápida no período</t>
         </is>
       </c>
       <c r="D108" s="43" t="n">
         <v>1</v>
       </c>
       <c r="E108" s="43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F108" s="43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109">
@@ -9705,69 +9829,69 @@
       </c>
       <c r="C109" s="43" t="inlineStr">
         <is>
-          <t>Dia com meta diária batida</t>
+          <t>Bônus: pontualidade perfeita no período</t>
         </is>
       </c>
       <c r="D109" s="43" t="n">
         <v>1</v>
       </c>
       <c r="E109" s="43" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="F109" s="43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="43" t="inlineStr">
         <is>
+          <t>Fabiana de Figueredo Vieira</t>
+        </is>
+      </c>
+      <c r="B110" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C110" s="43" t="inlineStr">
+        <is>
+          <t>Dia com meta diária batida</t>
+        </is>
+      </c>
+      <c r="D110" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" s="43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F110" s="43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="43" t="inlineStr">
+        <is>
           <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
-      <c r="B110" s="43" t="inlineStr">
+      <c r="B111" s="43" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C110" s="43" t="inlineStr">
+      <c r="C111" s="43" t="inlineStr">
         <is>
           <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
-      <c r="D110" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E110" s="43" t="n">
+      <c r="D111" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" s="43" t="n">
         <v>5</v>
       </c>
-      <c r="F110" s="43" t="n">
+      <c r="F111" s="43" t="n">
         <v>5</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="44" t="inlineStr">
-        <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
-        </is>
-      </c>
-      <c r="B111" s="44" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C111" s="44" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D111" s="44" t="n">
-        <v>4</v>
-      </c>
-      <c r="E111" s="44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F111" s="44" t="n">
-        <v>-4</v>
       </c>
     </row>
     <row r="112">
@@ -9783,17 +9907,17 @@
       </c>
       <c r="C112" s="44" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D112" s="44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E112" s="44" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F112" s="44" t="n">
-        <v>-0.6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="113">
@@ -9809,17 +9933,17 @@
       </c>
       <c r="C113" s="44" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D113" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E113" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="F113" s="44" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="114">
@@ -9835,17 +9959,17 @@
       </c>
       <c r="C114" s="44" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D114" s="44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E114" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="F114" s="44" t="n">
-        <v>-1.8</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="115">
@@ -9861,43 +9985,43 @@
       </c>
       <c r="C115" s="44" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D115" s="44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E115" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="F115" s="44" t="n">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="44" t="inlineStr">
+        <is>
+          <t>Gabriel Alan de Oliveira Martins</t>
+        </is>
+      </c>
+      <c r="B116" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C116" s="44" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D116" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" s="44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F116" s="44" t="n">
         <v>-0.6</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="43" t="inlineStr">
-        <is>
-          <t>Geancarlos Ferreira Barrios</t>
-        </is>
-      </c>
-      <c r="B116" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C116" s="43" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D116" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E116" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="F116" s="43" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="117">
@@ -9913,7 +10037,7 @@
       </c>
       <c r="C117" s="43" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D117" s="43" t="n">
@@ -9939,43 +10063,43 @@
       </c>
       <c r="C118" s="43" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D118" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F118" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="43" t="inlineStr">
+        <is>
+          <t>Geancarlos Ferreira Barrios</t>
+        </is>
+      </c>
+      <c r="B119" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C119" s="43" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D118" s="43" t="n">
+      <c r="D119" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="E118" s="43" t="n">
+      <c r="E119" s="43" t="n">
         <v>0.5</v>
       </c>
-      <c r="F118" s="43" t="n">
+      <c r="F119" s="43" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="44" t="inlineStr">
-        <is>
-          <t>Geancarlos Ferreira Barrios</t>
-        </is>
-      </c>
-      <c r="B119" s="44" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C119" s="44" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D119" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="E119" s="44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F119" s="44" t="n">
-        <v>-2</v>
       </c>
     </row>
     <row r="120">
@@ -9991,17 +10115,17 @@
       </c>
       <c r="C120" s="44" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D120" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E120" s="44" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F120" s="44" t="n">
-        <v>-0.6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="121">
@@ -10017,7 +10141,7 @@
       </c>
       <c r="C121" s="44" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D121" s="44" t="n">
@@ -10043,17 +10167,17 @@
       </c>
       <c r="C122" s="44" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D122" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E122" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="F122" s="44" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="123">
@@ -10069,43 +10193,43 @@
       </c>
       <c r="C123" s="44" t="inlineStr">
         <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D123" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="E123" s="44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F123" s="44" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="44" t="inlineStr">
+        <is>
+          <t>Geancarlos Ferreira Barrios</t>
+        </is>
+      </c>
+      <c r="B124" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C124" s="44" t="inlineStr">
+        <is>
           <t>Visita fora do expediente/fim de semana</t>
         </is>
       </c>
-      <c r="D123" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E123" s="44" t="n">
+      <c r="D124" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" s="44" t="n">
         <v>0.5</v>
       </c>
-      <c r="F123" s="44" t="n">
+      <c r="F124" s="44" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="43" t="inlineStr">
-        <is>
-          <t>Gilmar Bitencourt Luiz</t>
-        </is>
-      </c>
-      <c r="B124" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C124" s="43" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D124" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E124" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="F124" s="43" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="125">
@@ -10121,7 +10245,7 @@
       </c>
       <c r="C125" s="43" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D125" s="43" t="n">
@@ -10147,69 +10271,69 @@
       </c>
       <c r="C126" s="43" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D126" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F126" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="43" t="inlineStr">
+        <is>
+          <t>Gilmar Bitencourt Luiz</t>
+        </is>
+      </c>
+      <c r="B127" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C127" s="43" t="inlineStr">
+        <is>
           <t>Bônus: pontualidade perfeita no período</t>
         </is>
       </c>
-      <c r="D126" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E126" s="43" t="n">
+      <c r="D127" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="F126" s="43" t="n">
+      <c r="F127" s="43" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="44" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="44" t="inlineStr">
         <is>
           <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
-      <c r="B127" s="44" t="inlineStr">
+      <c r="B128" s="44" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C127" s="44" t="inlineStr">
+      <c r="C128" s="44" t="inlineStr">
         <is>
           <t>Dia sem bater a meta diária</t>
         </is>
       </c>
-      <c r="D127" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E127" s="44" t="n">
+      <c r="D128" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" s="44" t="n">
         <v>0.5</v>
       </c>
-      <c r="F127" s="44" t="n">
+      <c r="F128" s="44" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="43" t="inlineStr">
-        <is>
-          <t>Gisele Lopes Justiniano</t>
-        </is>
-      </c>
-      <c r="B128" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C128" s="43" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D128" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E128" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="F128" s="43" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="129">
@@ -10225,7 +10349,7 @@
       </c>
       <c r="C129" s="43" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D129" s="43" t="n">
@@ -10251,43 +10375,43 @@
       </c>
       <c r="C130" s="43" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D130" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F130" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="43" t="inlineStr">
+        <is>
+          <t>Gisele Lopes Justiniano</t>
+        </is>
+      </c>
+      <c r="B131" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C131" s="43" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D130" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E130" s="43" t="n">
+      <c r="D131" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" s="43" t="n">
         <v>0.5</v>
       </c>
-      <c r="F130" s="43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="44" t="inlineStr">
-        <is>
-          <t>Gisele Lopes Justiniano</t>
-        </is>
-      </c>
-      <c r="B131" s="44" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C131" s="44" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D131" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="E131" s="44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F131" s="44" t="n">
-        <v>-2</v>
+      <c r="F131" s="43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -10303,17 +10427,17 @@
       </c>
       <c r="C132" s="44" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D132" s="44" t="n">
         <v>2</v>
       </c>
       <c r="E132" s="44" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F132" s="44" t="n">
-        <v>-1.2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="133">
@@ -10329,17 +10453,17 @@
       </c>
       <c r="C133" s="44" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D133" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E133" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="F133" s="44" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="134">
@@ -10355,69 +10479,69 @@
       </c>
       <c r="C134" s="44" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D134" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E134" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="F134" s="44" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="44" t="inlineStr">
+        <is>
+          <t>Gisele Lopes Justiniano</t>
+        </is>
+      </c>
+      <c r="B135" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C135" s="44" t="inlineStr">
+        <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D135" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="E135" s="44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F135" s="44" t="n">
         <v>-1.2</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="43" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="43" t="inlineStr">
         <is>
           <t>Gisele Olimpia Torres</t>
         </is>
       </c>
-      <c r="B135" s="43" t="inlineStr">
+      <c r="B136" s="43" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C135" s="43" t="inlineStr">
+      <c r="C136" s="43" t="inlineStr">
         <is>
           <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
-      <c r="D135" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E135" s="43" t="n">
+      <c r="D136" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E136" s="43" t="n">
         <v>5</v>
       </c>
-      <c r="F135" s="43" t="n">
+      <c r="F136" s="43" t="n">
         <v>5</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="44" t="inlineStr">
-        <is>
-          <t>Gisele Olimpia Torres</t>
-        </is>
-      </c>
-      <c r="B136" s="44" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C136" s="44" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D136" s="44" t="n">
-        <v>3</v>
-      </c>
-      <c r="E136" s="44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F136" s="44" t="n">
-        <v>-3</v>
       </c>
     </row>
     <row r="137">
@@ -10433,17 +10557,17 @@
       </c>
       <c r="C137" s="44" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D137" s="44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E137" s="44" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F137" s="44" t="n">
-        <v>-0.6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="138">
@@ -10459,7 +10583,7 @@
       </c>
       <c r="C138" s="44" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D138" s="44" t="n">
@@ -10485,7 +10609,7 @@
       </c>
       <c r="C139" s="44" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D139" s="44" t="n">
@@ -10511,69 +10635,69 @@
       </c>
       <c r="C140" s="44" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D140" s="44" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E140" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="F140" s="44" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="44" t="inlineStr">
+        <is>
+          <t>Gisele Olimpia Torres</t>
+        </is>
+      </c>
+      <c r="B141" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C141" s="44" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D141" s="44" t="n">
+        <v>8</v>
+      </c>
+      <c r="E141" s="44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F141" s="44" t="n">
         <v>-4.8</v>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="43" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="43" t="inlineStr">
         <is>
           <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
-      <c r="B141" s="43" t="inlineStr">
+      <c r="B142" s="43" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C141" s="43" t="inlineStr">
+      <c r="C142" s="43" t="inlineStr">
         <is>
           <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
-      <c r="D141" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E141" s="43" t="n">
+      <c r="D142" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E142" s="43" t="n">
         <v>5</v>
       </c>
-      <c r="F141" s="43" t="n">
+      <c r="F142" s="43" t="n">
         <v>5</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="44" t="inlineStr">
-        <is>
-          <t>Juliana Patricia Goncalves</t>
-        </is>
-      </c>
-      <c r="B142" s="44" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C142" s="44" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D142" s="44" t="n">
-        <v>4</v>
-      </c>
-      <c r="E142" s="44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F142" s="44" t="n">
-        <v>-4</v>
       </c>
     </row>
     <row r="143">
@@ -10589,17 +10713,17 @@
       </c>
       <c r="C143" s="44" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D143" s="44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E143" s="44" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F143" s="44" t="n">
-        <v>-1.8</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="144">
@@ -10615,17 +10739,17 @@
       </c>
       <c r="C144" s="44" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D144" s="44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E144" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="F144" s="44" t="n">
-        <v>-0.6</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="145">
@@ -10641,17 +10765,17 @@
       </c>
       <c r="C145" s="44" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D145" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E145" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="F145" s="44" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="146">
@@ -10667,43 +10791,43 @@
       </c>
       <c r="C146" s="44" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D146" s="44" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E146" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="F146" s="44" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="44" t="inlineStr">
+        <is>
+          <t>Juliana Patricia Goncalves</t>
+        </is>
+      </c>
+      <c r="B147" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C147" s="44" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D147" s="44" t="n">
+        <v>11</v>
+      </c>
+      <c r="E147" s="44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F147" s="44" t="n">
         <v>-6.6</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="43" t="inlineStr">
-        <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
-        </is>
-      </c>
-      <c r="B147" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C147" s="43" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D147" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E147" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="F147" s="43" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="148">
@@ -10719,43 +10843,43 @@
       </c>
       <c r="C148" s="43" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D148" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F148" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="43" t="inlineStr">
+        <is>
+          <t>Kariele Jackeline Rodrigues Silva</t>
+        </is>
+      </c>
+      <c r="B149" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C149" s="43" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D148" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E148" s="43" t="n">
+      <c r="D149" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E149" s="43" t="n">
         <v>0.5</v>
       </c>
-      <c r="F148" s="43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="44" t="inlineStr">
-        <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
-        </is>
-      </c>
-      <c r="B149" s="44" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C149" s="44" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D149" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E149" s="44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F149" s="44" t="n">
-        <v>-1</v>
+      <c r="F149" s="43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -10771,17 +10895,17 @@
       </c>
       <c r="C150" s="44" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D150" s="44" t="n">
         <v>1</v>
       </c>
       <c r="E150" s="44" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F150" s="44" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="151">
@@ -10797,43 +10921,43 @@
       </c>
       <c r="C151" s="44" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D151" s="44" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E151" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="F151" s="44" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="44" t="inlineStr">
+        <is>
+          <t>Kariele Jackeline Rodrigues Silva</t>
+        </is>
+      </c>
+      <c r="B152" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C152" s="44" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D152" s="44" t="n">
+        <v>9</v>
+      </c>
+      <c r="E152" s="44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F152" s="44" t="n">
         <v>-5.4</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="43" t="inlineStr">
-        <is>
-          <t>Kátia Cilene Silveira Machado</t>
-        </is>
-      </c>
-      <c r="B152" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C152" s="43" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D152" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E152" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="F152" s="43" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="153">
@@ -10849,43 +10973,43 @@
       </c>
       <c r="C153" s="43" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D153" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E153" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F153" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="43" t="inlineStr">
+        <is>
+          <t>Kátia Cilene Silveira Machado</t>
+        </is>
+      </c>
+      <c r="B154" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C154" s="43" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D153" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E153" s="43" t="n">
+      <c r="D154" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E154" s="43" t="n">
         <v>0.5</v>
       </c>
-      <c r="F153" s="43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="44" t="inlineStr">
-        <is>
-          <t>Kátia Cilene Silveira Machado</t>
-        </is>
-      </c>
-      <c r="B154" s="44" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C154" s="44" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D154" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E154" s="44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F154" s="44" t="n">
-        <v>-1</v>
+      <c r="F154" s="43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -10901,17 +11025,17 @@
       </c>
       <c r="C155" s="44" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D155" s="44" t="n">
         <v>1</v>
       </c>
       <c r="E155" s="44" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F155" s="44" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="156">
@@ -10927,17 +11051,17 @@
       </c>
       <c r="C156" s="44" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D156" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E156" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="F156" s="44" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="157">
@@ -10953,43 +11077,43 @@
       </c>
       <c r="C157" s="44" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D157" s="44" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E157" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="F157" s="44" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="44" t="inlineStr">
+        <is>
+          <t>Kátia Cilene Silveira Machado</t>
+        </is>
+      </c>
+      <c r="B158" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C158" s="44" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D158" s="44" t="n">
+        <v>5</v>
+      </c>
+      <c r="E158" s="44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F158" s="44" t="n">
         <v>-3</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="43" t="inlineStr">
-        <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
-        </is>
-      </c>
-      <c r="B158" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C158" s="43" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D158" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E158" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="F158" s="43" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="159">
@@ -11005,43 +11129,43 @@
       </c>
       <c r="C159" s="43" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D159" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E159" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F159" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="43" t="inlineStr">
+        <is>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
+        </is>
+      </c>
+      <c r="B160" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C160" s="43" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D159" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E159" s="43" t="n">
+      <c r="D160" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E160" s="43" t="n">
         <v>0.5</v>
       </c>
-      <c r="F159" s="43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="44" t="inlineStr">
-        <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
-        </is>
-      </c>
-      <c r="B160" s="44" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C160" s="44" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D160" s="44" t="n">
-        <v>3</v>
-      </c>
-      <c r="E160" s="44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F160" s="44" t="n">
-        <v>-3</v>
+      <c r="F160" s="43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="161">
@@ -11057,17 +11181,17 @@
       </c>
       <c r="C161" s="44" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D161" s="44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E161" s="44" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F161" s="44" t="n">
-        <v>-0.6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="162">
@@ -11083,7 +11207,7 @@
       </c>
       <c r="C162" s="44" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D162" s="44" t="n">
@@ -11109,7 +11233,7 @@
       </c>
       <c r="C163" s="44" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D163" s="44" t="n">
@@ -11135,43 +11259,43 @@
       </c>
       <c r="C164" s="44" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D164" s="44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E164" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="F164" s="44" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="44" t="inlineStr">
+        <is>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
+        </is>
+      </c>
+      <c r="B165" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C165" s="44" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D165" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="E165" s="44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F165" s="44" t="n">
         <v>-1.8</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="43" t="inlineStr">
-        <is>
-          <t>Mateus Falcao de Souza</t>
-        </is>
-      </c>
-      <c r="B165" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C165" s="43" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D165" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E165" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="F165" s="43" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="166">
@@ -11187,43 +11311,43 @@
       </c>
       <c r="C166" s="43" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D166" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E166" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F166" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="43" t="inlineStr">
+        <is>
+          <t>Mateus Falcao de Souza</t>
+        </is>
+      </c>
+      <c r="B167" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C167" s="43" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D166" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E166" s="43" t="n">
+      <c r="D167" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E167" s="43" t="n">
         <v>0.5</v>
       </c>
-      <c r="F166" s="43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="44" t="inlineStr">
-        <is>
-          <t>Mateus Falcao de Souza</t>
-        </is>
-      </c>
-      <c r="B167" s="44" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C167" s="44" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D167" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E167" s="44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F167" s="44" t="n">
-        <v>-1</v>
+      <c r="F167" s="43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="168">
@@ -11239,17 +11363,17 @@
       </c>
       <c r="C168" s="44" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D168" s="44" t="n">
         <v>1</v>
       </c>
       <c r="E168" s="44" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F168" s="44" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="169">
@@ -11265,7 +11389,7 @@
       </c>
       <c r="C169" s="44" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D169" s="44" t="n">
@@ -11291,7 +11415,7 @@
       </c>
       <c r="C170" s="44" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D170" s="44" t="n">
@@ -11317,43 +11441,43 @@
       </c>
       <c r="C171" s="44" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D171" s="44" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="E171" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="F171" s="44" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="44" t="inlineStr">
+        <is>
+          <t>Mateus Falcao de Souza</t>
+        </is>
+      </c>
+      <c r="B172" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C172" s="44" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D172" s="44" t="n">
+        <v>23</v>
+      </c>
+      <c r="E172" s="44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F172" s="44" t="n">
         <v>-13.8</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="43" t="inlineStr">
-        <is>
-          <t>Miglidiane Maciel Ajala</t>
-        </is>
-      </c>
-      <c r="B172" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C172" s="43" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D172" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E172" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="F172" s="43" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="173">
@@ -11369,43 +11493,43 @@
       </c>
       <c r="C173" s="43" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D173" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E173" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F173" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="43" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="B174" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C174" s="43" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D173" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E173" s="43" t="n">
+      <c r="D174" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E174" s="43" t="n">
         <v>0.5</v>
       </c>
-      <c r="F173" s="43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="44" t="inlineStr">
-        <is>
-          <t>Miglidiane Maciel Ajala</t>
-        </is>
-      </c>
-      <c r="B174" s="44" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C174" s="44" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D174" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="E174" s="44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F174" s="44" t="n">
-        <v>-2</v>
+      <c r="F174" s="43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="175">
@@ -11421,17 +11545,17 @@
       </c>
       <c r="C175" s="44" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D175" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E175" s="44" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F175" s="44" t="n">
-        <v>-0.6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="176">
@@ -11447,7 +11571,7 @@
       </c>
       <c r="C176" s="44" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D176" s="44" t="n">
@@ -11473,43 +11597,43 @@
       </c>
       <c r="C177" s="44" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D177" s="44" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E177" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="F177" s="44" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="44" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="B178" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C178" s="44" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D178" s="44" t="n">
+        <v>5</v>
+      </c>
+      <c r="E178" s="44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F178" s="44" t="n">
         <v>-3</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="43" t="inlineStr">
-        <is>
-          <t>Naime Cristina Freitas</t>
-        </is>
-      </c>
-      <c r="B178" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C178" s="43" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D178" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E178" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="F178" s="43" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="179">
@@ -11525,7 +11649,7 @@
       </c>
       <c r="C179" s="43" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D179" s="43" t="n">
@@ -11551,95 +11675,95 @@
       </c>
       <c r="C180" s="43" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D180" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E180" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F180" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="43" t="inlineStr">
+        <is>
+          <t>Naime Cristina Freitas</t>
+        </is>
+      </c>
+      <c r="B181" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C181" s="43" t="inlineStr">
+        <is>
           <t>Bônus: pontualidade perfeita no período</t>
         </is>
       </c>
-      <c r="D180" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E180" s="43" t="n">
+      <c r="D181" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E181" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="F180" s="43" t="n">
+      <c r="F181" s="43" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="44" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="44" t="inlineStr">
         <is>
           <t>Naime Cristina Freitas</t>
         </is>
       </c>
-      <c r="B181" s="44" t="inlineStr">
+      <c r="B182" s="44" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C181" s="44" t="inlineStr">
+      <c r="C182" s="44" t="inlineStr">
         <is>
           <t>Dia sem bater a meta diária</t>
         </is>
       </c>
-      <c r="D181" s="44" t="n">
+      <c r="D182" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="E181" s="44" t="n">
+      <c r="E182" s="44" t="n">
         <v>0.5</v>
       </c>
-      <c r="F181" s="44" t="n">
+      <c r="F182" s="44" t="n">
         <v>-2</v>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="43" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="43" t="inlineStr">
         <is>
           <t>Rafael Ramos Recalde</t>
         </is>
       </c>
-      <c r="B182" s="43" t="inlineStr">
+      <c r="B183" s="43" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C182" s="43" t="inlineStr">
+      <c r="C183" s="43" t="inlineStr">
         <is>
           <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
-      <c r="D182" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E182" s="43" t="n">
+      <c r="D183" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E183" s="43" t="n">
         <v>5</v>
       </c>
-      <c r="F182" s="43" t="n">
+      <c r="F183" s="43" t="n">
         <v>5</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="44" t="inlineStr">
-        <is>
-          <t>Rafael Ramos Recalde</t>
-        </is>
-      </c>
-      <c r="B183" s="44" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C183" s="44" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D183" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E183" s="44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F183" s="44" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="184">
@@ -11655,17 +11779,17 @@
       </c>
       <c r="C184" s="44" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D184" s="44" t="n">
         <v>1</v>
       </c>
       <c r="E184" s="44" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F184" s="44" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="185">
@@ -11681,7 +11805,7 @@
       </c>
       <c r="C185" s="44" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D185" s="44" t="n">
@@ -11707,43 +11831,43 @@
       </c>
       <c r="C186" s="44" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D186" s="44" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E186" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="F186" s="44" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="44" t="inlineStr">
+        <is>
+          <t>Rafael Ramos Recalde</t>
+        </is>
+      </c>
+      <c r="B187" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C187" s="44" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D187" s="44" t="n">
+        <v>7</v>
+      </c>
+      <c r="E187" s="44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F187" s="44" t="n">
         <v>-4.2</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="43" t="inlineStr">
-        <is>
-          <t>Ramona dos Santos Oliveira</t>
-        </is>
-      </c>
-      <c r="B187" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C187" s="43" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D187" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E187" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="F187" s="43" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="188">
@@ -11759,43 +11883,43 @@
       </c>
       <c r="C188" s="43" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D188" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E188" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F188" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="43" t="inlineStr">
+        <is>
+          <t>Ramona dos Santos Oliveira</t>
+        </is>
+      </c>
+      <c r="B189" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C189" s="43" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D188" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E188" s="43" t="n">
+      <c r="D189" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E189" s="43" t="n">
         <v>0.5</v>
       </c>
-      <c r="F188" s="43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="44" t="inlineStr">
-        <is>
-          <t>Ramona dos Santos Oliveira</t>
-        </is>
-      </c>
-      <c r="B189" s="44" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C189" s="44" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D189" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="E189" s="44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F189" s="44" t="n">
-        <v>-2</v>
+      <c r="F189" s="43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="190">
@@ -11811,17 +11935,17 @@
       </c>
       <c r="C190" s="44" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D190" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E190" s="44" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F190" s="44" t="n">
-        <v>-0.6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="191">
@@ -11837,7 +11961,7 @@
       </c>
       <c r="C191" s="44" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D191" s="44" t="n">
@@ -11863,17 +11987,17 @@
       </c>
       <c r="C192" s="44" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D192" s="44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E192" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="F192" s="44" t="n">
-        <v>-1.8</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="193">
@@ -11889,43 +12013,43 @@
       </c>
       <c r="C193" s="44" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D193" s="44" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="E193" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="F193" s="44" t="n">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="44" t="inlineStr">
+        <is>
+          <t>Ramona dos Santos Oliveira</t>
+        </is>
+      </c>
+      <c r="B194" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C194" s="44" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D194" s="44" t="n">
+        <v>22</v>
+      </c>
+      <c r="E194" s="44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F194" s="44" t="n">
         <v>-13.2</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="43" t="inlineStr">
-        <is>
-          <t>Raquel Ortiz dos Santos</t>
-        </is>
-      </c>
-      <c r="B194" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C194" s="43" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D194" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E194" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="F194" s="43" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="195">
@@ -11941,43 +12065,43 @@
       </c>
       <c r="C195" s="43" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D195" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E195" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F195" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="43" t="inlineStr">
+        <is>
+          <t>Raquel Ortiz dos Santos</t>
+        </is>
+      </c>
+      <c r="B196" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C196" s="43" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D195" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E195" s="43" t="n">
+      <c r="D196" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E196" s="43" t="n">
         <v>0.5</v>
       </c>
-      <c r="F195" s="43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="44" t="inlineStr">
-        <is>
-          <t>Raquel Ortiz dos Santos</t>
-        </is>
-      </c>
-      <c r="B196" s="44" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C196" s="44" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D196" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="E196" s="44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F196" s="44" t="n">
-        <v>-2</v>
+      <c r="F196" s="43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="197">
@@ -11993,17 +12117,17 @@
       </c>
       <c r="C197" s="44" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D197" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E197" s="44" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F197" s="44" t="n">
-        <v>-0.6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="198">
@@ -12019,7 +12143,7 @@
       </c>
       <c r="C198" s="44" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D198" s="44" t="n">
@@ -12045,7 +12169,7 @@
       </c>
       <c r="C199" s="44" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D199" s="44" t="n">
@@ -12071,43 +12195,43 @@
       </c>
       <c r="C200" s="44" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D200" s="44" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E200" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="F200" s="44" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="44" t="inlineStr">
+        <is>
+          <t>Raquel Ortiz dos Santos</t>
+        </is>
+      </c>
+      <c r="B201" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C201" s="44" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D201" s="44" t="n">
+        <v>17</v>
+      </c>
+      <c r="E201" s="44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F201" s="44" t="n">
         <v>-10.2</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="43" t="inlineStr">
-        <is>
-          <t>Rosalina Beniel Vargas</t>
-        </is>
-      </c>
-      <c r="B201" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C201" s="43" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D201" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E201" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="F201" s="43" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="202">
@@ -12123,7 +12247,7 @@
       </c>
       <c r="C202" s="43" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D202" s="43" t="n">
@@ -12149,17 +12273,17 @@
       </c>
       <c r="C203" s="43" t="inlineStr">
         <is>
-          <t>Bônus: pontualidade perfeita no período</t>
+          <t>Bônus: nenhuma visita rápida no período</t>
         </is>
       </c>
       <c r="D203" s="43" t="n">
         <v>1</v>
       </c>
       <c r="E203" s="43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F203" s="43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="204">
@@ -12175,69 +12299,69 @@
       </c>
       <c r="C204" s="43" t="inlineStr">
         <is>
+          <t>Bônus: pontualidade perfeita no período</t>
+        </is>
+      </c>
+      <c r="D204" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E204" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="F204" s="43" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="43" t="inlineStr">
+        <is>
+          <t>Rosalina Beniel Vargas</t>
+        </is>
+      </c>
+      <c r="B205" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C205" s="43" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D204" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E204" s="43" t="n">
+      <c r="D205" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E205" s="43" t="n">
         <v>0.5</v>
       </c>
-      <c r="F204" s="43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="44" t="inlineStr">
+      <c r="F205" s="43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="44" t="inlineStr">
         <is>
           <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
-      <c r="B205" s="44" t="inlineStr">
+      <c r="B206" s="44" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C205" s="44" t="inlineStr">
+      <c r="C206" s="44" t="inlineStr">
         <is>
           <t>Dia sem bater a meta diária</t>
         </is>
       </c>
-      <c r="D205" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E205" s="44" t="n">
+      <c r="D206" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E206" s="44" t="n">
         <v>0.5</v>
       </c>
-      <c r="F205" s="44" t="n">
+      <c r="F206" s="44" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="43" t="inlineStr">
-        <is>
-          <t>Rozana Reis da Silva</t>
-        </is>
-      </c>
-      <c r="B206" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C206" s="43" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D206" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E206" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="F206" s="43" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="207">
@@ -12253,43 +12377,43 @@
       </c>
       <c r="C207" s="43" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D207" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E207" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F207" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="43" t="inlineStr">
+        <is>
+          <t>Rozana Reis da Silva</t>
+        </is>
+      </c>
+      <c r="B208" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C208" s="43" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D207" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E207" s="43" t="n">
+      <c r="D208" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E208" s="43" t="n">
         <v>0.5</v>
       </c>
-      <c r="F207" s="43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="44" t="inlineStr">
-        <is>
-          <t>Rozana Reis da Silva</t>
-        </is>
-      </c>
-      <c r="B208" s="44" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C208" s="44" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D208" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E208" s="44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F208" s="44" t="n">
-        <v>-1</v>
+      <c r="F208" s="43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="209">
@@ -12305,17 +12429,17 @@
       </c>
       <c r="C209" s="44" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D209" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E209" s="44" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F209" s="44" t="n">
-        <v>-1.2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="210">
@@ -12331,17 +12455,17 @@
       </c>
       <c r="C210" s="44" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D210" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E210" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="F210" s="44" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="211">
@@ -12357,43 +12481,43 @@
       </c>
       <c r="C211" s="44" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D211" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E211" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="F211" s="44" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="44" t="inlineStr">
+        <is>
+          <t>Rozana Reis da Silva</t>
+        </is>
+      </c>
+      <c r="B212" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C212" s="44" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D212" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="E212" s="44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F212" s="44" t="n">
         <v>-1.2</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="43" t="inlineStr">
-        <is>
-          <t>Rozentina Matos de Oliveira</t>
-        </is>
-      </c>
-      <c r="B212" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C212" s="43" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D212" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E212" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="F212" s="43" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="213">
@@ -12409,7 +12533,7 @@
       </c>
       <c r="C213" s="43" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D213" s="43" t="n">
@@ -12435,43 +12559,43 @@
       </c>
       <c r="C214" s="43" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D214" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E214" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F214" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="43" t="inlineStr">
+        <is>
+          <t>Rozentina Matos de Oliveira</t>
+        </is>
+      </c>
+      <c r="B215" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C215" s="43" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D214" s="43" t="n">
+      <c r="D215" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="E214" s="43" t="n">
+      <c r="E215" s="43" t="n">
         <v>0.5</v>
       </c>
-      <c r="F214" s="43" t="n">
+      <c r="F215" s="43" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="44" t="inlineStr">
-        <is>
-          <t>Rozentina Matos de Oliveira</t>
-        </is>
-      </c>
-      <c r="B215" s="44" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C215" s="44" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D215" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="E215" s="44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F215" s="44" t="n">
-        <v>-2</v>
       </c>
     </row>
     <row r="216">
@@ -12487,17 +12611,17 @@
       </c>
       <c r="C216" s="44" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D216" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E216" s="44" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F216" s="44" t="n">
-        <v>-0.6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="217">
@@ -12513,7 +12637,7 @@
       </c>
       <c r="C217" s="44" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D217" s="44" t="n">
@@ -12539,7 +12663,7 @@
       </c>
       <c r="C218" s="44" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D218" s="44" t="n">
@@ -12553,29 +12677,29 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="43" t="inlineStr">
-        <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
-        </is>
-      </c>
-      <c r="B219" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C219" s="43" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D219" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E219" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="F219" s="43" t="n">
-        <v>5</v>
+      <c r="A219" s="44" t="inlineStr">
+        <is>
+          <t>Rozentina Matos de Oliveira</t>
+        </is>
+      </c>
+      <c r="B219" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C219" s="44" t="inlineStr">
+        <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D219" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E219" s="44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F219" s="44" t="n">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="220">
@@ -12591,7 +12715,7 @@
       </c>
       <c r="C220" s="43" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D220" s="43" t="n">
@@ -12605,29 +12729,29 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="44" t="inlineStr">
+      <c r="A221" s="43" t="inlineStr">
         <is>
           <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
-      <c r="B221" s="44" t="inlineStr">
+      <c r="B221" s="43" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C221" s="44" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D221" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E221" s="44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F221" s="44" t="n">
-        <v>-1</v>
+      <c r="C221" s="43" t="inlineStr">
+        <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D221" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E221" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F221" s="43" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="222">
@@ -12643,43 +12767,43 @@
       </c>
       <c r="C222" s="44" t="inlineStr">
         <is>
+          <t>Dia sem bater a meta diária</t>
+        </is>
+      </c>
+      <c r="D222" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E222" s="44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F222" s="44" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="44" t="inlineStr">
+        <is>
+          <t>Sara Eliane Talaveira de Oliveira</t>
+        </is>
+      </c>
+      <c r="B223" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C223" s="44" t="inlineStr">
+        <is>
           <t>Início manhã após 08h30</t>
         </is>
       </c>
-      <c r="D222" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E222" s="44" t="n">
+      <c r="D223" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E223" s="44" t="n">
         <v>0.3</v>
       </c>
-      <c r="F222" s="44" t="n">
+      <c r="F223" s="44" t="n">
         <v>-0.6</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="43" t="inlineStr">
-        <is>
-          <t>Selba Ramona Afonso</t>
-        </is>
-      </c>
-      <c r="B223" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C223" s="43" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D223" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E223" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="F223" s="43" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="224">
@@ -12695,7 +12819,7 @@
       </c>
       <c r="C224" s="43" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D224" s="43" t="n">
@@ -12721,43 +12845,43 @@
       </c>
       <c r="C225" s="43" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D225" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E225" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F225" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="43" t="inlineStr">
+        <is>
+          <t>Selba Ramona Afonso</t>
+        </is>
+      </c>
+      <c r="B226" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C226" s="43" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D225" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E225" s="43" t="n">
+      <c r="D226" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E226" s="43" t="n">
         <v>0.5</v>
       </c>
-      <c r="F225" s="43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="44" t="inlineStr">
-        <is>
-          <t>Selba Ramona Afonso</t>
-        </is>
-      </c>
-      <c r="B226" s="44" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C226" s="44" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D226" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E226" s="44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F226" s="44" t="n">
-        <v>-1</v>
+      <c r="F226" s="43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="227">
@@ -12773,43 +12897,43 @@
       </c>
       <c r="C227" s="44" t="inlineStr">
         <is>
+          <t>Dia sem bater a meta diária</t>
+        </is>
+      </c>
+      <c r="D227" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E227" s="44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F227" s="44" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="44" t="inlineStr">
+        <is>
+          <t>Selba Ramona Afonso</t>
+        </is>
+      </c>
+      <c r="B228" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C228" s="44" t="inlineStr">
+        <is>
           <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
-      <c r="D227" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E227" s="44" t="n">
+      <c r="D228" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E228" s="44" t="n">
         <v>0.3</v>
       </c>
-      <c r="F227" s="44" t="n">
+      <c r="F228" s="44" t="n">
         <v>-0.6</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="43" t="inlineStr">
-        <is>
-          <t>Silvina Regina de Souza Valiente</t>
-        </is>
-      </c>
-      <c r="B228" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C228" s="43" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D228" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E228" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="F228" s="43" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="229">
@@ -12825,7 +12949,7 @@
       </c>
       <c r="C229" s="43" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D229" s="43" t="n">
@@ -12851,43 +12975,43 @@
       </c>
       <c r="C230" s="43" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D230" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E230" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F230" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="43" t="inlineStr">
+        <is>
+          <t>Silvina Regina de Souza Valiente</t>
+        </is>
+      </c>
+      <c r="B231" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C231" s="43" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D230" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E230" s="43" t="n">
+      <c r="D231" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E231" s="43" t="n">
         <v>0.5</v>
       </c>
-      <c r="F230" s="43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="44" t="inlineStr">
-        <is>
-          <t>Silvina Regina de Souza Valiente</t>
-        </is>
-      </c>
-      <c r="B231" s="44" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C231" s="44" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D231" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="E231" s="44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F231" s="44" t="n">
-        <v>-2</v>
+      <c r="F231" s="43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="232">
@@ -12903,17 +13027,17 @@
       </c>
       <c r="C232" s="44" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D232" s="44" t="n">
         <v>2</v>
       </c>
       <c r="E232" s="44" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F232" s="44" t="n">
-        <v>-1.2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="233">
@@ -12929,43 +13053,43 @@
       </c>
       <c r="C233" s="44" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D233" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E233" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="F233" s="44" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="44" t="inlineStr">
+        <is>
+          <t>Silvina Regina de Souza Valiente</t>
+        </is>
+      </c>
+      <c r="B234" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C234" s="44" t="inlineStr">
+        <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D234" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E234" s="44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F234" s="44" t="n">
         <v>-0.6</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="43" t="inlineStr">
-        <is>
-          <t>Suely Aguiar Alves Luiz</t>
-        </is>
-      </c>
-      <c r="B234" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C234" s="43" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D234" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E234" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="F234" s="43" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="235">
@@ -12981,7 +13105,7 @@
       </c>
       <c r="C235" s="43" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D235" s="43" t="n">
@@ -13007,69 +13131,69 @@
       </c>
       <c r="C236" s="43" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D236" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E236" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F236" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="43" t="inlineStr">
+        <is>
+          <t>Suely Aguiar Alves Luiz</t>
+        </is>
+      </c>
+      <c r="B237" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C237" s="43" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D236" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E236" s="43" t="n">
+      <c r="D237" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E237" s="43" t="n">
         <v>0.5</v>
       </c>
-      <c r="F236" s="43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="44" t="inlineStr">
+      <c r="F237" s="43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="44" t="inlineStr">
         <is>
           <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
-      <c r="B237" s="44" t="inlineStr">
+      <c r="B238" s="44" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C237" s="44" t="inlineStr">
+      <c r="C238" s="44" t="inlineStr">
         <is>
           <t>Início manhã após 08h30</t>
         </is>
       </c>
-      <c r="D237" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E237" s="44" t="n">
+      <c r="D238" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E238" s="44" t="n">
         <v>0.3</v>
       </c>
-      <c r="F237" s="44" t="n">
+      <c r="F238" s="44" t="n">
         <v>-0.6</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="43" t="inlineStr">
-        <is>
-          <t>Tania Maria Montania</t>
-        </is>
-      </c>
-      <c r="B238" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C238" s="43" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D238" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E238" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="F238" s="43" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="239">
@@ -13085,7 +13209,7 @@
       </c>
       <c r="C239" s="43" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D239" s="43" t="n">
@@ -13111,43 +13235,43 @@
       </c>
       <c r="C240" s="43" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D240" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E240" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F240" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="43" t="inlineStr">
+        <is>
+          <t>Tania Maria Montania</t>
+        </is>
+      </c>
+      <c r="B241" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C241" s="43" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D240" s="43" t="n">
+      <c r="D241" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="E240" s="43" t="n">
+      <c r="E241" s="43" t="n">
         <v>0.5</v>
       </c>
-      <c r="F240" s="43" t="n">
+      <c r="F241" s="43" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="44" t="inlineStr">
-        <is>
-          <t>Tania Maria Montania</t>
-        </is>
-      </c>
-      <c r="B241" s="44" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C241" s="44" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D241" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E241" s="44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F241" s="44" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="242">
@@ -13163,17 +13287,17 @@
       </c>
       <c r="C242" s="44" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D242" s="44" t="n">
         <v>1</v>
       </c>
       <c r="E242" s="44" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F242" s="44" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="243">
@@ -13189,7 +13313,7 @@
       </c>
       <c r="C243" s="44" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D243" s="44" t="n">
@@ -13203,29 +13327,29 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="43" t="inlineStr">
-        <is>
-          <t>Wagner Tarlei Gomes</t>
-        </is>
-      </c>
-      <c r="B244" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C244" s="43" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D244" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E244" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="F244" s="43" t="n">
-        <v>5</v>
+      <c r="A244" s="44" t="inlineStr">
+        <is>
+          <t>Tania Maria Montania</t>
+        </is>
+      </c>
+      <c r="B244" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C244" s="44" t="inlineStr">
+        <is>
+          <t>Início manhã após 08h30</t>
+        </is>
+      </c>
+      <c r="D244" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E244" s="44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F244" s="44" t="n">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="245">
@@ -13241,43 +13365,43 @@
       </c>
       <c r="C245" s="43" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D245" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E245" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F245" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="43" t="inlineStr">
+        <is>
+          <t>Wagner Tarlei Gomes</t>
+        </is>
+      </c>
+      <c r="B246" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C246" s="43" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D245" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E245" s="43" t="n">
+      <c r="D246" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E246" s="43" t="n">
         <v>0.5</v>
       </c>
-      <c r="F245" s="43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="44" t="inlineStr">
-        <is>
-          <t>Wagner Tarlei Gomes</t>
-        </is>
-      </c>
-      <c r="B246" s="44" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C246" s="44" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D246" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E246" s="44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F246" s="44" t="n">
-        <v>-1</v>
+      <c r="F246" s="43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="247">
@@ -13293,17 +13417,17 @@
       </c>
       <c r="C247" s="44" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D247" s="44" t="n">
         <v>1</v>
       </c>
       <c r="E247" s="44" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F247" s="44" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="248">
@@ -13319,7 +13443,7 @@
       </c>
       <c r="C248" s="44" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D248" s="44" t="n">
@@ -13345,7 +13469,7 @@
       </c>
       <c r="C249" s="44" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D249" s="44" t="n">
@@ -13371,59 +13495,59 @@
       </c>
       <c r="C250" s="44" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D250" s="44" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E250" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="F250" s="44" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="44" t="inlineStr">
+        <is>
+          <t>Wagner Tarlei Gomes</t>
+        </is>
+      </c>
+      <c r="B251" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C251" s="44" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D251" s="44" t="n">
+        <v>8</v>
+      </c>
+      <c r="E251" s="44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F251" s="44" t="n">
         <v>-4.8</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="43" t="inlineStr">
-        <is>
-          <t>Wesley de Souza Leal</t>
-        </is>
-      </c>
-      <c r="B251" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C251" s="43" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D251" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E251" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="F251" s="43" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="43" t="inlineStr">
         <is>
-          <t>Wesley de Souza Leal</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="B252" s="43" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C252" s="43" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D252" s="43" t="n">
@@ -13439,12 +13563,12 @@
     <row r="253">
       <c r="A253" s="44" t="inlineStr">
         <is>
-          <t>Wesley de Souza Leal</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="B253" s="44" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C253" s="44" t="inlineStr">
@@ -13465,17 +13589,17 @@
     <row r="254">
       <c r="A254" s="44" t="inlineStr">
         <is>
-          <t>Wesley de Souza Leal</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="B254" s="44" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C254" s="44" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D254" s="44" t="n">
@@ -13489,35 +13613,35 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="43" t="inlineStr">
-        <is>
-          <t>William Anderson Chamorro Tavares</t>
-        </is>
-      </c>
-      <c r="B255" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C255" s="43" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D255" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E255" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="F255" s="43" t="n">
-        <v>5</v>
+      <c r="A255" s="44" t="inlineStr">
+        <is>
+          <t>Walquiria Araujo Flores</t>
+        </is>
+      </c>
+      <c r="B255" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C255" s="44" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D255" s="44" t="n">
+        <v>4</v>
+      </c>
+      <c r="E255" s="44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F255" s="44" t="n">
+        <v>-2.4</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="43" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Wesley de Souza Leal</t>
         </is>
       </c>
       <c r="B256" s="43" t="inlineStr">
@@ -13527,7 +13651,7 @@
       </c>
       <c r="C256" s="43" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D256" s="43" t="n">
@@ -13541,35 +13665,35 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="44" t="inlineStr">
-        <is>
-          <t>William Anderson Chamorro Tavares</t>
-        </is>
-      </c>
-      <c r="B257" s="44" t="inlineStr">
+      <c r="A257" s="43" t="inlineStr">
+        <is>
+          <t>Wesley de Souza Leal</t>
+        </is>
+      </c>
+      <c r="B257" s="43" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C257" s="44" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D257" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="E257" s="44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F257" s="44" t="n">
-        <v>-2</v>
+      <c r="C257" s="43" t="inlineStr">
+        <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D257" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E257" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F257" s="43" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="44" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Wesley de Souza Leal</t>
         </is>
       </c>
       <c r="B258" s="44" t="inlineStr">
@@ -13579,23 +13703,23 @@
       </c>
       <c r="C258" s="44" t="inlineStr">
         <is>
-          <t>Fim manhã antes de 10h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D258" s="44" t="n">
         <v>1</v>
       </c>
       <c r="E258" s="44" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F258" s="44" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="44" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Wesley de Souza Leal</t>
         </is>
       </c>
       <c r="B259" s="44" t="inlineStr">
@@ -13605,50 +13729,180 @@
       </c>
       <c r="C259" s="44" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D259" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E259" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="F259" s="44" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="43" t="inlineStr">
+        <is>
+          <t>William Anderson Chamorro Tavares</t>
+        </is>
+      </c>
+      <c r="B260" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C260" s="43" t="inlineStr">
+        <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D260" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E260" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F260" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="43" t="inlineStr">
+        <is>
+          <t>William Anderson Chamorro Tavares</t>
+        </is>
+      </c>
+      <c r="B261" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C261" s="43" t="inlineStr">
+        <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D261" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E261" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F261" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="44" t="inlineStr">
+        <is>
+          <t>William Anderson Chamorro Tavares</t>
+        </is>
+      </c>
+      <c r="B262" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C262" s="44" t="inlineStr">
+        <is>
+          <t>Dia sem bater a meta diária</t>
+        </is>
+      </c>
+      <c r="D262" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="E262" s="44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F262" s="44" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="44" t="inlineStr">
+        <is>
+          <t>William Anderson Chamorro Tavares</t>
+        </is>
+      </c>
+      <c r="B263" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C263" s="44" t="inlineStr">
+        <is>
+          <t>Fim manhã antes de 10h00</t>
+        </is>
+      </c>
+      <c r="D263" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E263" s="44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F263" s="44" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="44" t="inlineStr">
+        <is>
+          <t>William Anderson Chamorro Tavares</t>
+        </is>
+      </c>
+      <c r="B264" s="44" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C264" s="44" t="inlineStr">
+        <is>
+          <t>Início manhã após 08h30</t>
+        </is>
+      </c>
+      <c r="D264" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="E264" s="44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F264" s="44" t="n">
         <v>-1.2</v>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" s="44" t="inlineStr">
+    <row r="265">
+      <c r="A265" s="44" t="inlineStr">
         <is>
           <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
-      <c r="B260" s="44" t="inlineStr">
+      <c r="B265" s="44" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C260" s="44" t="inlineStr">
+      <c r="C265" s="44" t="inlineStr">
         <is>
           <t>Início tarde após 14h30</t>
         </is>
       </c>
-      <c r="D260" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E260" s="44" t="n">
+      <c r="D265" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E265" s="44" t="n">
         <v>0.3</v>
       </c>
-      <c r="F260" s="44" t="n">
+      <c r="F265" s="44" t="n">
         <v>-0.6</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:E40"/>
+  <autoFilter ref="A2:E41"/>
   <mergeCells count="2">
+    <mergeCell ref="A44:F44"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A43:F43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13660,7 +13914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -15215,13 +15469,13 @@
         <v>0</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L29" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>62.5</v>
+        <v>62.18</v>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
@@ -15823,123 +16077,177 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="7" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Walquiria Araujo Flores</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>440 - JARDIM IBIRAPUERA</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Q024</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>21.05</v>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="5" t="n">
+        <v>17.39</v>
+      </c>
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t>🔴 CRÍTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>LEGENDA — CLASSIFICAÇÃO (baseada em % de Visitas Rápidas)</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>🟢 NORMAL</t>
         </is>
       </c>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>% Rápidas até 10%</t>
         </is>
       </c>
-      <c r="C44" s="10" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+      <c r="C45" s="10" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>🟡 ATENÇÃO</t>
         </is>
       </c>
-      <c r="B45" s="9" t="inlineStr">
+      <c r="B46" s="9" t="inlineStr">
         <is>
           <t>% Rápidas entre 11% e 20%</t>
         </is>
       </c>
-      <c r="C45" s="10" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="12" t="inlineStr">
+      <c r="C46" s="10" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
       </c>
-      <c r="B46" s="9" t="inlineStr">
+      <c r="B47" s="9" t="inlineStr">
         <is>
           <t>% Rápidas acima de 20%</t>
         </is>
       </c>
-      <c r="C46" s="10" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="13" t="inlineStr">
+      <c r="C47" s="10" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="13" t="inlineStr">
         <is>
           <t>⚠️ SEQUÊNCIA SUSPEITA</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="45" customHeight="1">
-      <c r="A49" s="14" t="inlineStr">
+    <row r="50" ht="45" customHeight="1">
+      <c r="A50" s="14" t="inlineStr">
         <is>
           <t>Duas ou mais visitas consecutivas do mesmo agente registradas no MESMO MINUTO de chegada são marcadas como suspeitas (o e-Visita não registra segundos, então o critério de negócio de 50s de diferença equivale, na prática, a 'mesmo minuto') — sugere lançamento em lote no sistema, não visita real de campo. Colunas: 'Visitas em Sequência Suspeita' (total de visitas envolvidas) e 'Maior Sequência Suspeita' (maior número de visitas seguidas nessa condição). Na aba 'Visitas Suspeitas', a coluna 'Diferença p/ Anterior (s)*' fica em branco quando o alerta da linha veio do par com a visita SEGUINTE (não da anterior).</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="15" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="15" t="inlineStr">
         <is>
           <t>🍽️ VISITAS NO HORÁRIO DE ALMOÇO</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="70" customHeight="1">
-      <c r="A52" s="14" t="inlineStr">
+    <row r="53" ht="70" customHeight="1">
+      <c r="A53" s="14" t="inlineStr">
         <is>
           <t>Coluna 'Visitas no Almoço (11h15-12h45)' conta as visitas com chegada registrada nesse intervalo — o horário oficial de almoço é 11h15 às 12h45, JÁ COM 15 MINUTOS DE TOLERÂNCIA em cada borda (visitas entre 11h-11h15 ou 12h45-13h não são tratadas como violação, só como 'fora do expediente' genérico) — use para checar se o agente está trabalhando no horário de almoço ou se há erro de lançamento. Essas visitas ficam de fora do cálculo de 'Início/Fim Manhã' e 'Início/Fim Tarde', que usam a primeira chegada e a última saída de cada dia (não a média de todos os horários), para refletir melhor o início e o fim reais do expediente.</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="16" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="16" t="inlineStr">
         <is>
           <t>💰 HORAS TRABALHADAS, HORAS ÚTEIS E CUSTO DA HORA ÚTIL</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" s="14" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" s="14" t="inlineStr">
         <is>
           <t>'Horas Trabalhadas' = jornada total do dia (primeira chegada até a última saída), descontando a sobreposição com o horário de almoço — depois tira-se a média entre os dias/semanas trabalhados, 'Horas Úteis' = soma das durações de visita no dia (tempo realmente dentro de imóveis), sem contar deslocamento entre visitas, 'Custo Hora Útil' = salário mensal do agente (R$ 4863,00, equivalente a 3 salários mínimos federais) dividido pelas horas úteis mensais estimadas (Média Horas Úteis/Dia × 22 dias úteis/mês). Quanto menos tempo o agente passa efetivamente em visita por dia, mais caro fica o custo por hora útil.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="17" t="inlineStr">
-        <is>
-          <t>ℹ️ A lista detalhada de visitas duplicadas (com endereço) está na aba 'Visitas Duplicadas' — use-a para localizar e excluir os registros repetidos.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="17" t="inlineStr">
         <is>
+          <t>ℹ️ A lista detalhada de visitas duplicadas (com endereço) está na aba 'Visitas Duplicadas' — use-a para localizar e excluir os registros repetidos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="17" t="inlineStr">
+        <is>
           <t>ℹ️ Visitas com duração NEGATIVA (saída antes da chegada — provável bug do sistema) foram excluídas do cálculo de Média/Mediana e estão detalhadas na aba 'Visitas Negativas', para investigação junto ao suporte do e-Visita.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:N40"/>
+  <autoFilter ref="A2:N41"/>
   <mergeCells count="13">
-    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B47:C47"/>
     <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A44:C44"/>
     <mergeCell ref="A58:C58"/>
     <mergeCell ref="B45:C45"/>
     <mergeCell ref="B46:C46"/>
-    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A53:C53"/>
     <mergeCell ref="A55:C55"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A59:C59"/>
     <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A51:C51"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16842,7 +17150,7 @@
       </c>
       <c r="C7" s="26" t="inlineStr">
         <is>
-          <t>16783019</t>
+          <t>16762591</t>
         </is>
       </c>
       <c r="D7" s="25" t="inlineStr">
@@ -16852,27 +17160,27 @@
       </c>
       <c r="E7" s="25" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q027</t>
         </is>
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>Rua MONTEVIDEO</t>
+          <t>Rua ROBERTO BUENO DA SILVA</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>301 - R</t>
+          <t>486 - OU</t>
         </is>
       </c>
       <c r="H7" s="25" t="inlineStr">
         <is>
-          <t>06/08/2026 16:07</t>
+          <t>05/08/2026 08:45</t>
         </is>
       </c>
       <c r="I7" s="25" t="inlineStr">
         <is>
-          <t>06/08/2026 16:27</t>
+          <t>05/08/2026 09:05</t>
         </is>
       </c>
       <c r="J7" s="25" t="n">
@@ -16892,7 +17200,7 @@
       </c>
       <c r="C8" s="26" t="inlineStr">
         <is>
-          <t>16762591</t>
+          <t>16783019</t>
         </is>
       </c>
       <c r="D8" s="25" t="inlineStr">
@@ -16902,27 +17210,27 @@
       </c>
       <c r="E8" s="25" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q029</t>
         </is>
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>Rua ROBERTO BUENO DA SILVA</t>
+          <t>Rua MONTEVIDEO</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>486 - OU</t>
+          <t>301 - R</t>
         </is>
       </c>
       <c r="H8" s="25" t="inlineStr">
         <is>
-          <t>05/08/2026 08:45</t>
+          <t>06/08/2026 16:07</t>
         </is>
       </c>
       <c r="I8" s="25" t="inlineStr">
         <is>
-          <t>05/08/2026 09:05</t>
+          <t>06/08/2026 16:27</t>
         </is>
       </c>
       <c r="J8" s="25" t="n">

--- a/data/historico/semana_318.xlsx
+++ b/data/historico/semana_318.xlsx
@@ -31,7 +31,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$E$41</definedName>
   </definedNames>
@@ -5098,7 +5098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5110,7 +5110,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (4 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
+          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (3 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5162,41 +5162,41 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="35" t="inlineStr">
-        <is>
-          <t>23/07/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="35" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="C4" s="35" t="inlineStr">
-        <is>
-          <t>Férias/Atestado (automático)</t>
-        </is>
-      </c>
-      <c r="D4" s="35" t="inlineStr">
-        <is>
-          <t>Agente_3035</t>
+      <c r="A4" s="36" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="36" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="C4" s="36" t="inlineStr">
+        <is>
+          <t>Levantamento de Índice</t>
+        </is>
+      </c>
+      <c r="D4" s="36" t="inlineStr">
+        <is>
+          <t>Todos os agentes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="36" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="B5" s="36" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="C5" s="36" t="inlineStr">
         <is>
-          <t>Levantamento de Índice</t>
+          <t>Instalação de Ovitrampa</t>
         </is>
       </c>
       <c r="D5" s="36" t="inlineStr">
@@ -5205,30 +5205,8 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="36" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="36" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="C6" s="36" t="inlineStr">
-        <is>
-          <t>Instalação de Ovitrampa</t>
-        </is>
-      </c>
-      <c r="D6" s="36" t="inlineStr">
-        <is>
-          <t>Todos os agentes</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:D6"/>
+  <autoFilter ref="A2:D5"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>

--- a/data/historico/semana_318.xlsx
+++ b/data/historico/semana_318.xlsx
@@ -31,7 +31,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$E$41</definedName>
   </definedNames>
@@ -5106,19 +5106,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (29 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
+          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (11 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="C7" s="35" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="C8" s="35" t="inlineStr">
@@ -5341,41 +5341,41 @@
       </c>
       <c r="D11" s="37" t="inlineStr">
         <is>
-          <t>Wesley de Souza Leal</t>
+          <t>Equipe 2</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="37" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="37" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="C12" s="37" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D12" s="37" t="inlineStr">
-        <is>
-          <t>Fabiana de Figueredo Vieira</t>
+      <c r="A12" s="36" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="36" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="C12" s="36" t="inlineStr">
+        <is>
+          <t>Instalação de Ovitrampa</t>
+        </is>
+      </c>
+      <c r="D12" s="36" t="inlineStr">
+        <is>
+          <t>Todos os agentes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="37" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="B13" s="37" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="C13" s="37" t="inlineStr">
@@ -5385,408 +5385,12 @@
       </c>
       <c r="D13" s="37" t="inlineStr">
         <is>
-          <t>Cicero Isrrael Sanabria</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="37" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="37" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="C14" s="37" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D14" s="37" t="inlineStr">
-        <is>
-          <t>Tania Maria Montania</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="37" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="37" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="C15" s="37" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D15" s="37" t="inlineStr">
-        <is>
-          <t>William Anderson Chamorro Tavares</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="37" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="37" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="C16" s="37" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D16" s="37" t="inlineStr">
-        <is>
-          <t>Gilmar Bitencourt Luiz</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="37" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="37" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="C17" s="37" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D17" s="37" t="inlineStr">
-        <is>
-          <t>Suely Aguiar Alves Luiz</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="37" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="37" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="C18" s="37" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D18" s="37" t="inlineStr">
-        <is>
-          <t>Mateus Falcao de Souza</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="37" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="37" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="C19" s="37" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D19" s="37" t="inlineStr">
-        <is>
-          <t>Bianca Afonso Narbaez</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="37" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="37" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="C20" s="37" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D20" s="37" t="inlineStr">
-        <is>
-          <t>Gisele Olimpia Torres</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="36" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="36" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="C21" s="36" t="inlineStr">
-        <is>
-          <t>Instalação de Ovitrampa</t>
-        </is>
-      </c>
-      <c r="D21" s="36" t="inlineStr">
-        <is>
-          <t>Todos os agentes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="37" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="37" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="C22" s="37" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D22" s="37" t="inlineStr">
-        <is>
-          <t>Wesley de Souza Leal</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="37" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="37" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="C23" s="37" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D23" s="37" t="inlineStr">
-        <is>
-          <t>Fabiana de Figueredo Vieira</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="37" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="37" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="C24" s="37" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D24" s="37" t="inlineStr">
-        <is>
-          <t>Cicero Isrrael Sanabria</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="37" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="37" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="C25" s="37" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D25" s="37" t="inlineStr">
-        <is>
-          <t>Tania Maria Montania</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="37" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="37" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="C26" s="37" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D26" s="37" t="inlineStr">
-        <is>
-          <t>William Anderson Chamorro Tavares</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="37" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="37" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="C27" s="37" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D27" s="37" t="inlineStr">
-        <is>
-          <t>Gilmar Bitencourt Luiz</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="37" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="37" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="C28" s="37" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D28" s="37" t="inlineStr">
-        <is>
-          <t>Suely Aguiar Alves Luiz</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="37" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="37" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="C29" s="37" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D29" s="37" t="inlineStr">
-        <is>
-          <t>Mateus Falcao de Souza</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="37" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="37" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="C30" s="37" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D30" s="37" t="inlineStr">
-        <is>
-          <t>Bianca Afonso Narbaez</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="37" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="37" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="C31" s="37" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D31" s="37" t="inlineStr">
-        <is>
-          <t>Gisele Olimpia Torres</t>
+          <t>Equipe 2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D31"/>
+  <autoFilter ref="A2:D13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -7746,16 +7350,16 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Adriano Ricardo Thiel</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -7770,16 +7374,16 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Rosalina Beniel Vargas</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
@@ -7794,7 +7398,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Carlos Alberto Albiero</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -7803,7 +7407,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>112.2</v>
+        <v>100</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -7818,16 +7422,16 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Bianca Afonso Narbaez</t>
+          <t>Cris Milene Cardenas da Silva</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -7842,16 +7446,16 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
@@ -7866,16 +7470,16 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Tania Maria Montania</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>111.8</v>
+        <v>100</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -7890,7 +7494,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Bianca Afonso Narbaez</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -7899,7 +7503,7 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>111.4</v>
+        <v>100</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
@@ -7914,16 +7518,16 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Cicero Isrrael Sanabria</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
@@ -7938,16 +7542,16 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Cris Milene Cardenas da Silva</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>110.4</v>
+        <v>100</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
@@ -7962,16 +7566,16 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>110.4</v>
+        <v>100</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -7986,16 +7590,16 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>109.8</v>
+        <v>100</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
@@ -8010,16 +7614,16 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Geancarlos Ferreira Barrios</t>
+          <t>Tania Maria Montania</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>108.6</v>
+        <v>100</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
@@ -8043,7 +7647,7 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>108.4</v>
+        <v>100</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -8058,16 +7662,16 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>108.4</v>
+        <v>100</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
@@ -8082,16 +7686,16 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>108.4</v>
+        <v>100</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
@@ -8106,16 +7710,16 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>108.2</v>
+        <v>100</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
@@ -8130,7 +7734,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Geancarlos Ferreira Barrios</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -8139,7 +7743,7 @@
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>107.4</v>
+        <v>100</v>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
@@ -8154,16 +7758,16 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
@@ -8178,16 +7782,16 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Carlos Alberto Albiero</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>106.8</v>
+        <v>100</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -8202,16 +7806,16 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Cicero Isrrael Sanabria</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>106.2</v>
+        <v>100</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -8226,16 +7830,16 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>105.6</v>
+        <v>100</v>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
@@ -8250,16 +7854,16 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
@@ -8274,16 +7878,16 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Adriano Ricardo Thiel</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>101.4</v>
+        <v>100</v>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
@@ -8298,16 +7902,16 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>101.2</v>
+        <v>100</v>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
@@ -8322,7 +7926,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -8331,7 +7935,7 @@
         </is>
       </c>
       <c r="D27" s="4" t="n">
-        <v>101.2</v>
+        <v>100</v>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
@@ -8346,7 +7950,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -8355,7 +7959,7 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
@@ -8370,16 +7974,16 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>100.8</v>
+        <v>100</v>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
@@ -8394,16 +7998,16 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>100.4</v>
+        <v>100</v>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
@@ -8427,7 +8031,7 @@
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>100</v>
+        <v>99.5</v>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
@@ -8442,16 +8046,16 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Adriana de Jesus Saraiva</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>99.40000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
@@ -8466,7 +8070,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Adriana de Jesus Saraiva</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -8475,7 +8079,7 @@
         </is>
       </c>
       <c r="D33" s="4" t="n">
-        <v>99.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
@@ -8490,16 +8094,16 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>98.59999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
@@ -8523,7 +8127,7 @@
         </is>
       </c>
       <c r="D35" s="4" t="n">
-        <v>96.8</v>
+        <v>98.8</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -8547,7 +8151,7 @@
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>95.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
@@ -8595,7 +8199,7 @@
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>90.8</v>
+        <v>92.8</v>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
@@ -8619,7 +8223,7 @@
         </is>
       </c>
       <c r="D39" s="4" t="n">
-        <v>90.40000000000001</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
@@ -8653,25 +8257,25 @@
       <c r="F40" s="2" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="n">
+      <c r="A41" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Anderson Jose de Santana</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="D41" s="6" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>🟡 BOM</t>
+      <c r="D41" s="4" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>🟢 EXCELENTE</t>
         </is>
       </c>
       <c r="F41" s="2" t="n"/>
@@ -8785,7 +8389,7 @@
         <v>1</v>
       </c>
       <c r="F47" s="44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -8811,7 +8415,7 @@
         <v>0.5</v>
       </c>
       <c r="F48" s="45" t="n">
-        <v>-3</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="49">
@@ -8967,7 +8571,7 @@
         <v>1</v>
       </c>
       <c r="F54" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -8993,7 +8597,7 @@
         <v>0.5</v>
       </c>
       <c r="F55" s="45" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="56">
@@ -9175,7 +8779,7 @@
         <v>1</v>
       </c>
       <c r="F62" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -9201,7 +8805,7 @@
         <v>0.5</v>
       </c>
       <c r="F63" s="45" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="64">
@@ -9305,7 +8909,7 @@
         <v>1</v>
       </c>
       <c r="F67" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -9331,7 +8935,7 @@
         <v>0.5</v>
       </c>
       <c r="F68" s="45" t="n">
-        <v>-3</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="69">
@@ -9539,7 +9143,7 @@
         <v>0.5</v>
       </c>
       <c r="F76" s="45" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="77">
@@ -9617,7 +9221,7 @@
         <v>0.5</v>
       </c>
       <c r="F79" s="45" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="80">
@@ -9747,7 +9351,7 @@
         <v>0.5</v>
       </c>
       <c r="F84" s="45" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="85">
@@ -9877,7 +9481,7 @@
         <v>0.5</v>
       </c>
       <c r="F89" s="45" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="90">
@@ -9981,7 +9585,7 @@
         <v>1</v>
       </c>
       <c r="F93" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -10007,7 +9611,7 @@
         <v>0.5</v>
       </c>
       <c r="F94" s="45" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="95">
@@ -10111,7 +9715,7 @@
         <v>0.5</v>
       </c>
       <c r="F98" s="45" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="99">
@@ -10215,7 +9819,7 @@
         <v>0.5</v>
       </c>
       <c r="F102" s="45" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="103">
@@ -10423,7 +10027,7 @@
         <v>1</v>
       </c>
       <c r="F110" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -10475,7 +10079,7 @@
         <v>0.5</v>
       </c>
       <c r="F112" s="45" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="113">
@@ -10657,7 +10261,7 @@
         <v>1</v>
       </c>
       <c r="F119" s="44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
@@ -10683,7 +10287,7 @@
         <v>0.5</v>
       </c>
       <c r="F120" s="45" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="121">
@@ -10891,7 +10495,7 @@
         <v>0.5</v>
       </c>
       <c r="F128" s="45" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="129">
@@ -10969,7 +10573,7 @@
         <v>1</v>
       </c>
       <c r="F131" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -10995,7 +10599,7 @@
         <v>0.5</v>
       </c>
       <c r="F132" s="45" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="133">
@@ -11125,7 +10729,7 @@
         <v>0.5</v>
       </c>
       <c r="F137" s="45" t="n">
-        <v>-3</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="138">
@@ -11281,7 +10885,7 @@
         <v>0.5</v>
       </c>
       <c r="F143" s="45" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="144">
@@ -11437,7 +11041,7 @@
         <v>1</v>
       </c>
       <c r="F149" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -11463,7 +11067,7 @@
         <v>0.5</v>
       </c>
       <c r="F150" s="45" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="151">
@@ -11567,7 +11171,7 @@
         <v>1</v>
       </c>
       <c r="F154" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -11593,7 +11197,7 @@
         <v>0.5</v>
       </c>
       <c r="F155" s="45" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="156">
@@ -11723,7 +11327,7 @@
         <v>1</v>
       </c>
       <c r="F160" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
@@ -11749,7 +11353,7 @@
         <v>0.5</v>
       </c>
       <c r="F161" s="45" t="n">
-        <v>-3</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="162">
@@ -11905,7 +11509,7 @@
         <v>1</v>
       </c>
       <c r="F167" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168">
@@ -11931,7 +11535,7 @@
         <v>0.5</v>
       </c>
       <c r="F168" s="45" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="169">
@@ -12087,7 +11691,7 @@
         <v>1</v>
       </c>
       <c r="F174" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
@@ -12113,7 +11717,7 @@
         <v>0.5</v>
       </c>
       <c r="F175" s="45" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="176">
@@ -12295,7 +11899,7 @@
         <v>0.5</v>
       </c>
       <c r="F182" s="45" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="183">
@@ -12347,7 +11951,7 @@
         <v>0.5</v>
       </c>
       <c r="F184" s="45" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="185">
@@ -12477,7 +12081,7 @@
         <v>1</v>
       </c>
       <c r="F189" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190">
@@ -12503,7 +12107,7 @@
         <v>0.5</v>
       </c>
       <c r="F190" s="45" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="191">
@@ -12659,7 +12263,7 @@
         <v>1</v>
       </c>
       <c r="F196" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
@@ -12685,7 +12289,7 @@
         <v>0.5</v>
       </c>
       <c r="F197" s="45" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="198">
@@ -12893,7 +12497,7 @@
         <v>1</v>
       </c>
       <c r="F205" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206">
@@ -12919,7 +12523,7 @@
         <v>0.5</v>
       </c>
       <c r="F206" s="45" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="207">
@@ -12971,7 +12575,7 @@
         <v>1</v>
       </c>
       <c r="F208" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209">
@@ -12997,7 +12601,7 @@
         <v>0.5</v>
       </c>
       <c r="F209" s="45" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="210">
@@ -13153,7 +12757,7 @@
         <v>1</v>
       </c>
       <c r="F215" s="44" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="216">
@@ -13179,7 +12783,7 @@
         <v>0.5</v>
       </c>
       <c r="F216" s="45" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="217">
@@ -13335,7 +12939,7 @@
         <v>0.5</v>
       </c>
       <c r="F222" s="45" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="223">
@@ -13439,7 +13043,7 @@
         <v>1</v>
       </c>
       <c r="F226" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227">
@@ -13465,7 +13069,7 @@
         <v>0.5</v>
       </c>
       <c r="F227" s="45" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="228">
@@ -13569,7 +13173,7 @@
         <v>1</v>
       </c>
       <c r="F231" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232">
@@ -13595,7 +13199,7 @@
         <v>0.5</v>
       </c>
       <c r="F232" s="45" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="233">
@@ -13725,7 +13329,7 @@
         <v>1</v>
       </c>
       <c r="F237" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238">
@@ -13829,7 +13433,7 @@
         <v>1</v>
       </c>
       <c r="F241" s="44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242">
@@ -13855,7 +13459,7 @@
         <v>0.5</v>
       </c>
       <c r="F242" s="45" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="243">
@@ -13959,7 +13563,7 @@
         <v>1</v>
       </c>
       <c r="F246" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247">
@@ -13985,7 +13589,7 @@
         <v>0.5</v>
       </c>
       <c r="F247" s="45" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="248">
@@ -14141,7 +13745,7 @@
         <v>0.5</v>
       </c>
       <c r="F253" s="45" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="254">
@@ -14271,7 +13875,7 @@
         <v>0.5</v>
       </c>
       <c r="F258" s="45" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="259">
@@ -14375,7 +13979,7 @@
         <v>0.5</v>
       </c>
       <c r="F262" s="45" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="263">

--- a/data/historico/semana_318.xlsx
+++ b/data/historico/semana_318.xlsx
@@ -31,7 +31,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$E$41</definedName>
   </definedNames>
@@ -5106,7 +5106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5118,7 +5118,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (11 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
+          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (12 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="B6" s="35" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="C6" s="35" t="inlineStr">
@@ -5231,19 +5231,19 @@
       </c>
       <c r="D6" s="35" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Agente_3035</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="C7" s="35" t="inlineStr">
@@ -5253,144 +5253,166 @@
       </c>
       <c r="D7" s="35" t="inlineStr">
         <is>
-          <t>Agente_3035</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
+          <t>23/07/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="35" t="inlineStr">
+        <is>
+          <t>Férias/Atestado (automático)</t>
+        </is>
+      </c>
+      <c r="D8" s="35" t="inlineStr">
+        <is>
+          <t>Agente_3035</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="35" t="inlineStr">
+        <is>
           <t>31/07/2026</t>
         </is>
       </c>
-      <c r="B8" s="35" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>12/08/2026</t>
         </is>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C9" s="35" t="inlineStr">
         <is>
           <t>Férias/Atestado (automático)</t>
         </is>
       </c>
-      <c r="D8" s="35" t="inlineStr">
+      <c r="D9" s="35" t="inlineStr">
         <is>
           <t>Agente_2951</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="36" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="B9" s="36" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>06/08/2026</t>
         </is>
       </c>
-      <c r="C9" s="36" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>Levantamento de Índice</t>
         </is>
       </c>
-      <c r="D9" s="36" t="inlineStr">
+      <c r="D10" s="36" t="inlineStr">
         <is>
           <t>Todos os agentes</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="35" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="B10" s="35" t="inlineStr">
+      <c r="B11" s="35" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="C10" s="35" t="inlineStr">
+      <c r="C11" s="35" t="inlineStr">
         <is>
           <t>Férias/Atestado (automático)</t>
         </is>
       </c>
-      <c r="D10" s="35" t="inlineStr">
+      <c r="D11" s="35" t="inlineStr">
         <is>
           <t>Agente_125</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="37" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="37" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="B11" s="37" t="inlineStr">
+      <c r="B12" s="37" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="C11" s="37" t="inlineStr">
+      <c r="C12" s="37" t="inlineStr">
         <is>
           <t>Chuva (confirmada)</t>
         </is>
       </c>
-      <c r="D11" s="37" t="inlineStr">
+      <c r="D12" s="37" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="36" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>07/08/2026</t>
         </is>
       </c>
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>07/08/2026</t>
         </is>
       </c>
-      <c r="C12" s="36" t="inlineStr">
+      <c r="C13" s="36" t="inlineStr">
         <is>
           <t>Instalação de Ovitrampa</t>
         </is>
       </c>
-      <c r="D12" s="36" t="inlineStr">
+      <c r="D13" s="36" t="inlineStr">
         <is>
           <t>Todos os agentes</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="37" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="37" t="inlineStr">
         <is>
           <t>07/08/2026</t>
         </is>
       </c>
-      <c r="B13" s="37" t="inlineStr">
+      <c r="B14" s="37" t="inlineStr">
         <is>
           <t>10/08/2026</t>
         </is>
       </c>
-      <c r="C13" s="37" t="inlineStr">
+      <c r="C14" s="37" t="inlineStr">
         <is>
           <t>Chuva (confirmada)</t>
         </is>
       </c>
-      <c r="D13" s="37" t="inlineStr">
+      <c r="D14" s="37" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D13"/>
+  <autoFilter ref="A2:D14"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>

--- a/data/historico/semana_318.xlsx
+++ b/data/historico/semana_318.xlsx
@@ -31,7 +31,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$E$41</definedName>
   </definedNames>
@@ -5081,19 +5081,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (12 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
+          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (13 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="D7" s="29" t="inlineStr">
         <is>
-          <t>Agente_3035</t>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
     </row>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="B8" s="29" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="C8" s="29" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="D8" s="29" t="inlineStr">
         <is>
-          <t>Agente_3035</t>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="B9" s="29" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="C9" s="29" t="inlineStr">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="D9" s="29" t="inlineStr">
         <is>
-          <t>Agente_2951</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="D11" s="29" t="inlineStr">
         <is>
-          <t>Agente_125</t>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
         </is>
       </c>
     </row>
@@ -5343,51 +5343,73 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="30" t="inlineStr">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="29" t="inlineStr">
+        <is>
+          <t>13/08/2026</t>
+        </is>
+      </c>
+      <c r="C13" s="29" t="inlineStr">
+        <is>
+          <t>Férias/Atestado (automático)</t>
+        </is>
+      </c>
+      <c r="D13" s="29" t="inlineStr">
+        <is>
+          <t>Cicero Isrrael Sanabria</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>07/08/2026</t>
         </is>
       </c>
-      <c r="B13" s="30" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>07/08/2026</t>
         </is>
       </c>
-      <c r="C13" s="30" t="inlineStr">
+      <c r="C14" s="30" t="inlineStr">
         <is>
           <t>Instalação de Ovitrampa</t>
         </is>
       </c>
-      <c r="D13" s="30" t="inlineStr">
+      <c r="D14" s="30" t="inlineStr">
         <is>
           <t>Todos os agentes</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="31" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>07/08/2026</t>
         </is>
       </c>
-      <c r="B14" s="31" t="inlineStr">
+      <c r="B15" s="31" t="inlineStr">
         <is>
           <t>10/08/2026</t>
         </is>
       </c>
-      <c r="C14" s="31" t="inlineStr">
+      <c r="C15" s="31" t="inlineStr">
         <is>
           <t>Chuva (confirmada)</t>
         </is>
       </c>
-      <c r="D14" s="31" t="inlineStr">
+      <c r="D15" s="31" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D14"/>
+  <autoFilter ref="A2:D15"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>

--- a/data/historico/semana_318.xlsx
+++ b/data/historico/semana_318.xlsx
@@ -8276,73 +8276,73 @@
       <c r="F38" s="2" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="n">
+      <c r="A39" s="6" t="n">
         <v>37</v>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>Mateus Falcao de Souza</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="D39" s="6" t="n">
         <v>89.90000000000001</v>
       </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>🟢 EXCELENTE</t>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>🟡 BOM</t>
         </is>
       </c>
       <c r="F39" s="2" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="n">
+      <c r="A40" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Ramona dos Santos Oliveira</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="D40" s="6" t="n">
         <v>88.8</v>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>🟢 EXCELENTE</t>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>🟡 BOM</t>
         </is>
       </c>
       <c r="F40" s="2" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n">
+      <c r="A41" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>Anderson Jose de Santana</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="D41" s="6" t="n">
         <v>85.3</v>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>🟢 EXCELENTE</t>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>🟡 BOM</t>
         </is>
       </c>
       <c r="F41" s="2" t="n"/>

--- a/data/historico/semana_318.xlsx
+++ b/data/historico/semana_318.xlsx
@@ -31,7 +31,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$E$41</definedName>
   </definedNames>
@@ -5081,7 +5081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5093,7 +5093,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (13 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
+          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (15 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="B8" s="29" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="C8" s="29" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="B9" s="29" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="C9" s="29" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="B13" s="29" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="C13" s="29" t="inlineStr">
@@ -5387,29 +5387,73 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="31" t="inlineStr">
+      <c r="A15" s="29" t="inlineStr">
         <is>
           <t>07/08/2026</t>
         </is>
       </c>
-      <c r="B15" s="31" t="inlineStr">
+      <c r="B15" s="29" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="C15" s="29" t="inlineStr">
+        <is>
+          <t>Férias/Atestado (automático)</t>
+        </is>
+      </c>
+      <c r="D15" s="29" t="inlineStr">
+        <is>
+          <t>Wagner Tarlei Gomes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="29" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="C16" s="29" t="inlineStr">
+        <is>
+          <t>Férias/Atestado (automático)</t>
+        </is>
+      </c>
+      <c r="D16" s="29" t="inlineStr">
+        <is>
+          <t>Ramona dos Santos Oliveira</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="31" t="inlineStr">
         <is>
           <t>10/08/2026</t>
         </is>
       </c>
-      <c r="C15" s="31" t="inlineStr">
+      <c r="C17" s="31" t="inlineStr">
         <is>
           <t>Chuva (confirmada)</t>
         </is>
       </c>
-      <c r="D15" s="31" t="inlineStr">
+      <c r="D17" s="31" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D15"/>
+  <autoFilter ref="A2:D17"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>

--- a/data/historico/semana_318.xlsx
+++ b/data/historico/semana_318.xlsx
@@ -31,7 +31,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$E$41</definedName>
   </definedNames>
@@ -5081,7 +5081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5093,7 +5093,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (15 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
+          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (14 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="B6" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="C6" s="29" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="D6" s="29" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="B7" s="29" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="C7" s="29" t="inlineStr">
@@ -5228,14 +5228,14 @@
       </c>
       <c r="D7" s="29" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="29" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="B8" s="29" t="inlineStr">
@@ -5250,139 +5250,139 @@
       </c>
       <c r="D8" s="29" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="30" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="30" t="inlineStr">
+        <is>
+          <t>Levantamento de Índice</t>
+        </is>
+      </c>
+      <c r="D9" s="30" t="inlineStr">
+        <is>
+          <t>Todos os agentes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="29" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="29" t="inlineStr">
+        <is>
+          <t>Férias/Atestado (automático)</t>
+        </is>
+      </c>
+      <c r="D10" s="29" t="inlineStr">
+        <is>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="C11" s="31" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D11" s="31" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>14/08/2026</t>
         </is>
       </c>
-      <c r="C9" s="29" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>Férias/Atestado (automático)</t>
         </is>
       </c>
-      <c r="D9" s="29" t="inlineStr">
-        <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="30" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="30" t="inlineStr">
-        <is>
-          <t>06/08/2026</t>
-        </is>
-      </c>
-      <c r="C10" s="30" t="inlineStr">
-        <is>
-          <t>Levantamento de Índice</t>
-        </is>
-      </c>
-      <c r="D10" s="30" t="inlineStr">
+      <c r="D12" s="29" t="inlineStr">
+        <is>
+          <t>Cicero Isrrael Sanabria</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="30" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="30" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="C13" s="30" t="inlineStr">
+        <is>
+          <t>Instalação de Ovitrampa</t>
+        </is>
+      </c>
+      <c r="D13" s="30" t="inlineStr">
         <is>
           <t>Todos os agentes</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="29" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="29" t="inlineStr">
-        <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-      <c r="C11" s="29" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="29" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>Férias/Atestado (automático)</t>
         </is>
       </c>
-      <c r="D11" s="29" t="inlineStr">
-        <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="31" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="31" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="C12" s="31" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D12" s="31" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="29" t="inlineStr">
-        <is>
-          <t>06/08/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="29" t="inlineStr">
-        <is>
-          <t>14/08/2026</t>
-        </is>
-      </c>
-      <c r="C13" s="29" t="inlineStr">
-        <is>
-          <t>Férias/Atestado (automático)</t>
-        </is>
-      </c>
-      <c r="D13" s="29" t="inlineStr">
-        <is>
-          <t>Cicero Isrrael Sanabria</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="30" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="30" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="C14" s="30" t="inlineStr">
-        <is>
-          <t>Instalação de Ovitrampa</t>
-        </is>
-      </c>
-      <c r="D14" s="30" t="inlineStr">
-        <is>
-          <t>Todos os agentes</t>
+      <c r="D14" s="29" t="inlineStr">
+        <is>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
     </row>
@@ -5404,56 +5404,34 @@
       </c>
       <c r="D15" s="29" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Ramona dos Santos Oliveira</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="29" t="inlineStr">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>07/08/2026</t>
         </is>
       </c>
-      <c r="B16" s="29" t="inlineStr">
-        <is>
-          <t>14/08/2026</t>
-        </is>
-      </c>
-      <c r="C16" s="29" t="inlineStr">
-        <is>
-          <t>Férias/Atestado (automático)</t>
-        </is>
-      </c>
-      <c r="D16" s="29" t="inlineStr">
-        <is>
-          <t>Ramona dos Santos Oliveira</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="31" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="31" t="inlineStr">
+      <c r="B16" s="31" t="inlineStr">
         <is>
           <t>10/08/2026</t>
         </is>
       </c>
-      <c r="C17" s="31" t="inlineStr">
+      <c r="C16" s="31" t="inlineStr">
         <is>
           <t>Chuva (confirmada)</t>
         </is>
       </c>
-      <c r="D17" s="31" t="inlineStr">
+      <c r="D16" s="31" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D17"/>
+  <autoFilter ref="A2:D16"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>

--- a/data/historico/semana_318.xlsx
+++ b/data/historico/semana_318.xlsx
@@ -31,7 +31,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$E$41</definedName>
   </definedNames>
@@ -5081,7 +5081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5093,7 +5093,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (14 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
+          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (12 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5125,12 +5125,12 @@
     <row r="3">
       <c r="A3" s="29" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="B3" s="29" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="C3" s="29" t="inlineStr">
@@ -5140,19 +5140,19 @@
       </c>
       <c r="D3" s="29" t="inlineStr">
         <is>
-          <t>Geancarlos Ferreira Barrios</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="29" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="B4" s="29" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="C4" s="29" t="inlineStr">
@@ -5162,19 +5162,19 @@
       </c>
       <c r="D4" s="29" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="29" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="B5" s="29" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="C5" s="29" t="inlineStr">
@@ -5184,14 +5184,14 @@
       </c>
       <c r="D5" s="29" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="29" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="B6" s="29" t="inlineStr">
@@ -5206,19 +5206,19 @@
       </c>
       <c r="D6" s="29" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="29" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="B7" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="C7" s="29" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="D7" s="29" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Geancarlos Ferreira Barrios</t>
         </is>
       </c>
     </row>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="B8" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="C8" s="29" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="D8" s="29" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
     </row>
@@ -5365,73 +5365,29 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="29" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>07/08/2026</t>
         </is>
       </c>
-      <c r="B14" s="29" t="inlineStr">
-        <is>
-          <t>14/08/2026</t>
-        </is>
-      </c>
-      <c r="C14" s="29" t="inlineStr">
-        <is>
-          <t>Férias/Atestado (automático)</t>
-        </is>
-      </c>
-      <c r="D14" s="29" t="inlineStr">
-        <is>
-          <t>Wagner Tarlei Gomes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="29" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="29" t="inlineStr">
-        <is>
-          <t>14/08/2026</t>
-        </is>
-      </c>
-      <c r="C15" s="29" t="inlineStr">
-        <is>
-          <t>Férias/Atestado (automático)</t>
-        </is>
-      </c>
-      <c r="D15" s="29" t="inlineStr">
-        <is>
-          <t>Ramona dos Santos Oliveira</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="31" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="31" t="inlineStr">
+      <c r="B14" s="31" t="inlineStr">
         <is>
           <t>10/08/2026</t>
         </is>
       </c>
-      <c r="C16" s="31" t="inlineStr">
+      <c r="C14" s="31" t="inlineStr">
         <is>
           <t>Chuva (confirmada)</t>
         </is>
       </c>
-      <c r="D16" s="31" t="inlineStr">
+      <c r="D14" s="31" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D16"/>
+  <autoFilter ref="A2:D14"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>

--- a/data/historico/semana_318.xlsx
+++ b/data/historico/semana_318.xlsx
@@ -31,7 +31,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$E$41</definedName>
   </definedNames>
@@ -5081,7 +5081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5093,7 +5093,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (12 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
+          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (13 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="B5" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="C5" s="29" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="B6" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="C6" s="29" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="B12" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="C12" s="29" t="inlineStr">
@@ -5365,29 +5365,51 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="29" t="inlineStr">
         <is>
           <t>07/08/2026</t>
         </is>
       </c>
-      <c r="B14" s="31" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="C14" s="29" t="inlineStr">
+        <is>
+          <t>Férias/Atestado (automático)</t>
+        </is>
+      </c>
+      <c r="D14" s="29" t="inlineStr">
+        <is>
+          <t>Ramona dos Santos Oliveira</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="31" t="inlineStr">
         <is>
           <t>10/08/2026</t>
         </is>
       </c>
-      <c r="C14" s="31" t="inlineStr">
+      <c r="C15" s="31" t="inlineStr">
         <is>
           <t>Chuva (confirmada)</t>
         </is>
       </c>
-      <c r="D14" s="31" t="inlineStr">
+      <c r="D15" s="31" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D14"/>
+  <autoFilter ref="A2:D15"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>

--- a/data/historico/semana_318.xlsx
+++ b/data/historico/semana_318.xlsx
@@ -5174,7 +5174,7 @@
       </c>
       <c r="B5" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="C5" s="29" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="B12" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="C12" s="29" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="B14" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="C14" s="29" t="inlineStr">

--- a/data/historico/semana_318.xlsx
+++ b/data/historico/semana_318.xlsx
@@ -33,7 +33,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$E$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$G$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="B12" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="C12" s="29" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="B14" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="C14" s="29" t="inlineStr">
@@ -7360,15 +7360,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F264"/>
+  <dimension ref="A1:G264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -7382,6 +7383,7 @@
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -7401,15 +7403,24 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
+          <t>Dias Trabalhados</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Dias Úteis Esperados no Mês</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
           <t>Pontuação Final</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -7426,14 +7437,19 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F3" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -7450,14 +7466,19 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F4" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -7474,14 +7495,19 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F5" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -7498,14 +7524,19 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F6" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -7522,14 +7553,19 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F7" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -7546,14 +7582,19 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F8" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -7570,14 +7611,19 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F9" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -7594,14 +7640,19 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F10" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -7618,14 +7669,19 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F11" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -7642,14 +7698,19 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F12" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -7666,14 +7727,19 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F13" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -7690,14 +7756,19 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F14" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -7714,14 +7785,19 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F15" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -7738,14 +7814,19 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F16" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -7762,14 +7843,19 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F17" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -7786,14 +7872,19 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F18" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -7810,14 +7901,19 @@
         </is>
       </c>
       <c r="D19" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F19" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -7834,14 +7930,19 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F20" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -7858,14 +7959,19 @@
         </is>
       </c>
       <c r="D21" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F21" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -7882,14 +7988,19 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F22" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -7906,14 +8017,19 @@
         </is>
       </c>
       <c r="D23" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F23" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -7930,14 +8046,19 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F24" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -7954,14 +8075,19 @@
         </is>
       </c>
       <c r="D25" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F25" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -7978,14 +8104,19 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F26" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -8002,14 +8133,19 @@
         </is>
       </c>
       <c r="D27" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F27" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -8026,14 +8162,19 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F28" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -8050,14 +8191,19 @@
         </is>
       </c>
       <c r="D29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F29" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -8074,14 +8220,19 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F30" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -8098,14 +8249,19 @@
         </is>
       </c>
       <c r="D31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F31" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -8122,14 +8278,19 @@
         </is>
       </c>
       <c r="D32" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F32" s="4" t="n">
         <v>99.5</v>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -8146,14 +8307,19 @@
         </is>
       </c>
       <c r="D33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F33" s="4" t="n">
         <v>99.09999999999999</v>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -8170,14 +8336,19 @@
         </is>
       </c>
       <c r="D34" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F34" s="4" t="n">
         <v>98.90000000000001</v>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -8194,14 +8365,19 @@
         </is>
       </c>
       <c r="D35" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F35" s="4" t="n">
         <v>98.8</v>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -8218,14 +8394,19 @@
         </is>
       </c>
       <c r="D36" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F36" s="4" t="n">
         <v>96.90000000000001</v>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -8242,14 +8423,19 @@
         </is>
       </c>
       <c r="D37" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F37" s="4" t="n">
         <v>93</v>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -8266,14 +8452,19 @@
         </is>
       </c>
       <c r="D38" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F38" s="4" t="n">
         <v>92.8</v>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
@@ -8290,14 +8481,19 @@
         </is>
       </c>
       <c r="D39" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="F39" s="6" t="n">
         <v>89.90000000000001</v>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="G39" s="6" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
       </c>
-      <c r="F39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
@@ -8314,14 +8510,19 @@
         </is>
       </c>
       <c r="D40" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="F40" s="6" t="n">
         <v>88.8</v>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="G40" s="6" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
       </c>
-      <c r="F40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
@@ -8338,14 +8539,19 @@
         </is>
       </c>
       <c r="D41" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="F41" s="6" t="n">
         <v>85.3</v>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
       </c>
-      <c r="F41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
@@ -8354,6 +8560,7 @@
       <c r="D42" s="2" t="n"/>
       <c r="E42" s="2" t="n"/>
       <c r="F42" s="2" t="n"/>
+      <c r="G42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>
@@ -8362,6 +8569,7 @@
       <c r="D43" s="2" t="n"/>
       <c r="E43" s="2" t="n"/>
       <c r="F43" s="2" t="n"/>
+      <c r="G43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="38" t="inlineStr">
@@ -8374,6 +8582,7 @@
       <c r="D44" s="2" t="n"/>
       <c r="E44" s="2" t="n"/>
       <c r="F44" s="2" t="n"/>
+      <c r="G44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -8406,6 +8615,7 @@
           <t>Pontos Aplicados</t>
         </is>
       </c>
+      <c r="G45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="39" t="inlineStr">
@@ -8432,6 +8642,7 @@
       <c r="F46" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="39" t="inlineStr">
@@ -8458,6 +8669,7 @@
       <c r="F47" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="39" t="inlineStr">
@@ -8484,6 +8696,7 @@
       <c r="F48" s="39" t="n">
         <v>2</v>
       </c>
+      <c r="G48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="40" t="inlineStr">
@@ -8510,6 +8723,7 @@
       <c r="F49" s="40" t="n">
         <v>-1</v>
       </c>
+      <c r="G49" s="2" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="40" t="inlineStr">
@@ -8531,11 +8745,12 @@
         <v>1</v>
       </c>
       <c r="E50" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F50" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="40" t="inlineStr">
@@ -8557,11 +8772,12 @@
         <v>2</v>
       </c>
       <c r="E51" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F51" s="40" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="39" t="inlineStr">
@@ -8588,6 +8804,7 @@
       <c r="F52" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="39" t="inlineStr">
@@ -8614,6 +8831,7 @@
       <c r="F53" s="39" t="n">
         <v>1</v>
       </c>
+      <c r="G53" s="2" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="40" t="inlineStr">
@@ -8640,6 +8858,7 @@
       <c r="F54" s="40" t="n">
         <v>-1</v>
       </c>
+      <c r="G54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="40" t="inlineStr">
@@ -8661,11 +8880,12 @@
         <v>1</v>
       </c>
       <c r="E55" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F55" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G55" s="2" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="40" t="inlineStr">
@@ -8687,11 +8907,12 @@
         <v>1</v>
       </c>
       <c r="E56" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F56" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G56" s="2" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="40" t="inlineStr">
@@ -8713,11 +8934,12 @@
         <v>1</v>
       </c>
       <c r="E57" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F57" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="40" t="inlineStr">
@@ -8739,11 +8961,12 @@
         <v>3</v>
       </c>
       <c r="E58" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F58" s="40" t="n">
         <v>-1.8</v>
       </c>
+      <c r="G58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="39" t="inlineStr">
@@ -8770,6 +8993,7 @@
       <c r="F59" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G59" s="2" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="39" t="inlineStr">
@@ -8796,6 +9020,7 @@
       <c r="F60" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G60" s="2" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="39" t="inlineStr">
@@ -8822,6 +9047,7 @@
       <c r="F61" s="39" t="n">
         <v>1</v>
       </c>
+      <c r="G61" s="2" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="40" t="inlineStr">
@@ -8848,6 +9074,7 @@
       <c r="F62" s="40" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G62" s="2" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="40" t="inlineStr">
@@ -8869,11 +9096,12 @@
         <v>1</v>
       </c>
       <c r="E63" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F63" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="40" t="inlineStr">
@@ -8895,11 +9123,12 @@
         <v>1</v>
       </c>
       <c r="E64" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F64" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G64" s="2" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="39" t="inlineStr">
@@ -8926,6 +9155,7 @@
       <c r="F65" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G65" s="2" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="39" t="inlineStr">
@@ -8952,6 +9182,7 @@
       <c r="F66" s="39" t="n">
         <v>1</v>
       </c>
+      <c r="G66" s="2" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="40" t="inlineStr">
@@ -8978,6 +9209,7 @@
       <c r="F67" s="40" t="n">
         <v>-1.5</v>
       </c>
+      <c r="G67" s="2" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="40" t="inlineStr">
@@ -8999,11 +9231,12 @@
         <v>1</v>
       </c>
       <c r="E68" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F68" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G68" s="2" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="40" t="inlineStr">
@@ -9025,11 +9258,12 @@
         <v>3</v>
       </c>
       <c r="E69" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F69" s="40" t="n">
         <v>-1.8</v>
       </c>
+      <c r="G69" s="2" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="40" t="inlineStr">
@@ -9051,11 +9285,12 @@
         <v>1</v>
       </c>
       <c r="E70" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F70" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G70" s="2" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="40" t="inlineStr">
@@ -9077,11 +9312,12 @@
         <v>27</v>
       </c>
       <c r="E71" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F71" s="40" t="n">
         <v>-16.2</v>
       </c>
+      <c r="G71" s="2" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="39" t="inlineStr">
@@ -9108,6 +9344,7 @@
       <c r="F72" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G72" s="2" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="39" t="inlineStr">
@@ -9134,6 +9371,7 @@
       <c r="F73" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G73" s="2" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="39" t="inlineStr">
@@ -9160,6 +9398,7 @@
       <c r="F74" s="39" t="n">
         <v>3</v>
       </c>
+      <c r="G74" s="2" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="40" t="inlineStr">
@@ -9186,6 +9425,7 @@
       <c r="F75" s="40" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G75" s="2" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="39" t="inlineStr">
@@ -9212,6 +9452,7 @@
       <c r="F76" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G76" s="2" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="39" t="inlineStr">
@@ -9238,6 +9479,7 @@
       <c r="F77" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G77" s="2" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="40" t="inlineStr">
@@ -9264,6 +9506,7 @@
       <c r="F78" s="40" t="n">
         <v>-1</v>
       </c>
+      <c r="G78" s="2" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="40" t="inlineStr">
@@ -9285,11 +9528,12 @@
         <v>1</v>
       </c>
       <c r="E79" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F79" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G79" s="2" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="40" t="inlineStr">
@@ -9311,11 +9555,12 @@
         <v>1</v>
       </c>
       <c r="E80" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F80" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G80" s="2" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="39" t="inlineStr">
@@ -9342,6 +9587,7 @@
       <c r="F81" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G81" s="2" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="39" t="inlineStr">
@@ -9368,6 +9614,7 @@
       <c r="F82" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G82" s="2" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="40" t="inlineStr">
@@ -9394,6 +9641,7 @@
       <c r="F83" s="40" t="n">
         <v>-1</v>
       </c>
+      <c r="G83" s="2" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="40" t="inlineStr">
@@ -9415,11 +9663,12 @@
         <v>2</v>
       </c>
       <c r="E84" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F84" s="40" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G84" s="2" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="40" t="inlineStr">
@@ -9441,11 +9690,12 @@
         <v>1</v>
       </c>
       <c r="E85" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F85" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G85" s="2" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="39" t="inlineStr">
@@ -9472,6 +9722,7 @@
       <c r="F86" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G86" s="2" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="39" t="inlineStr">
@@ -9498,6 +9749,7 @@
       <c r="F87" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G87" s="2" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="40" t="inlineStr">
@@ -9524,6 +9776,7 @@
       <c r="F88" s="40" t="n">
         <v>-1</v>
       </c>
+      <c r="G88" s="2" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="40" t="inlineStr">
@@ -9545,11 +9798,12 @@
         <v>1</v>
       </c>
       <c r="E89" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F89" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G89" s="2" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="39" t="inlineStr">
@@ -9576,6 +9830,7 @@
       <c r="F90" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G90" s="2" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="39" t="inlineStr">
@@ -9602,6 +9857,7 @@
       <c r="F91" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G91" s="2" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="39" t="inlineStr">
@@ -9628,6 +9884,7 @@
       <c r="F92" s="39" t="n">
         <v>1</v>
       </c>
+      <c r="G92" s="2" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="40" t="inlineStr">
@@ -9654,6 +9911,7 @@
       <c r="F93" s="40" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G93" s="2" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="40" t="inlineStr">
@@ -9675,11 +9933,12 @@
         <v>1</v>
       </c>
       <c r="E94" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F94" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G94" s="2" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="39" t="inlineStr">
@@ -9706,6 +9965,7 @@
       <c r="F95" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G95" s="2" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="40" t="inlineStr">
@@ -9732,6 +9992,7 @@
       <c r="F96" s="40" t="n">
         <v>-1</v>
       </c>
+      <c r="G96" s="2" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="40" t="inlineStr">
@@ -9753,11 +10014,12 @@
         <v>1</v>
       </c>
       <c r="E97" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F97" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G97" s="2" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="40" t="inlineStr">
@@ -9779,11 +10041,12 @@
         <v>1</v>
       </c>
       <c r="E98" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F98" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G98" s="2" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="40" t="inlineStr">
@@ -9805,11 +10068,12 @@
         <v>1</v>
       </c>
       <c r="E99" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F99" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G99" s="2" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="39" t="inlineStr">
@@ -9836,6 +10100,7 @@
       <c r="F100" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G100" s="2" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="39" t="inlineStr">
@@ -9862,6 +10127,7 @@
       <c r="F101" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G101" s="2" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="40" t="inlineStr">
@@ -9888,6 +10154,7 @@
       <c r="F102" s="40" t="n">
         <v>-2</v>
       </c>
+      <c r="G102" s="2" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="40" t="inlineStr">
@@ -9909,11 +10176,12 @@
         <v>1</v>
       </c>
       <c r="E103" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F103" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G103" s="2" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="40" t="inlineStr">
@@ -9935,11 +10203,12 @@
         <v>2</v>
       </c>
       <c r="E104" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F104" s="40" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G104" s="2" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="40" t="inlineStr">
@@ -9961,11 +10230,12 @@
         <v>2</v>
       </c>
       <c r="E105" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F105" s="40" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G105" s="2" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="40" t="inlineStr">
@@ -9987,11 +10257,12 @@
         <v>3</v>
       </c>
       <c r="E106" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F106" s="40" t="n">
         <v>-1.8</v>
       </c>
+      <c r="G106" s="2" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="39" t="inlineStr">
@@ -10018,6 +10289,7 @@
       <c r="F107" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G107" s="2" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="39" t="inlineStr">
@@ -10044,6 +10316,7 @@
       <c r="F108" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G108" s="2" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="39" t="inlineStr">
@@ -10070,6 +10343,7 @@
       <c r="F109" s="39" t="n">
         <v>3</v>
       </c>
+      <c r="G109" s="2" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="39" t="inlineStr">
@@ -10096,6 +10370,7 @@
       <c r="F110" s="39" t="n">
         <v>1</v>
       </c>
+      <c r="G110" s="2" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="39" t="inlineStr">
@@ -10122,6 +10397,7 @@
       <c r="F111" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G111" s="2" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="40" t="inlineStr">
@@ -10148,6 +10424,7 @@
       <c r="F112" s="40" t="n">
         <v>-2</v>
       </c>
+      <c r="G112" s="2" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="40" t="inlineStr">
@@ -10169,11 +10446,12 @@
         <v>1</v>
       </c>
       <c r="E113" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F113" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G113" s="2" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="40" t="inlineStr">
@@ -10195,11 +10473,12 @@
         <v>2</v>
       </c>
       <c r="E114" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F114" s="40" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G114" s="2" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="40" t="inlineStr">
@@ -10221,11 +10500,12 @@
         <v>3</v>
       </c>
       <c r="E115" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F115" s="40" t="n">
         <v>-1.8</v>
       </c>
+      <c r="G115" s="2" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="40" t="inlineStr">
@@ -10247,11 +10527,12 @@
         <v>1</v>
       </c>
       <c r="E116" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F116" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G116" s="2" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="39" t="inlineStr">
@@ -10278,6 +10559,7 @@
       <c r="F117" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G117" s="2" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="39" t="inlineStr">
@@ -10304,6 +10586,7 @@
       <c r="F118" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G118" s="2" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="39" t="inlineStr">
@@ -10330,6 +10613,7 @@
       <c r="F119" s="39" t="n">
         <v>2</v>
       </c>
+      <c r="G119" s="2" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="40" t="inlineStr">
@@ -10356,6 +10640,7 @@
       <c r="F120" s="40" t="n">
         <v>-1</v>
       </c>
+      <c r="G120" s="2" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="40" t="inlineStr">
@@ -10377,11 +10662,12 @@
         <v>1</v>
       </c>
       <c r="E121" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F121" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G121" s="2" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="40" t="inlineStr">
@@ -10403,11 +10689,12 @@
         <v>1</v>
       </c>
       <c r="E122" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F122" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G122" s="2" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="40" t="inlineStr">
@@ -10429,11 +10716,12 @@
         <v>2</v>
       </c>
       <c r="E123" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F123" s="40" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G123" s="2" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="39" t="inlineStr">
@@ -10460,6 +10748,7 @@
       <c r="F124" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G124" s="2" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="39" t="inlineStr">
@@ -10486,6 +10775,7 @@
       <c r="F125" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G125" s="2" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="39" t="inlineStr">
@@ -10512,6 +10802,7 @@
       <c r="F126" s="39" t="n">
         <v>3</v>
       </c>
+      <c r="G126" s="2" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="40" t="inlineStr">
@@ -10538,6 +10829,7 @@
       <c r="F127" s="40" t="n">
         <v>-1</v>
       </c>
+      <c r="G127" s="2" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="39" t="inlineStr">
@@ -10564,6 +10856,7 @@
       <c r="F128" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G128" s="2" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="39" t="inlineStr">
@@ -10590,6 +10883,7 @@
       <c r="F129" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G129" s="2" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="39" t="inlineStr">
@@ -10616,6 +10910,7 @@
       <c r="F130" s="39" t="n">
         <v>1</v>
       </c>
+      <c r="G130" s="2" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="40" t="inlineStr">
@@ -10642,6 +10937,7 @@
       <c r="F131" s="40" t="n">
         <v>-1</v>
       </c>
+      <c r="G131" s="2" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="40" t="inlineStr">
@@ -10663,11 +10959,12 @@
         <v>2</v>
       </c>
       <c r="E132" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F132" s="40" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G132" s="2" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="40" t="inlineStr">
@@ -10689,11 +10986,12 @@
         <v>1</v>
       </c>
       <c r="E133" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F133" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G133" s="2" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="40" t="inlineStr">
@@ -10715,11 +11013,12 @@
         <v>2</v>
       </c>
       <c r="E134" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F134" s="40" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G134" s="2" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="39" t="inlineStr">
@@ -10746,6 +11045,7 @@
       <c r="F135" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G135" s="2" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="40" t="inlineStr">
@@ -10772,6 +11072,7 @@
       <c r="F136" s="40" t="n">
         <v>-1.5</v>
       </c>
+      <c r="G136" s="2" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="40" t="inlineStr">
@@ -10793,11 +11094,12 @@
         <v>1</v>
       </c>
       <c r="E137" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F137" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G137" s="2" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="40" t="inlineStr">
@@ -10819,11 +11121,12 @@
         <v>1</v>
       </c>
       <c r="E138" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F138" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G138" s="2" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="40" t="inlineStr">
@@ -10845,11 +11148,12 @@
         <v>1</v>
       </c>
       <c r="E139" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F139" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G139" s="2" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="40" t="inlineStr">
@@ -10871,11 +11175,12 @@
         <v>8</v>
       </c>
       <c r="E140" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F140" s="40" t="n">
         <v>-4.8</v>
       </c>
+      <c r="G140" s="2" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="39" t="inlineStr">
@@ -10902,6 +11207,7 @@
       <c r="F141" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G141" s="2" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="40" t="inlineStr">
@@ -10928,6 +11234,7 @@
       <c r="F142" s="40" t="n">
         <v>-2</v>
       </c>
+      <c r="G142" s="2" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="40" t="inlineStr">
@@ -10949,11 +11256,12 @@
         <v>3</v>
       </c>
       <c r="E143" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F143" s="40" t="n">
         <v>-1.8</v>
       </c>
+      <c r="G143" s="2" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="40" t="inlineStr">
@@ -10975,11 +11283,12 @@
         <v>1</v>
       </c>
       <c r="E144" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F144" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G144" s="2" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="40" t="inlineStr">
@@ -11001,11 +11310,12 @@
         <v>2</v>
       </c>
       <c r="E145" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F145" s="40" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G145" s="2" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="40" t="inlineStr">
@@ -11027,11 +11337,12 @@
         <v>11</v>
       </c>
       <c r="E146" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F146" s="40" t="n">
         <v>-6.6</v>
       </c>
+      <c r="G146" s="2" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="39" t="inlineStr">
@@ -11058,6 +11369,7 @@
       <c r="F147" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G147" s="2" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="39" t="inlineStr">
@@ -11084,6 +11396,7 @@
       <c r="F148" s="39" t="n">
         <v>1</v>
       </c>
+      <c r="G148" s="2" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="40" t="inlineStr">
@@ -11110,6 +11423,7 @@
       <c r="F149" s="40" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G149" s="2" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="40" t="inlineStr">
@@ -11131,11 +11445,12 @@
         <v>1</v>
       </c>
       <c r="E150" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F150" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G150" s="2" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="40" t="inlineStr">
@@ -11157,11 +11472,12 @@
         <v>9</v>
       </c>
       <c r="E151" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F151" s="40" t="n">
         <v>-5.4</v>
       </c>
+      <c r="G151" s="2" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="39" t="inlineStr">
@@ -11188,6 +11504,7 @@
       <c r="F152" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G152" s="2" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="39" t="inlineStr">
@@ -11214,6 +11531,7 @@
       <c r="F153" s="39" t="n">
         <v>1</v>
       </c>
+      <c r="G153" s="2" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="40" t="inlineStr">
@@ -11240,6 +11558,7 @@
       <c r="F154" s="40" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G154" s="2" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="40" t="inlineStr">
@@ -11261,11 +11580,12 @@
         <v>1</v>
       </c>
       <c r="E155" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F155" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G155" s="2" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="40" t="inlineStr">
@@ -11287,11 +11607,12 @@
         <v>2</v>
       </c>
       <c r="E156" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F156" s="40" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G156" s="2" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="40" t="inlineStr">
@@ -11313,11 +11634,12 @@
         <v>5</v>
       </c>
       <c r="E157" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F157" s="40" t="n">
         <v>-3</v>
       </c>
+      <c r="G157" s="2" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="39" t="inlineStr">
@@ -11344,6 +11666,7 @@
       <c r="F158" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G158" s="2" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="39" t="inlineStr">
@@ -11370,6 +11693,7 @@
       <c r="F159" s="39" t="n">
         <v>1</v>
       </c>
+      <c r="G159" s="2" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="40" t="inlineStr">
@@ -11396,6 +11720,7 @@
       <c r="F160" s="40" t="n">
         <v>-1.5</v>
       </c>
+      <c r="G160" s="2" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="40" t="inlineStr">
@@ -11417,11 +11742,12 @@
         <v>1</v>
       </c>
       <c r="E161" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F161" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G161" s="2" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="40" t="inlineStr">
@@ -11443,11 +11769,12 @@
         <v>1</v>
       </c>
       <c r="E162" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F162" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G162" s="2" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="40" t="inlineStr">
@@ -11469,11 +11796,12 @@
         <v>1</v>
       </c>
       <c r="E163" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F163" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G163" s="2" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="40" t="inlineStr">
@@ -11495,11 +11823,12 @@
         <v>3</v>
       </c>
       <c r="E164" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F164" s="40" t="n">
         <v>-1.8</v>
       </c>
+      <c r="G164" s="2" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="39" t="inlineStr">
@@ -11526,6 +11855,7 @@
       <c r="F165" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G165" s="2" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="39" t="inlineStr">
@@ -11552,6 +11882,7 @@
       <c r="F166" s="39" t="n">
         <v>1</v>
       </c>
+      <c r="G166" s="2" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="40" t="inlineStr">
@@ -11578,6 +11909,7 @@
       <c r="F167" s="40" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G167" s="2" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="40" t="inlineStr">
@@ -11599,11 +11931,12 @@
         <v>1</v>
       </c>
       <c r="E168" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F168" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G168" s="2" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="40" t="inlineStr">
@@ -11625,11 +11958,12 @@
         <v>1</v>
       </c>
       <c r="E169" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F169" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G169" s="2" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="40" t="inlineStr">
@@ -11651,11 +11985,12 @@
         <v>1</v>
       </c>
       <c r="E170" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F170" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G170" s="2" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="40" t="inlineStr">
@@ -11677,11 +12012,12 @@
         <v>23</v>
       </c>
       <c r="E171" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F171" s="40" t="n">
         <v>-13.8</v>
       </c>
+      <c r="G171" s="2" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="39" t="inlineStr">
@@ -11708,6 +12044,7 @@
       <c r="F172" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G172" s="2" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="39" t="inlineStr">
@@ -11734,6 +12071,7 @@
       <c r="F173" s="39" t="n">
         <v>1</v>
       </c>
+      <c r="G173" s="2" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="40" t="inlineStr">
@@ -11760,6 +12098,7 @@
       <c r="F174" s="40" t="n">
         <v>-1</v>
       </c>
+      <c r="G174" s="2" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="40" t="inlineStr">
@@ -11781,11 +12120,12 @@
         <v>1</v>
       </c>
       <c r="E175" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F175" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G175" s="2" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="40" t="inlineStr">
@@ -11807,11 +12147,12 @@
         <v>1</v>
       </c>
       <c r="E176" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F176" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G176" s="2" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="40" t="inlineStr">
@@ -11833,11 +12174,12 @@
         <v>5</v>
       </c>
       <c r="E177" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F177" s="40" t="n">
         <v>-3</v>
       </c>
+      <c r="G177" s="2" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="39" t="inlineStr">
@@ -11864,6 +12206,7 @@
       <c r="F178" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G178" s="2" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="39" t="inlineStr">
@@ -11890,6 +12233,7 @@
       <c r="F179" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G179" s="2" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="39" t="inlineStr">
@@ -11916,6 +12260,7 @@
       <c r="F180" s="39" t="n">
         <v>3</v>
       </c>
+      <c r="G180" s="2" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="40" t="inlineStr">
@@ -11942,6 +12287,7 @@
       <c r="F181" s="40" t="n">
         <v>-1</v>
       </c>
+      <c r="G181" s="2" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="39" t="inlineStr">
@@ -11968,6 +12314,7 @@
       <c r="F182" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G182" s="2" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="40" t="inlineStr">
@@ -11994,6 +12341,7 @@
       <c r="F183" s="40" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G183" s="2" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="40" t="inlineStr">
@@ -12015,11 +12363,12 @@
         <v>1</v>
       </c>
       <c r="E184" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F184" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G184" s="2" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="40" t="inlineStr">
@@ -12041,11 +12390,12 @@
         <v>1</v>
       </c>
       <c r="E185" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F185" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G185" s="2" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="40" t="inlineStr">
@@ -12067,11 +12417,12 @@
         <v>7</v>
       </c>
       <c r="E186" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F186" s="40" t="n">
         <v>-4.2</v>
       </c>
+      <c r="G186" s="2" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="39" t="inlineStr">
@@ -12098,6 +12449,7 @@
       <c r="F187" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G187" s="2" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="39" t="inlineStr">
@@ -12124,6 +12476,7 @@
       <c r="F188" s="39" t="n">
         <v>1</v>
       </c>
+      <c r="G188" s="2" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="40" t="inlineStr">
@@ -12150,6 +12503,7 @@
       <c r="F189" s="40" t="n">
         <v>-1</v>
       </c>
+      <c r="G189" s="2" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="40" t="inlineStr">
@@ -12171,11 +12525,12 @@
         <v>1</v>
       </c>
       <c r="E190" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F190" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G190" s="2" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="40" t="inlineStr">
@@ -12197,11 +12552,12 @@
         <v>1</v>
       </c>
       <c r="E191" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F191" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G191" s="2" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="40" t="inlineStr">
@@ -12223,11 +12579,12 @@
         <v>3</v>
       </c>
       <c r="E192" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F192" s="40" t="n">
         <v>-1.8</v>
       </c>
+      <c r="G192" s="2" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="40" t="inlineStr">
@@ -12249,11 +12606,12 @@
         <v>22</v>
       </c>
       <c r="E193" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F193" s="40" t="n">
         <v>-13.2</v>
       </c>
+      <c r="G193" s="2" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="39" t="inlineStr">
@@ -12280,6 +12638,7 @@
       <c r="F194" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G194" s="2" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="39" t="inlineStr">
@@ -12306,6 +12665,7 @@
       <c r="F195" s="39" t="n">
         <v>1</v>
       </c>
+      <c r="G195" s="2" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="40" t="inlineStr">
@@ -12332,6 +12692,7 @@
       <c r="F196" s="40" t="n">
         <v>-1</v>
       </c>
+      <c r="G196" s="2" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="40" t="inlineStr">
@@ -12353,11 +12714,12 @@
         <v>1</v>
       </c>
       <c r="E197" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F197" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G197" s="2" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="40" t="inlineStr">
@@ -12379,11 +12741,12 @@
         <v>1</v>
       </c>
       <c r="E198" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F198" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G198" s="2" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="40" t="inlineStr">
@@ -12405,11 +12768,12 @@
         <v>1</v>
       </c>
       <c r="E199" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F199" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G199" s="2" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="40" t="inlineStr">
@@ -12431,11 +12795,12 @@
         <v>17</v>
       </c>
       <c r="E200" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F200" s="40" t="n">
         <v>-10.2</v>
       </c>
+      <c r="G200" s="2" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="39" t="inlineStr">
@@ -12462,6 +12827,7 @@
       <c r="F201" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G201" s="2" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="39" t="inlineStr">
@@ -12488,6 +12854,7 @@
       <c r="F202" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G202" s="2" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="39" t="inlineStr">
@@ -12514,6 +12881,7 @@
       <c r="F203" s="39" t="n">
         <v>3</v>
       </c>
+      <c r="G203" s="2" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="39" t="inlineStr">
@@ -12540,6 +12908,7 @@
       <c r="F204" s="39" t="n">
         <v>1</v>
       </c>
+      <c r="G204" s="2" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="40" t="inlineStr">
@@ -12566,6 +12935,7 @@
       <c r="F205" s="40" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G205" s="2" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="39" t="inlineStr">
@@ -12592,6 +12962,7 @@
       <c r="F206" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G206" s="2" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="39" t="inlineStr">
@@ -12618,6 +12989,7 @@
       <c r="F207" s="39" t="n">
         <v>1</v>
       </c>
+      <c r="G207" s="2" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="40" t="inlineStr">
@@ -12644,6 +13016,7 @@
       <c r="F208" s="40" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G208" s="2" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="40" t="inlineStr">
@@ -12665,11 +13038,12 @@
         <v>2</v>
       </c>
       <c r="E209" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F209" s="40" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G209" s="2" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="40" t="inlineStr">
@@ -12691,11 +13065,12 @@
         <v>1</v>
       </c>
       <c r="E210" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F210" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G210" s="2" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="40" t="inlineStr">
@@ -12717,11 +13092,12 @@
         <v>2</v>
       </c>
       <c r="E211" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F211" s="40" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G211" s="2" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="39" t="inlineStr">
@@ -12748,6 +13124,7 @@
       <c r="F212" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G212" s="2" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="39" t="inlineStr">
@@ -12774,6 +13151,7 @@
       <c r="F213" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G213" s="2" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="39" t="inlineStr">
@@ -12800,6 +13178,7 @@
       <c r="F214" s="39" t="n">
         <v>3</v>
       </c>
+      <c r="G214" s="2" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="40" t="inlineStr">
@@ -12826,6 +13205,7 @@
       <c r="F215" s="40" t="n">
         <v>-1</v>
       </c>
+      <c r="G215" s="2" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="40" t="inlineStr">
@@ -12847,11 +13227,12 @@
         <v>1</v>
       </c>
       <c r="E216" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F216" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G216" s="2" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="40" t="inlineStr">
@@ -12873,11 +13254,12 @@
         <v>1</v>
       </c>
       <c r="E217" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F217" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G217" s="2" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="40" t="inlineStr">
@@ -12899,11 +13281,12 @@
         <v>1</v>
       </c>
       <c r="E218" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F218" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G218" s="2" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="39" t="inlineStr">
@@ -12930,6 +13313,7 @@
       <c r="F219" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G219" s="2" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="39" t="inlineStr">
@@ -12956,6 +13340,7 @@
       <c r="F220" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G220" s="2" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="40" t="inlineStr">
@@ -12982,6 +13367,7 @@
       <c r="F221" s="40" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G221" s="2" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="40" t="inlineStr">
@@ -13003,11 +13389,12 @@
         <v>1</v>
       </c>
       <c r="E222" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F222" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G222" s="2" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="39" t="inlineStr">
@@ -13034,6 +13421,7 @@
       <c r="F223" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G223" s="2" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="39" t="inlineStr">
@@ -13060,6 +13448,7 @@
       <c r="F224" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G224" s="2" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="39" t="inlineStr">
@@ -13086,6 +13475,7 @@
       <c r="F225" s="39" t="n">
         <v>1</v>
       </c>
+      <c r="G225" s="2" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="40" t="inlineStr">
@@ -13112,6 +13502,7 @@
       <c r="F226" s="40" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G226" s="2" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="40" t="inlineStr">
@@ -13133,11 +13524,12 @@
         <v>1</v>
       </c>
       <c r="E227" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F227" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G227" s="2" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="39" t="inlineStr">
@@ -13164,6 +13556,7 @@
       <c r="F228" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G228" s="2" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="39" t="inlineStr">
@@ -13190,6 +13583,7 @@
       <c r="F229" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G229" s="2" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="39" t="inlineStr">
@@ -13216,6 +13610,7 @@
       <c r="F230" s="39" t="n">
         <v>1</v>
       </c>
+      <c r="G230" s="2" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="40" t="inlineStr">
@@ -13242,6 +13637,7 @@
       <c r="F231" s="40" t="n">
         <v>-1</v>
       </c>
+      <c r="G231" s="2" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="40" t="inlineStr">
@@ -13263,11 +13659,12 @@
         <v>2</v>
       </c>
       <c r="E232" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F232" s="40" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G232" s="2" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="40" t="inlineStr">
@@ -13289,11 +13686,12 @@
         <v>1</v>
       </c>
       <c r="E233" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F233" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G233" s="2" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="39" t="inlineStr">
@@ -13320,6 +13718,7 @@
       <c r="F234" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G234" s="2" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="39" t="inlineStr">
@@ -13346,6 +13745,7 @@
       <c r="F235" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G235" s="2" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="39" t="inlineStr">
@@ -13372,6 +13772,7 @@
       <c r="F236" s="39" t="n">
         <v>1</v>
       </c>
+      <c r="G236" s="2" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="40" t="inlineStr">
@@ -13393,11 +13794,12 @@
         <v>1</v>
       </c>
       <c r="E237" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F237" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G237" s="2" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="39" t="inlineStr">
@@ -13424,6 +13826,7 @@
       <c r="F238" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G238" s="2" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="39" t="inlineStr">
@@ -13450,6 +13853,7 @@
       <c r="F239" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G239" s="2" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="39" t="inlineStr">
@@ -13476,6 +13880,7 @@
       <c r="F240" s="39" t="n">
         <v>2</v>
       </c>
+      <c r="G240" s="2" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="40" t="inlineStr">
@@ -13502,6 +13907,7 @@
       <c r="F241" s="40" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G241" s="2" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="40" t="inlineStr">
@@ -13523,11 +13929,12 @@
         <v>1</v>
       </c>
       <c r="E242" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F242" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G242" s="2" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="40" t="inlineStr">
@@ -13549,11 +13956,12 @@
         <v>1</v>
       </c>
       <c r="E243" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F243" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G243" s="2" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="39" t="inlineStr">
@@ -13580,6 +13988,7 @@
       <c r="F244" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G244" s="2" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="39" t="inlineStr">
@@ -13606,6 +14015,7 @@
       <c r="F245" s="39" t="n">
         <v>1</v>
       </c>
+      <c r="G245" s="2" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="40" t="inlineStr">
@@ -13632,6 +14042,7 @@
       <c r="F246" s="40" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G246" s="2" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="40" t="inlineStr">
@@ -13653,11 +14064,12 @@
         <v>1</v>
       </c>
       <c r="E247" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F247" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G247" s="2" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="40" t="inlineStr">
@@ -13679,11 +14091,12 @@
         <v>1</v>
       </c>
       <c r="E248" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F248" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G248" s="2" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="40" t="inlineStr">
@@ -13705,11 +14118,12 @@
         <v>1</v>
       </c>
       <c r="E249" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F249" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G249" s="2" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="40" t="inlineStr">
@@ -13731,11 +14145,12 @@
         <v>8</v>
       </c>
       <c r="E250" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F250" s="40" t="n">
         <v>-4.8</v>
       </c>
+      <c r="G250" s="2" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="39" t="inlineStr">
@@ -13762,6 +14177,7 @@
       <c r="F251" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G251" s="2" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="40" t="inlineStr">
@@ -13788,6 +14204,7 @@
       <c r="F252" s="40" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G252" s="2" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="40" t="inlineStr">
@@ -13809,11 +14226,12 @@
         <v>1</v>
       </c>
       <c r="E253" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F253" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G253" s="2" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="40" t="inlineStr">
@@ -13835,11 +14253,12 @@
         <v>4</v>
       </c>
       <c r="E254" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F254" s="40" t="n">
         <v>-2.4</v>
       </c>
+      <c r="G254" s="2" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="39" t="inlineStr">
@@ -13866,6 +14285,7 @@
       <c r="F255" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G255" s="2" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="39" t="inlineStr">
@@ -13892,6 +14312,7 @@
       <c r="F256" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G256" s="2" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="40" t="inlineStr">
@@ -13918,6 +14339,7 @@
       <c r="F257" s="40" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G257" s="2" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="40" t="inlineStr">
@@ -13939,11 +14361,12 @@
         <v>1</v>
       </c>
       <c r="E258" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F258" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G258" s="2" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="39" t="inlineStr">
@@ -13970,6 +14393,7 @@
       <c r="F259" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G259" s="2" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="39" t="inlineStr">
@@ -13996,6 +14420,7 @@
       <c r="F260" s="39" t="n">
         <v>5</v>
       </c>
+      <c r="G260" s="2" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="40" t="inlineStr">
@@ -14022,6 +14447,7 @@
       <c r="F261" s="40" t="n">
         <v>-1</v>
       </c>
+      <c r="G261" s="2" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="40" t="inlineStr">
@@ -14043,11 +14469,12 @@
         <v>1</v>
       </c>
       <c r="E262" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F262" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G262" s="2" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="40" t="inlineStr">
@@ -14069,11 +14496,12 @@
         <v>2</v>
       </c>
       <c r="E263" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F263" s="40" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G263" s="2" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="40" t="inlineStr">
@@ -14095,17 +14523,18 @@
         <v>1</v>
       </c>
       <c r="E264" s="40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F264" s="40" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G264" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:E41"/>
+  <autoFilter ref="A2:G41"/>
   <mergeCells count="2">
     <mergeCell ref="A44:F44"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/historico/semana_318.xlsx
+++ b/data/historico/semana_318.xlsx
@@ -33,7 +33,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$G$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$H$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -7360,16 +7360,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G264"/>
+  <dimension ref="A1:H264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="29" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -7384,6 +7385,7 @@
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -7413,10 +7415,15 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
+          <t>Turnos Sem Trabalhar</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>Pontuação Final</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
@@ -7440,12 +7447,15 @@
         <v>4</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="F3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7469,12 +7479,15 @@
         <v>3</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="F4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7498,12 +7511,15 @@
         <v>2</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="F5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7527,12 +7543,15 @@
         <v>2</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="F6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7556,12 +7575,15 @@
         <v>2</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="F7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7585,12 +7607,15 @@
         <v>4</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="F8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7602,7 +7627,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -7611,15 +7636,18 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7631,24 +7659,27 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Bianca Afonso Narbaez</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7660,24 +7691,27 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Cicero Isrrael Sanabria</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="F11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7689,7 +7723,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Bianca Afonso Narbaez</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -7701,12 +7735,15 @@
         <v>1</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7718,7 +7755,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Cicero Isrrael Sanabria</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -7730,12 +7767,15 @@
         <v>2</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7747,7 +7787,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -7759,12 +7799,15 @@
         <v>1</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7776,7 +7819,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Tania Maria Montania</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -7785,15 +7828,18 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7805,7 +7851,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Wesley de Souza Leal</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -7817,12 +7863,15 @@
         <v>1</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7834,7 +7883,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Tania Maria Montania</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -7843,15 +7892,18 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7863,24 +7915,27 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Wesley de Souza Leal</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7892,24 +7947,27 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7921,7 +7979,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Geancarlos Ferreira Barrios</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -7930,15 +7988,18 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7950,7 +8011,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -7959,15 +8020,18 @@
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7979,7 +8043,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Geancarlos Ferreira Barrios</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -7988,15 +8052,18 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -8008,7 +8075,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -8017,15 +8084,18 @@
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -8037,7 +8107,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Rosalina Beniel Vargas</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -8046,15 +8116,18 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -8066,7 +8139,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -8078,12 +8151,15 @@
         <v>2</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -8095,24 +8171,27 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="F26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -8124,24 +8203,27 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D27" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="F27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -8153,7 +8235,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -8162,15 +8244,18 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="F28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -8182,7 +8267,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -8191,15 +8276,18 @@
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="F29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="H29" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -8211,7 +8299,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -8220,15 +8308,18 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="F30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -8240,7 +8331,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -8252,12 +8343,15 @@
         <v>1</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="F31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -8269,7 +8363,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -8281,12 +8375,15 @@
         <v>2</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>99.5</v>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -8298,7 +8395,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -8310,12 +8407,15 @@
         <v>1</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -8327,24 +8427,27 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -8356,24 +8459,27 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D35" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -8397,12 +8503,15 @@
         <v>3</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>99.33</v>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -8414,24 +8523,27 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Raquel Ortiz dos Santos</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D37" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>93</v>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>98</v>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -8443,113 +8555,125 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Raquel Ortiz dos Santos</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>97.83</v>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>🟢 EXCELENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Anderson Jose de Santana</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="D39" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E38" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="F38" s="4" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
+      <c r="E39" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>95.88</v>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="6" t="n">
-        <v>37</v>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Ramona dos Santos Oliveira</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>95.17</v>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>🟢 EXCELENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Mateus Falcao de Souza</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D41" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E39" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="F39" s="6" t="n">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="G39" s="6" t="inlineStr">
-        <is>
-          <t>🟡 BOM</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>Ramona dos Santos Oliveira</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E40" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="F40" s="6" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="G40" s="6" t="inlineStr">
-        <is>
-          <t>🟡 BOM</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>Anderson Jose de Santana</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E41" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="F41" s="6" t="n">
-        <v>85.3</v>
-      </c>
-      <c r="G41" s="6" t="inlineStr">
-        <is>
-          <t>🟡 BOM</t>
+      <c r="E41" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>🟢 EXCELENTE</t>
         </is>
       </c>
     </row>
@@ -8561,6 +8685,7 @@
       <c r="E42" s="2" t="n"/>
       <c r="F42" s="2" t="n"/>
       <c r="G42" s="2" t="n"/>
+      <c r="H42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>
@@ -8570,6 +8695,7 @@
       <c r="E43" s="2" t="n"/>
       <c r="F43" s="2" t="n"/>
       <c r="G43" s="2" t="n"/>
+      <c r="H43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="38" t="inlineStr">
@@ -8583,6 +8709,7 @@
       <c r="E44" s="2" t="n"/>
       <c r="F44" s="2" t="n"/>
       <c r="G44" s="2" t="n"/>
+      <c r="H44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -8607,15 +8734,24 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Peso (pontos/ocorrência)</t>
+          <t>Peso Nominal (tabela de critérios)</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
+          <t>Fator de Normalização</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>Peso Efetivo (nominal × fator)</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
           <t>Pontos Aplicados</t>
         </is>
       </c>
-      <c r="G45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="39" t="inlineStr">
@@ -8640,9 +8776,14 @@
         <v>5</v>
       </c>
       <c r="F46" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G46" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G46" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H46" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="39" t="inlineStr">
@@ -8667,9 +8808,14 @@
         <v>5</v>
       </c>
       <c r="F47" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G47" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G47" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H47" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="39" t="inlineStr">
@@ -8694,9 +8840,14 @@
         <v>1</v>
       </c>
       <c r="F48" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="G48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="40" t="inlineStr">
@@ -8721,9 +8872,14 @@
         <v>0.5</v>
       </c>
       <c r="F49" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H49" s="40" t="n">
         <v>-1</v>
       </c>
-      <c r="G49" s="2" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="40" t="inlineStr">
@@ -8745,12 +8901,17 @@
         <v>1</v>
       </c>
       <c r="E50" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F50" s="40" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G50" s="2" t="n"/>
+        <v>1.25</v>
+      </c>
+      <c r="G50" s="40" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="H50" s="40" t="n">
+        <v>-0.38</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="40" t="inlineStr">
@@ -8772,12 +8933,17 @@
         <v>2</v>
       </c>
       <c r="E51" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F51" s="40" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="G51" s="2" t="n"/>
+        <v>1.25</v>
+      </c>
+      <c r="G51" s="40" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="H51" s="40" t="n">
+        <v>-0.75</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="39" t="inlineStr">
@@ -8802,9 +8968,14 @@
         <v>5</v>
       </c>
       <c r="F52" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G52" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G52" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H52" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="39" t="inlineStr">
@@ -8831,7 +9002,12 @@
       <c r="F53" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="G53" s="2" t="n"/>
+      <c r="G53" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" s="39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="40" t="inlineStr">
@@ -8856,9 +9032,14 @@
         <v>0.5</v>
       </c>
       <c r="F54" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H54" s="40" t="n">
         <v>-1</v>
       </c>
-      <c r="G54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="40" t="inlineStr">
@@ -8880,12 +9061,17 @@
         <v>1</v>
       </c>
       <c r="E55" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F55" s="40" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G55" s="2" t="n"/>
+        <v>1.667</v>
+      </c>
+      <c r="G55" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H55" s="40" t="n">
+        <v>-0.5</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="40" t="inlineStr">
@@ -8907,12 +9093,17 @@
         <v>1</v>
       </c>
       <c r="E56" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F56" s="40" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G56" s="2" t="n"/>
+        <v>1.667</v>
+      </c>
+      <c r="G56" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H56" s="40" t="n">
+        <v>-0.5</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="40" t="inlineStr">
@@ -8934,12 +9125,17 @@
         <v>1</v>
       </c>
       <c r="E57" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F57" s="40" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G57" s="2" t="n"/>
+        <v>1.667</v>
+      </c>
+      <c r="G57" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H57" s="40" t="n">
+        <v>-0.5</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="40" t="inlineStr">
@@ -8961,12 +9157,17 @@
         <v>3</v>
       </c>
       <c r="E58" s="40" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F58" s="40" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="G58" s="2" t="n"/>
+        <v>1.667</v>
+      </c>
+      <c r="G58" s="40" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="H58" s="40" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="39" t="inlineStr">
@@ -8991,9 +9192,14 @@
         <v>5</v>
       </c>
       <c r="F59" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G59" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G59" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H59" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="39" t="inlineStr">
@@ -9018,9 +9224,14 @@
         <v>5</v>
       </c>
       <c r="F60" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G60" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G60" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H60" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="39" t="inlineStr">
@@ -9047,7 +9258,12 @@
       <c r="F61" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="G61" s="2" t="n"/>
+      <c r="G61" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" s="39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="40" t="inlineStr">
@@ -9072,9 +9288,14 @@
         <v>0.5</v>
       </c>
       <c r="F62" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H62" s="40" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G62" s="2" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="40" t="inlineStr">
@@ -9096,12 +9317,17 @@
         <v>1</v>
       </c>
       <c r="E63" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F63" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G63" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="F63" s="40" t="n">
+      <c r="H63" s="40" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="40" t="inlineStr">
@@ -9123,12 +9349,17 @@
         <v>1</v>
       </c>
       <c r="E64" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F64" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G64" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="F64" s="40" t="n">
+      <c r="H64" s="40" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G64" s="2" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="39" t="inlineStr">
@@ -9153,9 +9384,14 @@
         <v>5</v>
       </c>
       <c r="F65" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G65" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G65" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H65" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="39" t="inlineStr">
@@ -9182,7 +9418,12 @@
       <c r="F66" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="G66" s="2" t="n"/>
+      <c r="G66" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" s="39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="40" t="inlineStr">
@@ -9207,9 +9448,14 @@
         <v>0.5</v>
       </c>
       <c r="F67" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H67" s="40" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G67" s="2" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="40" t="inlineStr">
@@ -9231,12 +9477,17 @@
         <v>1</v>
       </c>
       <c r="E68" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F68" s="40" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G68" s="2" t="n"/>
+        <v>1.25</v>
+      </c>
+      <c r="G68" s="40" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="H68" s="40" t="n">
+        <v>-0.38</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="40" t="inlineStr">
@@ -9258,12 +9509,17 @@
         <v>3</v>
       </c>
       <c r="E69" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F69" s="40" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="G69" s="2" t="n"/>
+        <v>1.25</v>
+      </c>
+      <c r="G69" s="40" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="H69" s="40" t="n">
+        <v>-1.12</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="40" t="inlineStr">
@@ -9285,12 +9541,17 @@
         <v>1</v>
       </c>
       <c r="E70" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F70" s="40" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G70" s="2" t="n"/>
+        <v>1.25</v>
+      </c>
+      <c r="G70" s="40" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="H70" s="40" t="n">
+        <v>-0.38</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="40" t="inlineStr">
@@ -9312,12 +9573,17 @@
         <v>27</v>
       </c>
       <c r="E71" s="40" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F71" s="40" t="n">
-        <v>-16.2</v>
-      </c>
-      <c r="G71" s="2" t="n"/>
+        <v>1.25</v>
+      </c>
+      <c r="G71" s="40" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H71" s="40" t="n">
+        <v>-6.75</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="39" t="inlineStr">
@@ -9342,9 +9608,14 @@
         <v>5</v>
       </c>
       <c r="F72" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G72" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G72" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H72" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="39" t="inlineStr">
@@ -9369,9 +9640,14 @@
         <v>5</v>
       </c>
       <c r="F73" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G73" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G73" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H73" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="39" t="inlineStr">
@@ -9396,9 +9672,14 @@
         <v>3</v>
       </c>
       <c r="F74" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="G74" s="2" t="n"/>
+      <c r="H74" s="39" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="40" t="inlineStr">
@@ -9423,9 +9704,14 @@
         <v>0.5</v>
       </c>
       <c r="F75" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H75" s="40" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G75" s="2" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="39" t="inlineStr">
@@ -9450,9 +9736,14 @@
         <v>5</v>
       </c>
       <c r="F76" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G76" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G76" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H76" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="39" t="inlineStr">
@@ -9477,9 +9768,14 @@
         <v>5</v>
       </c>
       <c r="F77" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G77" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G77" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H77" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="40" t="inlineStr">
@@ -9504,9 +9800,14 @@
         <v>0.5</v>
       </c>
       <c r="F78" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H78" s="40" t="n">
         <v>-1</v>
       </c>
-      <c r="G78" s="2" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="40" t="inlineStr">
@@ -9528,12 +9829,17 @@
         <v>1</v>
       </c>
       <c r="E79" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F79" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G79" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="F79" s="40" t="n">
+      <c r="H79" s="40" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G79" s="2" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="40" t="inlineStr">
@@ -9555,12 +9861,17 @@
         <v>1</v>
       </c>
       <c r="E80" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F80" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G80" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="F80" s="40" t="n">
+      <c r="H80" s="40" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G80" s="2" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="39" t="inlineStr">
@@ -9585,9 +9896,14 @@
         <v>5</v>
       </c>
       <c r="F81" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G81" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G81" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H81" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="39" t="inlineStr">
@@ -9612,9 +9928,14 @@
         <v>5</v>
       </c>
       <c r="F82" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G82" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G82" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H82" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="40" t="inlineStr">
@@ -9639,9 +9960,14 @@
         <v>0.5</v>
       </c>
       <c r="F83" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H83" s="40" t="n">
         <v>-1</v>
       </c>
-      <c r="G83" s="2" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="40" t="inlineStr">
@@ -9663,12 +9989,17 @@
         <v>2</v>
       </c>
       <c r="E84" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F84" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G84" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="F84" s="40" t="n">
+      <c r="H84" s="40" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G84" s="2" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="40" t="inlineStr">
@@ -9690,12 +10021,17 @@
         <v>1</v>
       </c>
       <c r="E85" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F85" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G85" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="F85" s="40" t="n">
+      <c r="H85" s="40" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G85" s="2" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="39" t="inlineStr">
@@ -9720,9 +10056,14 @@
         <v>5</v>
       </c>
       <c r="F86" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G86" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G86" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H86" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="39" t="inlineStr">
@@ -9747,9 +10088,14 @@
         <v>5</v>
       </c>
       <c r="F87" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G87" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G87" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H87" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="40" t="inlineStr">
@@ -9774,9 +10120,14 @@
         <v>0.5</v>
       </c>
       <c r="F88" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H88" s="40" t="n">
         <v>-1</v>
       </c>
-      <c r="G88" s="2" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="40" t="inlineStr">
@@ -9798,12 +10149,17 @@
         <v>1</v>
       </c>
       <c r="E89" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F89" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G89" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="F89" s="40" t="n">
+      <c r="H89" s="40" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G89" s="2" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="39" t="inlineStr">
@@ -9828,9 +10184,14 @@
         <v>5</v>
       </c>
       <c r="F90" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G90" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G90" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H90" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="39" t="inlineStr">
@@ -9855,9 +10216,14 @@
         <v>5</v>
       </c>
       <c r="F91" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G91" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G91" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H91" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="39" t="inlineStr">
@@ -9884,7 +10250,12 @@
       <c r="F92" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="G92" s="2" t="n"/>
+      <c r="G92" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" s="39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="40" t="inlineStr">
@@ -9909,9 +10280,14 @@
         <v>0.5</v>
       </c>
       <c r="F93" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H93" s="40" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G93" s="2" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="40" t="inlineStr">
@@ -9933,12 +10309,17 @@
         <v>1</v>
       </c>
       <c r="E94" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F94" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G94" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="F94" s="40" t="n">
+      <c r="H94" s="40" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G94" s="2" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="39" t="inlineStr">
@@ -9963,9 +10344,14 @@
         <v>5</v>
       </c>
       <c r="F95" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G95" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G95" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H95" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="40" t="inlineStr">
@@ -9990,9 +10376,14 @@
         <v>0.5</v>
       </c>
       <c r="F96" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H96" s="40" t="n">
         <v>-1</v>
       </c>
-      <c r="G96" s="2" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="40" t="inlineStr">
@@ -10014,12 +10405,17 @@
         <v>1</v>
       </c>
       <c r="E97" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F97" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G97" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="F97" s="40" t="n">
+      <c r="H97" s="40" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G97" s="2" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="40" t="inlineStr">
@@ -10041,12 +10437,17 @@
         <v>1</v>
       </c>
       <c r="E98" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F98" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G98" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="F98" s="40" t="n">
+      <c r="H98" s="40" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G98" s="2" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="40" t="inlineStr">
@@ -10068,12 +10469,17 @@
         <v>1</v>
       </c>
       <c r="E99" s="40" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F99" s="40" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G99" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G99" s="40" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H99" s="40" t="n">
+        <v>-0.4</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="39" t="inlineStr">
@@ -10098,9 +10504,14 @@
         <v>5</v>
       </c>
       <c r="F100" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G100" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G100" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H100" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="39" t="inlineStr">
@@ -10125,9 +10536,14 @@
         <v>5</v>
       </c>
       <c r="F101" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G101" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G101" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H101" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="40" t="inlineStr">
@@ -10152,9 +10568,14 @@
         <v>0.5</v>
       </c>
       <c r="F102" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H102" s="40" t="n">
         <v>-2</v>
       </c>
-      <c r="G102" s="2" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="40" t="inlineStr">
@@ -10176,12 +10597,17 @@
         <v>1</v>
       </c>
       <c r="E103" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F103" s="40" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G103" s="2" t="n"/>
+        <v>1.25</v>
+      </c>
+      <c r="G103" s="40" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="H103" s="40" t="n">
+        <v>-0.38</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="40" t="inlineStr">
@@ -10203,12 +10629,17 @@
         <v>2</v>
       </c>
       <c r="E104" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F104" s="40" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="G104" s="2" t="n"/>
+        <v>1.25</v>
+      </c>
+      <c r="G104" s="40" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="H104" s="40" t="n">
+        <v>-0.75</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="40" t="inlineStr">
@@ -10230,12 +10661,17 @@
         <v>2</v>
       </c>
       <c r="E105" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F105" s="40" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="G105" s="2" t="n"/>
+        <v>1.25</v>
+      </c>
+      <c r="G105" s="40" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="H105" s="40" t="n">
+        <v>-0.75</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="40" t="inlineStr">
@@ -10257,12 +10693,17 @@
         <v>3</v>
       </c>
       <c r="E106" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F106" s="40" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="G106" s="2" t="n"/>
+        <v>1.25</v>
+      </c>
+      <c r="G106" s="40" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="H106" s="40" t="n">
+        <v>-1.12</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="39" t="inlineStr">
@@ -10287,9 +10728,14 @@
         <v>5</v>
       </c>
       <c r="F107" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G107" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G107" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H107" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="39" t="inlineStr">
@@ -10314,9 +10760,14 @@
         <v>5</v>
       </c>
       <c r="F108" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G108" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G108" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H108" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="39" t="inlineStr">
@@ -10341,9 +10792,14 @@
         <v>3</v>
       </c>
       <c r="F109" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="G109" s="2" t="n"/>
+      <c r="H109" s="39" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="39" t="inlineStr">
@@ -10370,7 +10826,12 @@
       <c r="F110" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="G110" s="2" t="n"/>
+      <c r="G110" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H110" s="39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="39" t="inlineStr">
@@ -10395,9 +10856,14 @@
         <v>5</v>
       </c>
       <c r="F111" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G111" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G111" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H111" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="40" t="inlineStr">
@@ -10422,9 +10888,14 @@
         <v>0.5</v>
       </c>
       <c r="F112" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H112" s="40" t="n">
         <v>-2</v>
       </c>
-      <c r="G112" s="2" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="40" t="inlineStr">
@@ -10446,12 +10917,17 @@
         <v>1</v>
       </c>
       <c r="E113" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F113" s="40" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G113" s="2" t="n"/>
+        <v>1.25</v>
+      </c>
+      <c r="G113" s="40" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="H113" s="40" t="n">
+        <v>-0.38</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="40" t="inlineStr">
@@ -10473,12 +10949,17 @@
         <v>2</v>
       </c>
       <c r="E114" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F114" s="40" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="G114" s="2" t="n"/>
+        <v>1.25</v>
+      </c>
+      <c r="G114" s="40" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="H114" s="40" t="n">
+        <v>-0.75</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="40" t="inlineStr">
@@ -10500,12 +10981,17 @@
         <v>3</v>
       </c>
       <c r="E115" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F115" s="40" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="G115" s="2" t="n"/>
+        <v>1.25</v>
+      </c>
+      <c r="G115" s="40" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="H115" s="40" t="n">
+        <v>-1.12</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="40" t="inlineStr">
@@ -10527,12 +11013,17 @@
         <v>1</v>
       </c>
       <c r="E116" s="40" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F116" s="40" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G116" s="2" t="n"/>
+        <v>1.25</v>
+      </c>
+      <c r="G116" s="40" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H116" s="40" t="n">
+        <v>-0.25</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="39" t="inlineStr">
@@ -10557,9 +11048,14 @@
         <v>5</v>
       </c>
       <c r="F117" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G117" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G117" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H117" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="39" t="inlineStr">
@@ -10584,9 +11080,14 @@
         <v>5</v>
       </c>
       <c r="F118" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G118" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G118" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H118" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="39" t="inlineStr">
@@ -10611,9 +11112,14 @@
         <v>1</v>
       </c>
       <c r="F119" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H119" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="G119" s="2" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="40" t="inlineStr">
@@ -10638,9 +11144,14 @@
         <v>0.5</v>
       </c>
       <c r="F120" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H120" s="40" t="n">
         <v>-1</v>
       </c>
-      <c r="G120" s="2" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="40" t="inlineStr">
@@ -10662,12 +11173,17 @@
         <v>1</v>
       </c>
       <c r="E121" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F121" s="40" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G121" s="2" t="n"/>
+        <v>1.25</v>
+      </c>
+      <c r="G121" s="40" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="H121" s="40" t="n">
+        <v>-0.38</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="40" t="inlineStr">
@@ -10689,12 +11205,17 @@
         <v>1</v>
       </c>
       <c r="E122" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F122" s="40" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G122" s="2" t="n"/>
+        <v>1.25</v>
+      </c>
+      <c r="G122" s="40" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="H122" s="40" t="n">
+        <v>-0.38</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="40" t="inlineStr">
@@ -10716,12 +11237,17 @@
         <v>2</v>
       </c>
       <c r="E123" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F123" s="40" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="G123" s="2" t="n"/>
+        <v>1.25</v>
+      </c>
+      <c r="G123" s="40" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="H123" s="40" t="n">
+        <v>-0.75</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="39" t="inlineStr">
@@ -10746,9 +11272,14 @@
         <v>5</v>
       </c>
       <c r="F124" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G124" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G124" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H124" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="39" t="inlineStr">
@@ -10773,9 +11304,14 @@
         <v>5</v>
       </c>
       <c r="F125" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G125" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G125" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H125" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="39" t="inlineStr">
@@ -10800,9 +11336,14 @@
         <v>3</v>
       </c>
       <c r="F126" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="G126" s="2" t="n"/>
+      <c r="H126" s="39" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="40" t="inlineStr">
@@ -10827,9 +11368,14 @@
         <v>0.5</v>
       </c>
       <c r="F127" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H127" s="40" t="n">
         <v>-1</v>
       </c>
-      <c r="G127" s="2" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="39" t="inlineStr">
@@ -10854,9 +11400,14 @@
         <v>5</v>
       </c>
       <c r="F128" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G128" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G128" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H128" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="39" t="inlineStr">
@@ -10881,9 +11432,14 @@
         <v>5</v>
       </c>
       <c r="F129" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G129" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G129" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H129" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="39" t="inlineStr">
@@ -10910,7 +11466,12 @@
       <c r="F130" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="G130" s="2" t="n"/>
+      <c r="G130" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H130" s="39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="40" t="inlineStr">
@@ -10935,9 +11496,14 @@
         <v>0.5</v>
       </c>
       <c r="F131" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G131" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H131" s="40" t="n">
         <v>-1</v>
       </c>
-      <c r="G131" s="2" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="40" t="inlineStr">
@@ -10959,12 +11525,17 @@
         <v>2</v>
       </c>
       <c r="E132" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F132" s="40" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="G132" s="2" t="n"/>
+        <v>1.667</v>
+      </c>
+      <c r="G132" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H132" s="40" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="40" t="inlineStr">
@@ -10986,12 +11557,17 @@
         <v>1</v>
       </c>
       <c r="E133" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F133" s="40" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G133" s="2" t="n"/>
+        <v>1.667</v>
+      </c>
+      <c r="G133" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H133" s="40" t="n">
+        <v>-0.5</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="40" t="inlineStr">
@@ -11013,12 +11589,17 @@
         <v>2</v>
       </c>
       <c r="E134" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F134" s="40" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="G134" s="2" t="n"/>
+        <v>1.667</v>
+      </c>
+      <c r="G134" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H134" s="40" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="39" t="inlineStr">
@@ -11043,9 +11624,14 @@
         <v>5</v>
       </c>
       <c r="F135" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G135" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G135" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H135" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="40" t="inlineStr">
@@ -11070,9 +11656,14 @@
         <v>0.5</v>
       </c>
       <c r="F136" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H136" s="40" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G136" s="2" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="40" t="inlineStr">
@@ -11094,12 +11685,17 @@
         <v>1</v>
       </c>
       <c r="E137" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F137" s="40" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G137" s="2" t="n"/>
+        <v>1.667</v>
+      </c>
+      <c r="G137" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H137" s="40" t="n">
+        <v>-0.5</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="40" t="inlineStr">
@@ -11121,12 +11717,17 @@
         <v>1</v>
       </c>
       <c r="E138" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F138" s="40" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G138" s="2" t="n"/>
+        <v>1.667</v>
+      </c>
+      <c r="G138" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H138" s="40" t="n">
+        <v>-0.5</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="40" t="inlineStr">
@@ -11148,12 +11749,17 @@
         <v>1</v>
       </c>
       <c r="E139" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F139" s="40" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G139" s="2" t="n"/>
+        <v>1.667</v>
+      </c>
+      <c r="G139" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H139" s="40" t="n">
+        <v>-0.5</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="40" t="inlineStr">
@@ -11175,12 +11781,17 @@
         <v>8</v>
       </c>
       <c r="E140" s="40" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F140" s="40" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="G140" s="2" t="n"/>
+        <v>1.667</v>
+      </c>
+      <c r="G140" s="40" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="H140" s="40" t="n">
+        <v>-2.67</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="39" t="inlineStr">
@@ -11205,9 +11816,14 @@
         <v>5</v>
       </c>
       <c r="F141" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G141" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G141" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H141" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="40" t="inlineStr">
@@ -11232,9 +11848,14 @@
         <v>0.5</v>
       </c>
       <c r="F142" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H142" s="40" t="n">
         <v>-2</v>
       </c>
-      <c r="G142" s="2" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="40" t="inlineStr">
@@ -11256,12 +11877,17 @@
         <v>3</v>
       </c>
       <c r="E143" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F143" s="40" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="G143" s="2" t="n"/>
+        <v>1.25</v>
+      </c>
+      <c r="G143" s="40" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="H143" s="40" t="n">
+        <v>-1.12</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="40" t="inlineStr">
@@ -11283,12 +11909,17 @@
         <v>1</v>
       </c>
       <c r="E144" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F144" s="40" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G144" s="2" t="n"/>
+        <v>1.25</v>
+      </c>
+      <c r="G144" s="40" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="H144" s="40" t="n">
+        <v>-0.38</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="40" t="inlineStr">
@@ -11310,12 +11941,17 @@
         <v>2</v>
       </c>
       <c r="E145" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F145" s="40" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="G145" s="2" t="n"/>
+        <v>1.25</v>
+      </c>
+      <c r="G145" s="40" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="H145" s="40" t="n">
+        <v>-0.75</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="40" t="inlineStr">
@@ -11337,12 +11973,17 @@
         <v>11</v>
       </c>
       <c r="E146" s="40" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F146" s="40" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="G146" s="2" t="n"/>
+        <v>1.25</v>
+      </c>
+      <c r="G146" s="40" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H146" s="40" t="n">
+        <v>-2.75</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="39" t="inlineStr">
@@ -11367,9 +12008,14 @@
         <v>5</v>
       </c>
       <c r="F147" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G147" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G147" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H147" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="39" t="inlineStr">
@@ -11396,7 +12042,12 @@
       <c r="F148" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="G148" s="2" t="n"/>
+      <c r="G148" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H148" s="39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="40" t="inlineStr">
@@ -11421,9 +12072,14 @@
         <v>0.5</v>
       </c>
       <c r="F149" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G149" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H149" s="40" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G149" s="2" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="40" t="inlineStr">
@@ -11445,12 +12101,17 @@
         <v>1</v>
       </c>
       <c r="E150" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F150" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G150" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="F150" s="40" t="n">
+      <c r="H150" s="40" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G150" s="2" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="40" t="inlineStr">
@@ -11472,12 +12133,17 @@
         <v>9</v>
       </c>
       <c r="E151" s="40" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F151" s="40" t="n">
-        <v>-5.4</v>
-      </c>
-      <c r="G151" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G151" s="40" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H151" s="40" t="n">
+        <v>-3.6</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="39" t="inlineStr">
@@ -11502,9 +12168,14 @@
         <v>5</v>
       </c>
       <c r="F152" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G152" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G152" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H152" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="39" t="inlineStr">
@@ -11531,7 +12202,12 @@
       <c r="F153" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="G153" s="2" t="n"/>
+      <c r="G153" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H153" s="39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="40" t="inlineStr">
@@ -11556,9 +12232,14 @@
         <v>0.5</v>
       </c>
       <c r="F154" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G154" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H154" s="40" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G154" s="2" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="40" t="inlineStr">
@@ -11580,12 +12261,17 @@
         <v>1</v>
       </c>
       <c r="E155" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F155" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G155" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="F155" s="40" t="n">
+      <c r="H155" s="40" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G155" s="2" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="40" t="inlineStr">
@@ -11607,12 +12293,17 @@
         <v>2</v>
       </c>
       <c r="E156" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F156" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G156" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="F156" s="40" t="n">
+      <c r="H156" s="40" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G156" s="2" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="40" t="inlineStr">
@@ -11634,12 +12325,17 @@
         <v>5</v>
       </c>
       <c r="E157" s="40" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F157" s="40" t="n">
-        <v>-3</v>
-      </c>
-      <c r="G157" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G157" s="40" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H157" s="40" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="39" t="inlineStr">
@@ -11664,9 +12360,14 @@
         <v>5</v>
       </c>
       <c r="F158" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G158" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G158" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H158" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="39" t="inlineStr">
@@ -11693,7 +12394,12 @@
       <c r="F159" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="G159" s="2" t="n"/>
+      <c r="G159" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H159" s="39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="40" t="inlineStr">
@@ -11718,9 +12424,14 @@
         <v>0.5</v>
       </c>
       <c r="F160" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G160" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H160" s="40" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G160" s="2" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="40" t="inlineStr">
@@ -11742,12 +12453,17 @@
         <v>1</v>
       </c>
       <c r="E161" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F161" s="40" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G161" s="2" t="n"/>
+        <v>1.25</v>
+      </c>
+      <c r="G161" s="40" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="H161" s="40" t="n">
+        <v>-0.38</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="40" t="inlineStr">
@@ -11769,12 +12485,17 @@
         <v>1</v>
       </c>
       <c r="E162" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F162" s="40" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G162" s="2" t="n"/>
+        <v>1.25</v>
+      </c>
+      <c r="G162" s="40" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="H162" s="40" t="n">
+        <v>-0.38</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="40" t="inlineStr">
@@ -11796,12 +12517,17 @@
         <v>1</v>
       </c>
       <c r="E163" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F163" s="40" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G163" s="2" t="n"/>
+        <v>1.25</v>
+      </c>
+      <c r="G163" s="40" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="H163" s="40" t="n">
+        <v>-0.38</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="40" t="inlineStr">
@@ -11823,12 +12549,17 @@
         <v>3</v>
       </c>
       <c r="E164" s="40" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F164" s="40" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="G164" s="2" t="n"/>
+        <v>1.25</v>
+      </c>
+      <c r="G164" s="40" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H164" s="40" t="n">
+        <v>-0.75</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="39" t="inlineStr">
@@ -11853,9 +12584,14 @@
         <v>5</v>
       </c>
       <c r="F165" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G165" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G165" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H165" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="39" t="inlineStr">
@@ -11882,7 +12618,12 @@
       <c r="F166" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="G166" s="2" t="n"/>
+      <c r="G166" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H166" s="39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="40" t="inlineStr">
@@ -11907,9 +12648,14 @@
         <v>0.5</v>
       </c>
       <c r="F167" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G167" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H167" s="40" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G167" s="2" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="40" t="inlineStr">
@@ -11931,12 +12677,17 @@
         <v>1</v>
       </c>
       <c r="E168" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F168" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G168" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="F168" s="40" t="n">
+      <c r="H168" s="40" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G168" s="2" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="40" t="inlineStr">
@@ -11958,12 +12709,17 @@
         <v>1</v>
       </c>
       <c r="E169" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F169" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G169" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="F169" s="40" t="n">
+      <c r="H169" s="40" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G169" s="2" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="40" t="inlineStr">
@@ -11985,12 +12741,17 @@
         <v>1</v>
       </c>
       <c r="E170" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F170" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G170" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="F170" s="40" t="n">
+      <c r="H170" s="40" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G170" s="2" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="40" t="inlineStr">
@@ -12012,12 +12773,17 @@
         <v>23</v>
       </c>
       <c r="E171" s="40" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F171" s="40" t="n">
-        <v>-13.8</v>
-      </c>
-      <c r="G171" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G171" s="40" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H171" s="40" t="n">
+        <v>-9.199999999999999</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="39" t="inlineStr">
@@ -12042,9 +12808,14 @@
         <v>5</v>
       </c>
       <c r="F172" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G172" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G172" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H172" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="39" t="inlineStr">
@@ -12071,7 +12842,12 @@
       <c r="F173" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="G173" s="2" t="n"/>
+      <c r="G173" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H173" s="39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="40" t="inlineStr">
@@ -12096,9 +12872,14 @@
         <v>0.5</v>
       </c>
       <c r="F174" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G174" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H174" s="40" t="n">
         <v>-1</v>
       </c>
-      <c r="G174" s="2" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="40" t="inlineStr">
@@ -12120,12 +12901,17 @@
         <v>1</v>
       </c>
       <c r="E175" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F175" s="40" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G175" s="2" t="n"/>
+        <v>1.667</v>
+      </c>
+      <c r="G175" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H175" s="40" t="n">
+        <v>-0.5</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="40" t="inlineStr">
@@ -12147,12 +12933,17 @@
         <v>1</v>
       </c>
       <c r="E176" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F176" s="40" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G176" s="2" t="n"/>
+        <v>1.667</v>
+      </c>
+      <c r="G176" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H176" s="40" t="n">
+        <v>-0.5</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="40" t="inlineStr">
@@ -12174,12 +12965,17 @@
         <v>5</v>
       </c>
       <c r="E177" s="40" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F177" s="40" t="n">
-        <v>-3</v>
-      </c>
-      <c r="G177" s="2" t="n"/>
+        <v>1.667</v>
+      </c>
+      <c r="G177" s="40" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="H177" s="40" t="n">
+        <v>-1.67</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="39" t="inlineStr">
@@ -12204,9 +13000,14 @@
         <v>5</v>
       </c>
       <c r="F178" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G178" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G178" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H178" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="39" t="inlineStr">
@@ -12231,9 +13032,14 @@
         <v>5</v>
       </c>
       <c r="F179" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G179" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G179" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H179" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="39" t="inlineStr">
@@ -12258,9 +13064,14 @@
         <v>3</v>
       </c>
       <c r="F180" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G180" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="G180" s="2" t="n"/>
+      <c r="H180" s="39" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="40" t="inlineStr">
@@ -12285,9 +13096,14 @@
         <v>0.5</v>
       </c>
       <c r="F181" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G181" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H181" s="40" t="n">
         <v>-1</v>
       </c>
-      <c r="G181" s="2" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="39" t="inlineStr">
@@ -12312,9 +13128,14 @@
         <v>5</v>
       </c>
       <c r="F182" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G182" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G182" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H182" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="40" t="inlineStr">
@@ -12339,9 +13160,14 @@
         <v>0.5</v>
       </c>
       <c r="F183" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G183" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H183" s="40" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G183" s="2" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="40" t="inlineStr">
@@ -12363,12 +13189,17 @@
         <v>1</v>
       </c>
       <c r="E184" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F184" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G184" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="F184" s="40" t="n">
+      <c r="H184" s="40" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G184" s="2" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="40" t="inlineStr">
@@ -12390,12 +13221,17 @@
         <v>1</v>
       </c>
       <c r="E185" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F185" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G185" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="F185" s="40" t="n">
+      <c r="H185" s="40" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G185" s="2" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="40" t="inlineStr">
@@ -12417,12 +13253,17 @@
         <v>7</v>
       </c>
       <c r="E186" s="40" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F186" s="40" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="G186" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G186" s="40" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H186" s="40" t="n">
+        <v>-2.8</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="39" t="inlineStr">
@@ -12447,9 +13288,14 @@
         <v>5</v>
       </c>
       <c r="F187" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G187" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G187" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H187" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="39" t="inlineStr">
@@ -12476,7 +13322,12 @@
       <c r="F188" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="G188" s="2" t="n"/>
+      <c r="G188" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H188" s="39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="40" t="inlineStr">
@@ -12501,9 +13352,14 @@
         <v>0.5</v>
       </c>
       <c r="F189" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G189" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H189" s="40" t="n">
         <v>-1</v>
       </c>
-      <c r="G189" s="2" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="40" t="inlineStr">
@@ -12525,12 +13381,17 @@
         <v>1</v>
       </c>
       <c r="E190" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F190" s="40" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G190" s="2" t="n"/>
+        <v>1.667</v>
+      </c>
+      <c r="G190" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H190" s="40" t="n">
+        <v>-0.5</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="40" t="inlineStr">
@@ -12552,12 +13413,17 @@
         <v>1</v>
       </c>
       <c r="E191" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F191" s="40" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G191" s="2" t="n"/>
+        <v>1.667</v>
+      </c>
+      <c r="G191" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H191" s="40" t="n">
+        <v>-0.5</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="40" t="inlineStr">
@@ -12579,12 +13445,17 @@
         <v>3</v>
       </c>
       <c r="E192" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F192" s="40" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="G192" s="2" t="n"/>
+        <v>1.667</v>
+      </c>
+      <c r="G192" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H192" s="40" t="n">
+        <v>-1.5</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="40" t="inlineStr">
@@ -12606,12 +13477,17 @@
         <v>22</v>
       </c>
       <c r="E193" s="40" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F193" s="40" t="n">
-        <v>-13.2</v>
-      </c>
-      <c r="G193" s="2" t="n"/>
+        <v>1.667</v>
+      </c>
+      <c r="G193" s="40" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="H193" s="40" t="n">
+        <v>-7.33</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="39" t="inlineStr">
@@ -12636,9 +13512,14 @@
         <v>5</v>
       </c>
       <c r="F194" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G194" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G194" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H194" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="39" t="inlineStr">
@@ -12665,7 +13546,12 @@
       <c r="F195" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="G195" s="2" t="n"/>
+      <c r="G195" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H195" s="39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="40" t="inlineStr">
@@ -12690,9 +13576,14 @@
         <v>0.5</v>
       </c>
       <c r="F196" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G196" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H196" s="40" t="n">
         <v>-1</v>
       </c>
-      <c r="G196" s="2" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="40" t="inlineStr">
@@ -12714,12 +13605,17 @@
         <v>1</v>
       </c>
       <c r="E197" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F197" s="40" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G197" s="2" t="n"/>
+        <v>1.667</v>
+      </c>
+      <c r="G197" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H197" s="40" t="n">
+        <v>-0.5</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="40" t="inlineStr">
@@ -12741,12 +13637,17 @@
         <v>1</v>
       </c>
       <c r="E198" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F198" s="40" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G198" s="2" t="n"/>
+        <v>1.667</v>
+      </c>
+      <c r="G198" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H198" s="40" t="n">
+        <v>-0.5</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="40" t="inlineStr">
@@ -12768,12 +13669,17 @@
         <v>1</v>
       </c>
       <c r="E199" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F199" s="40" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G199" s="2" t="n"/>
+        <v>1.667</v>
+      </c>
+      <c r="G199" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H199" s="40" t="n">
+        <v>-0.5</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="40" t="inlineStr">
@@ -12795,12 +13701,17 @@
         <v>17</v>
       </c>
       <c r="E200" s="40" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F200" s="40" t="n">
-        <v>-10.2</v>
-      </c>
-      <c r="G200" s="2" t="n"/>
+        <v>1.667</v>
+      </c>
+      <c r="G200" s="40" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="H200" s="40" t="n">
+        <v>-5.67</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="39" t="inlineStr">
@@ -12825,9 +13736,14 @@
         <v>5</v>
       </c>
       <c r="F201" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G201" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G201" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H201" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="39" t="inlineStr">
@@ -12852,9 +13768,14 @@
         <v>5</v>
       </c>
       <c r="F202" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G202" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G202" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H202" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="39" t="inlineStr">
@@ -12879,9 +13800,14 @@
         <v>3</v>
       </c>
       <c r="F203" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G203" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="G203" s="2" t="n"/>
+      <c r="H203" s="39" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="39" t="inlineStr">
@@ -12908,7 +13834,12 @@
       <c r="F204" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="G204" s="2" t="n"/>
+      <c r="G204" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H204" s="39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="40" t="inlineStr">
@@ -12933,9 +13864,14 @@
         <v>0.5</v>
       </c>
       <c r="F205" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G205" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H205" s="40" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G205" s="2" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="39" t="inlineStr">
@@ -12960,9 +13896,14 @@
         <v>5</v>
       </c>
       <c r="F206" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G206" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G206" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H206" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="39" t="inlineStr">
@@ -12989,7 +13930,12 @@
       <c r="F207" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="G207" s="2" t="n"/>
+      <c r="G207" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H207" s="39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="40" t="inlineStr">
@@ -13014,9 +13960,14 @@
         <v>0.5</v>
       </c>
       <c r="F208" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G208" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H208" s="40" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G208" s="2" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="40" t="inlineStr">
@@ -13038,12 +13989,17 @@
         <v>2</v>
       </c>
       <c r="E209" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F209" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G209" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="F209" s="40" t="n">
+      <c r="H209" s="40" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G209" s="2" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="40" t="inlineStr">
@@ -13065,12 +14021,17 @@
         <v>1</v>
       </c>
       <c r="E210" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F210" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G210" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="F210" s="40" t="n">
+      <c r="H210" s="40" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G210" s="2" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="40" t="inlineStr">
@@ -13092,12 +14053,17 @@
         <v>2</v>
       </c>
       <c r="E211" s="40" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F211" s="40" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="G211" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G211" s="40" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H211" s="40" t="n">
+        <v>-0.8</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="39" t="inlineStr">
@@ -13122,9 +14088,14 @@
         <v>5</v>
       </c>
       <c r="F212" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G212" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G212" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H212" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="39" t="inlineStr">
@@ -13149,9 +14120,14 @@
         <v>5</v>
       </c>
       <c r="F213" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G213" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G213" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H213" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="39" t="inlineStr">
@@ -13176,9 +14152,14 @@
         <v>1</v>
       </c>
       <c r="F214" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G214" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H214" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="G214" s="2" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="40" t="inlineStr">
@@ -13203,9 +14184,14 @@
         <v>0.5</v>
       </c>
       <c r="F215" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G215" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H215" s="40" t="n">
         <v>-1</v>
       </c>
-      <c r="G215" s="2" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="40" t="inlineStr">
@@ -13227,12 +14213,17 @@
         <v>1</v>
       </c>
       <c r="E216" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F216" s="40" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G216" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G216" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H216" s="40" t="n">
+        <v>-0.3</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="40" t="inlineStr">
@@ -13254,12 +14245,17 @@
         <v>1</v>
       </c>
       <c r="E217" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F217" s="40" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G217" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G217" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H217" s="40" t="n">
+        <v>-0.3</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="40" t="inlineStr">
@@ -13281,12 +14277,17 @@
         <v>1</v>
       </c>
       <c r="E218" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F218" s="40" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G218" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G218" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H218" s="40" t="n">
+        <v>-0.3</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="39" t="inlineStr">
@@ -13311,9 +14312,14 @@
         <v>5</v>
       </c>
       <c r="F219" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G219" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G219" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H219" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="39" t="inlineStr">
@@ -13338,9 +14344,14 @@
         <v>5</v>
       </c>
       <c r="F220" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G220" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G220" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H220" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="40" t="inlineStr">
@@ -13365,9 +14376,14 @@
         <v>0.5</v>
       </c>
       <c r="F221" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G221" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H221" s="40" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G221" s="2" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="40" t="inlineStr">
@@ -13389,12 +14405,17 @@
         <v>1</v>
       </c>
       <c r="E222" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F222" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G222" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="F222" s="40" t="n">
+      <c r="H222" s="40" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G222" s="2" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="39" t="inlineStr">
@@ -13419,9 +14440,14 @@
         <v>5</v>
       </c>
       <c r="F223" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G223" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G223" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H223" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="39" t="inlineStr">
@@ -13446,9 +14472,14 @@
         <v>5</v>
       </c>
       <c r="F224" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G224" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G224" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H224" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="39" t="inlineStr">
@@ -13475,7 +14506,12 @@
       <c r="F225" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="G225" s="2" t="n"/>
+      <c r="G225" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H225" s="39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="40" t="inlineStr">
@@ -13500,9 +14536,14 @@
         <v>0.5</v>
       </c>
       <c r="F226" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G226" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H226" s="40" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G226" s="2" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="40" t="inlineStr">
@@ -13524,12 +14565,17 @@
         <v>1</v>
       </c>
       <c r="E227" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F227" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G227" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="F227" s="40" t="n">
+      <c r="H227" s="40" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G227" s="2" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="39" t="inlineStr">
@@ -13554,9 +14600,14 @@
         <v>5</v>
       </c>
       <c r="F228" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G228" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G228" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H228" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="39" t="inlineStr">
@@ -13581,9 +14632,14 @@
         <v>5</v>
       </c>
       <c r="F229" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G229" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G229" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H229" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="39" t="inlineStr">
@@ -13610,7 +14666,12 @@
       <c r="F230" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="G230" s="2" t="n"/>
+      <c r="G230" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H230" s="39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="40" t="inlineStr">
@@ -13635,9 +14696,14 @@
         <v>0.5</v>
       </c>
       <c r="F231" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G231" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H231" s="40" t="n">
         <v>-1</v>
       </c>
-      <c r="G231" s="2" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="40" t="inlineStr">
@@ -13659,12 +14725,17 @@
         <v>2</v>
       </c>
       <c r="E232" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F232" s="40" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="G232" s="2" t="n"/>
+        <v>1.667</v>
+      </c>
+      <c r="G232" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H232" s="40" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="40" t="inlineStr">
@@ -13686,12 +14757,17 @@
         <v>1</v>
       </c>
       <c r="E233" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F233" s="40" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G233" s="2" t="n"/>
+        <v>1.667</v>
+      </c>
+      <c r="G233" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H233" s="40" t="n">
+        <v>-0.5</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="39" t="inlineStr">
@@ -13716,9 +14792,14 @@
         <v>5</v>
       </c>
       <c r="F234" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G234" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G234" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H234" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="39" t="inlineStr">
@@ -13743,9 +14824,14 @@
         <v>5</v>
       </c>
       <c r="F235" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G235" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G235" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H235" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="39" t="inlineStr">
@@ -13772,7 +14858,12 @@
       <c r="F236" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="G236" s="2" t="n"/>
+      <c r="G236" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H236" s="39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="40" t="inlineStr">
@@ -13794,12 +14885,17 @@
         <v>1</v>
       </c>
       <c r="E237" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F237" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G237" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="F237" s="40" t="n">
+      <c r="H237" s="40" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G237" s="2" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="39" t="inlineStr">
@@ -13824,9 +14920,14 @@
         <v>5</v>
       </c>
       <c r="F238" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G238" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G238" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H238" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="39" t="inlineStr">
@@ -13851,9 +14952,14 @@
         <v>5</v>
       </c>
       <c r="F239" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G239" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G239" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H239" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="39" t="inlineStr">
@@ -13878,9 +14984,14 @@
         <v>1</v>
       </c>
       <c r="F240" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G240" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H240" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="G240" s="2" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="40" t="inlineStr">
@@ -13905,9 +15016,14 @@
         <v>0.5</v>
       </c>
       <c r="F241" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G241" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H241" s="40" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G241" s="2" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="40" t="inlineStr">
@@ -13929,12 +15045,17 @@
         <v>1</v>
       </c>
       <c r="E242" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F242" s="40" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G242" s="2" t="n"/>
+        <v>1.667</v>
+      </c>
+      <c r="G242" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H242" s="40" t="n">
+        <v>-0.5</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="40" t="inlineStr">
@@ -13956,12 +15077,17 @@
         <v>1</v>
       </c>
       <c r="E243" s="40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F243" s="40" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G243" s="2" t="n"/>
+        <v>1.667</v>
+      </c>
+      <c r="G243" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H243" s="40" t="n">
+        <v>-0.5</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="39" t="inlineStr">
@@ -13986,9 +15112,14 @@
         <v>5</v>
       </c>
       <c r="F244" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G244" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G244" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H244" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="39" t="inlineStr">
@@ -14015,7 +15146,12 @@
       <c r="F245" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="G245" s="2" t="n"/>
+      <c r="G245" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H245" s="39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="40" t="inlineStr">
@@ -14040,9 +15176,14 @@
         <v>0.5</v>
       </c>
       <c r="F246" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G246" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H246" s="40" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G246" s="2" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="40" t="inlineStr">
@@ -14064,12 +15205,17 @@
         <v>1</v>
       </c>
       <c r="E247" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F247" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G247" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="F247" s="40" t="n">
+      <c r="H247" s="40" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G247" s="2" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="40" t="inlineStr">
@@ -14091,12 +15237,17 @@
         <v>1</v>
       </c>
       <c r="E248" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F248" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G248" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="F248" s="40" t="n">
+      <c r="H248" s="40" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G248" s="2" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="40" t="inlineStr">
@@ -14118,12 +15269,17 @@
         <v>1</v>
       </c>
       <c r="E249" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F249" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G249" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="F249" s="40" t="n">
+      <c r="H249" s="40" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G249" s="2" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="40" t="inlineStr">
@@ -14145,12 +15301,17 @@
         <v>8</v>
       </c>
       <c r="E250" s="40" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F250" s="40" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="G250" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G250" s="40" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H250" s="40" t="n">
+        <v>-3.2</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="39" t="inlineStr">
@@ -14175,9 +15336,14 @@
         <v>5</v>
       </c>
       <c r="F251" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G251" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G251" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H251" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="40" t="inlineStr">
@@ -14202,9 +15368,14 @@
         <v>0.5</v>
       </c>
       <c r="F252" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G252" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H252" s="40" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G252" s="2" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="40" t="inlineStr">
@@ -14226,12 +15397,17 @@
         <v>1</v>
       </c>
       <c r="E253" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F253" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G253" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="F253" s="40" t="n">
+      <c r="H253" s="40" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G253" s="2" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="40" t="inlineStr">
@@ -14253,12 +15429,17 @@
         <v>4</v>
       </c>
       <c r="E254" s="40" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F254" s="40" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="G254" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G254" s="40" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H254" s="40" t="n">
+        <v>-1.6</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="39" t="inlineStr">
@@ -14283,9 +15464,14 @@
         <v>5</v>
       </c>
       <c r="F255" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G255" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G255" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H255" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="39" t="inlineStr">
@@ -14310,9 +15496,14 @@
         <v>5</v>
       </c>
       <c r="F256" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G256" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G256" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H256" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="40" t="inlineStr">
@@ -14337,9 +15528,14 @@
         <v>0.5</v>
       </c>
       <c r="F257" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G257" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H257" s="40" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G257" s="2" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="40" t="inlineStr">
@@ -14361,12 +15557,17 @@
         <v>1</v>
       </c>
       <c r="E258" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F258" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G258" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="F258" s="40" t="n">
+      <c r="H258" s="40" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G258" s="2" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="39" t="inlineStr">
@@ -14391,9 +15592,14 @@
         <v>5</v>
       </c>
       <c r="F259" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G259" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G259" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H259" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="39" t="inlineStr">
@@ -14418,9 +15624,14 @@
         <v>5</v>
       </c>
       <c r="F260" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G260" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G260" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H260" s="39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="40" t="inlineStr">
@@ -14445,9 +15656,14 @@
         <v>0.5</v>
       </c>
       <c r="F261" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G261" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H261" s="40" t="n">
         <v>-1</v>
       </c>
-      <c r="G261" s="2" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="40" t="inlineStr">
@@ -14469,12 +15685,17 @@
         <v>1</v>
       </c>
       <c r="E262" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F262" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G262" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="F262" s="40" t="n">
+      <c r="H262" s="40" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G262" s="2" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="40" t="inlineStr">
@@ -14496,12 +15717,17 @@
         <v>2</v>
       </c>
       <c r="E263" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F263" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G263" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="F263" s="40" t="n">
+      <c r="H263" s="40" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G263" s="2" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="40" t="inlineStr">
@@ -14523,18 +15749,23 @@
         <v>1</v>
       </c>
       <c r="E264" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F264" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G264" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="F264" s="40" t="n">
+      <c r="H264" s="40" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G264" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:G41"/>
+  <autoFilter ref="A2:H41"/>
   <mergeCells count="2">
-    <mergeCell ref="A44:F44"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/historico/semana_318.xlsx
+++ b/data/historico/semana_318.xlsx
@@ -5328,7 +5328,7 @@
       </c>
       <c r="B12" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="C12" s="29" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="B14" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="C14" s="29" t="inlineStr">

--- a/data/historico/semana_318.xlsx
+++ b/data/historico/semana_318.xlsx
@@ -5328,7 +5328,7 @@
       </c>
       <c r="B12" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="C12" s="29" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="B14" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="C14" s="29" t="inlineStr">

--- a/data/historico/semana_318.xlsx
+++ b/data/historico/semana_318.xlsx
@@ -5372,7 +5372,7 @@
       </c>
       <c r="B14" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="C14" s="29" t="inlineStr">

--- a/data/historico/semana_318.xlsx
+++ b/data/historico/semana_318.xlsx
@@ -5372,7 +5372,7 @@
       </c>
       <c r="B14" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="C14" s="29" t="inlineStr">

--- a/data/historico/semana_318.xlsx
+++ b/data/historico/semana_318.xlsx
@@ -5372,7 +5372,7 @@
       </c>
       <c r="B14" s="29" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="C14" s="29" t="inlineStr">

--- a/data/historico/semana_318.xlsx
+++ b/data/historico/semana_318.xlsx
@@ -5372,7 +5372,7 @@
       </c>
       <c r="B14" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="C14" s="29" t="inlineStr">

--- a/data/historico/semana_318.xlsx
+++ b/data/historico/semana_318.xlsx
@@ -5196,7 +5196,7 @@
       </c>
       <c r="B6" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="C6" s="29" t="inlineStr">
